--- a/research/traditional_assets/database/data/poland/poland_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_cable_tv.xlsx
@@ -647,10 +647,10 @@
         <v>0.05003982703686846</v>
       </c>
       <c r="X2">
-        <v>0.133104736896895</v>
+        <v>0.1330689807566186</v>
       </c>
       <c r="Y2">
-        <v>-0.08306490986002654</v>
+        <v>-0.08302915371975014</v>
       </c>
       <c r="Z2">
         <v>1.002235916453073</v>
@@ -659,10 +659,10 @@
         <v>0.08487745472672432</v>
       </c>
       <c r="AB2">
-        <v>0.08271718004636558</v>
+        <v>0.08270564144160499</v>
       </c>
       <c r="AC2">
-        <v>0.002160274680358745</v>
+        <v>0.002171813285119339</v>
       </c>
       <c r="AD2">
         <v>3954.4</v>
@@ -781,10 +781,10 @@
         <v>0.05003982703686846</v>
       </c>
       <c r="X3">
-        <v>0.133104736896895</v>
+        <v>0.1330689807566186</v>
       </c>
       <c r="Y3">
-        <v>-0.08306490986002654</v>
+        <v>-0.08302915371975014</v>
       </c>
       <c r="Z3">
         <v>1.002235916453073</v>
@@ -793,10 +793,10 @@
         <v>0.08487745472672432</v>
       </c>
       <c r="AB3">
-        <v>0.08271718004636558</v>
+        <v>0.08270564144160499</v>
       </c>
       <c r="AC3">
-        <v>0.002160274680358745</v>
+        <v>0.002171813285119339</v>
       </c>
       <c r="AD3">
         <v>3954.4</v>
@@ -1133,49 +1133,49 @@
         <v>1.41086065573771</v>
       </c>
       <c r="F2">
-        <v>13.1738413685733</v>
+        <v>12.8458474023543</v>
       </c>
       <c r="G2">
         <v>5.1576887961393</v>
       </c>
       <c r="H2">
-        <v>1.52302073822877</v>
+        <v>1.59917177514021</v>
       </c>
       <c r="I2">
         <v>0.677297251006252</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K2">
         <v>1884.1</v>
       </c>
       <c r="L2">
-        <v>5503.94015814155</v>
+        <v>5496.74925820292</v>
       </c>
       <c r="M2">
         <v>5038.5</v>
       </c>
       <c r="N2">
-        <v>5871.64015814155</v>
+        <v>5922.83425820292</v>
       </c>
       <c r="O2">
         <v>3954.4</v>
       </c>
       <c r="P2">
-        <v>1167.7</v>
+        <v>1226.085</v>
       </c>
       <c r="Q2">
-        <v>0.08271718004636559</v>
+        <v>0.082705641441605</v>
       </c>
       <c r="R2">
-        <v>0.0774789187780347</v>
+        <v>0.0771952858204657</v>
       </c>
       <c r="S2">
         <v>0.0587096957599802</v>
       </c>
       <c r="T2">
-        <v>0.0486656957599802</v>
+        <v>0.0475316957599802</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.133104736896895</v>
+        <v>0.133068980756619</v>
       </c>
       <c r="X2">
-        <v>0.0846822245325483</v>
+        <v>0.08508054393781</v>
       </c>
       <c r="Y2">
         <v>1.59836203015761</v>
       </c>
       <c r="Z2">
-        <v>0.71184993563732</v>
+        <v>0.719436956978227</v>
       </c>
       <c r="AA2">
         <v>3954.4</v>
@@ -1230,7 +1230,7 @@
         <v>1884.1</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788712</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0781344902557574</v>
+        <v>0.07812124748554304</v>
       </c>
       <c r="C2">
-        <v>6552.59452653635</v>
+        <v>6553.152766974722</v>
       </c>
       <c r="D2">
-        <v>5752.59452653635</v>
+        <v>5753.152766974722</v>
       </c>
       <c r="E2">
         <v>-3954.4</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0781344902557574</v>
+        <v>0.07812124748554304</v>
       </c>
       <c r="T2">
         <v>0.5919749984509941</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0.19</v>
       </c>
       <c r="W2">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07810171168187127</v>
+        <v>0.07807715407292032</v>
       </c>
       <c r="C3">
-        <v>6500.047045197345</v>
+        <v>6502.627076325932</v>
       </c>
       <c r="D3">
-        <v>5758.432045197345</v>
+        <v>5761.012076325932</v>
       </c>
       <c r="E3">
         <v>-3896.015</v>
@@ -1533,37 +1533,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M3">
-        <v>3.507835366600546</v>
+        <v>3.426096366600546</v>
       </c>
       <c r="N3">
-        <v>920.7254979667329</v>
+        <v>920.8072369667329</v>
       </c>
       <c r="O3">
-        <v>174.9378446136792</v>
+        <v>174.9533750236793</v>
       </c>
       <c r="P3">
-        <v>745.7876533530537</v>
+        <v>745.8538619430537</v>
       </c>
       <c r="Q3">
-        <v>1099.387653353054</v>
+        <v>1099.453861943054</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07839904517603179</v>
+        <v>0.07838569405587931</v>
       </c>
       <c r="T3">
         <v>0.5968184302565023</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0.19</v>
       </c>
       <c r="W3">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>263.4768273714655</v>
+        <v>269.7627954494403</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07806893310798513</v>
+        <v>0.07803306066029758</v>
       </c>
       <c r="C4">
-        <v>6447.511423285867</v>
+        <v>6452.12288805781</v>
       </c>
       <c r="D4">
-        <v>5764.281423285867</v>
+        <v>5768.892888057811</v>
       </c>
       <c r="E4">
         <v>-3837.63</v>
@@ -1615,37 +1615,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M4">
-        <v>7.015670733201092</v>
+        <v>6.852192733201091</v>
       </c>
       <c r="N4">
-        <v>917.2176626001324</v>
+        <v>917.3811406001324</v>
       </c>
       <c r="O4">
-        <v>174.2713558940252</v>
+        <v>174.3024167140252</v>
       </c>
       <c r="P4">
-        <v>742.9463067061072</v>
+        <v>743.0787238861072</v>
       </c>
       <c r="Q4">
-        <v>1096.546306706107</v>
+        <v>1096.678723886107</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07866899917631176</v>
+        <v>0.07865553749499794</v>
       </c>
       <c r="T4">
         <v>0.6017607076090616</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0.19</v>
       </c>
       <c r="W4">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>131.7384136857328</v>
+        <v>134.8813977247201</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.078036154534099</v>
+        <v>0.07798896724767486</v>
       </c>
       <c r="C5">
-        <v>6394.98769697885</v>
+        <v>6401.640290534169</v>
       </c>
       <c r="D5">
-        <v>5770.14269697885</v>
+        <v>5776.795290534169</v>
       </c>
       <c r="E5">
         <v>-3779.245</v>
@@ -1697,37 +1697,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M5">
-        <v>10.52350609980164</v>
+        <v>10.27828909980164</v>
       </c>
       <c r="N5">
-        <v>913.7098272335318</v>
+        <v>913.9550442335318</v>
       </c>
       <c r="O5">
-        <v>173.604867174371</v>
+        <v>173.6514584043711</v>
       </c>
       <c r="P5">
-        <v>740.1049600591607</v>
+        <v>740.3035858291607</v>
       </c>
       <c r="Q5">
-        <v>1093.704960059161</v>
+        <v>1093.903585829161</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07894451923845319</v>
+        <v>0.07893094471636644</v>
       </c>
       <c r="T5">
         <v>0.6068048875874469</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0.19</v>
       </c>
       <c r="W5">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>87.82560912382182</v>
+        <v>89.92093181648008</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07800337596021285</v>
+        <v>0.07794487383505212</v>
       </c>
       <c r="C6">
-        <v>6342.475902600527</v>
+        <v>6351.179372603666</v>
       </c>
       <c r="D6">
-        <v>5776.015902600527</v>
+        <v>5784.719372603666</v>
       </c>
       <c r="E6">
         <v>-3720.86</v>
@@ -1779,37 +1779,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M6">
-        <v>14.03134146640218</v>
+        <v>13.70438546640218</v>
       </c>
       <c r="N6">
-        <v>910.2019918669313</v>
+        <v>910.5289478669313</v>
       </c>
       <c r="O6">
-        <v>172.9383784547169</v>
+        <v>173.000500094717</v>
       </c>
       <c r="P6">
-        <v>737.2636134122143</v>
+        <v>737.5284477722143</v>
       </c>
       <c r="Q6">
-        <v>1090.863613412214</v>
+        <v>1091.128447772214</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07922577930188922</v>
+        <v>0.07921208958818013</v>
       </c>
       <c r="T6">
         <v>0.6119541546487152</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0.19</v>
       </c>
       <c r="W6">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>65.86920684286638</v>
+        <v>67.44069886236007</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07797059738632671</v>
+        <v>0.0779007804224294</v>
       </c>
       <c r="C7">
-        <v>6289.976076623171</v>
+        <v>6300.740223603121</v>
       </c>
       <c r="D7">
-        <v>5781.901076623171</v>
+        <v>5792.665223603121</v>
       </c>
       <c r="E7">
         <v>-3662.475</v>
@@ -1861,37 +1861,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M7">
-        <v>17.53917683300273</v>
+        <v>17.13048183300273</v>
       </c>
       <c r="N7">
-        <v>906.6941565003307</v>
+        <v>907.1028515003308</v>
       </c>
       <c r="O7">
-        <v>172.2718897350628</v>
+        <v>172.3495417850629</v>
       </c>
       <c r="P7">
-        <v>734.4222667652679</v>
+        <v>734.753309715268</v>
       </c>
       <c r="Q7">
-        <v>1088.022266765268</v>
+        <v>1088.353309715268</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07951296062981864</v>
+        <v>0.07949915329940041</v>
       </c>
       <c r="T7">
         <v>0.6172118273323259</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0.19</v>
       </c>
       <c r="W7">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.69536547429309</v>
+        <v>53.95255908988805</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07793781881244057</v>
+        <v>0.07785668700980666</v>
       </c>
       <c r="C8">
-        <v>6237.488255667851</v>
+        <v>6250.322933360889</v>
       </c>
       <c r="D8">
-        <v>5787.798255667852</v>
+        <v>5800.632933360889</v>
       </c>
       <c r="E8">
         <v>-3604.09</v>
@@ -1943,37 +1943,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M8">
-        <v>21.04701219960328</v>
+        <v>20.55657819960328</v>
       </c>
       <c r="N8">
-        <v>903.1863211337302</v>
+        <v>903.6767551337302</v>
       </c>
       <c r="O8">
-        <v>171.6054010154087</v>
+        <v>171.6985834754088</v>
       </c>
       <c r="P8">
-        <v>731.5809201183215</v>
+        <v>731.9781716583215</v>
       </c>
       <c r="Q8">
-        <v>1085.180920118321</v>
+        <v>1085.578171658321</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07980625219876783</v>
+        <v>0.07979232474915729</v>
       </c>
       <c r="T8">
         <v>0.6225813653921838</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0.19</v>
       </c>
       <c r="W8">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.91280456191092</v>
+        <v>44.96046590824004</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07790504023855442</v>
+        <v>0.07781259359718393</v>
       </c>
       <c r="C9">
-        <v>6185.012476505199</v>
+        <v>6199.927592200223</v>
       </c>
       <c r="D9">
-        <v>5793.707476505198</v>
+        <v>5808.622592200222</v>
       </c>
       <c r="E9">
         <v>-3545.705</v>
@@ -2025,37 +2025,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M9">
-        <v>24.55484756620383</v>
+        <v>23.98267456620383</v>
       </c>
       <c r="N9">
-        <v>899.6784857671296</v>
+        <v>900.2506587671296</v>
       </c>
       <c r="O9">
-        <v>170.9389122957546</v>
+        <v>171.0476251657546</v>
       </c>
       <c r="P9">
-        <v>728.739573471375</v>
+        <v>729.203033601375</v>
       </c>
       <c r="Q9">
-        <v>1082.339573471375</v>
+        <v>1082.803033601375</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08010585111328583</v>
+        <v>0.08009180096127454</v>
       </c>
       <c r="T9">
         <v>0.6280663773888128</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0.19</v>
       </c>
       <c r="W9">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.63954676735221</v>
+        <v>38.53754220706288</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0778722616646683</v>
+        <v>0.07776850018456122</v>
       </c>
       <c r="C10">
-        <v>6132.548776056155</v>
+        <v>6149.554290942697</v>
       </c>
       <c r="D10">
-        <v>5799.628776056154</v>
+        <v>5816.634290942697</v>
       </c>
       <c r="E10">
         <v>-3487.32</v>
@@ -2107,37 +2107,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M10">
-        <v>28.06268293280437</v>
+        <v>27.40877093280437</v>
       </c>
       <c r="N10">
-        <v>896.1706504005291</v>
+        <v>896.8245624005291</v>
       </c>
       <c r="O10">
-        <v>170.2724235761005</v>
+        <v>170.3966668561005</v>
       </c>
       <c r="P10">
-        <v>725.8982268244285</v>
+        <v>726.4278955444286</v>
       </c>
       <c r="Q10">
-        <v>1079.498226824428</v>
+        <v>1080.027895544429</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08041196304768466</v>
+        <v>0.08039778752582913</v>
       </c>
       <c r="T10">
         <v>0.6336706287766729</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.93460342143319</v>
+        <v>33.72034943118003</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07783948309078217</v>
+        <v>0.07772440677193848</v>
       </c>
       <c r="C11">
-        <v>6080.09719139277</v>
+        <v>6099.20312091167</v>
       </c>
       <c r="D11">
-        <v>5805.56219139277</v>
+        <v>5824.66812091167</v>
       </c>
       <c r="E11">
         <v>-3428.935</v>
@@ -2189,37 +2189,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M11">
-        <v>31.57051829940492</v>
+        <v>30.83486729940492</v>
       </c>
       <c r="N11">
-        <v>892.6628150339285</v>
+        <v>893.3984660339286</v>
       </c>
       <c r="O11">
-        <v>169.6059348564464</v>
+        <v>169.7457085464464</v>
       </c>
       <c r="P11">
-        <v>723.0568801774821</v>
+        <v>723.6527574874822</v>
       </c>
       <c r="Q11">
-        <v>1076.656880177482</v>
+        <v>1077.252757487482</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08072480271690544</v>
+        <v>0.08071049906982446</v>
       </c>
       <c r="T11">
         <v>0.6393980505247056</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0.19</v>
       </c>
       <c r="W11">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.27520304127394</v>
+        <v>29.97364393882669</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07780670451689603</v>
+        <v>0.07768031335931574</v>
       </c>
       <c r="C12">
-        <v>6027.65775973895</v>
+        <v>6048.874173935716</v>
       </c>
       <c r="D12">
-        <v>5811.50775973895</v>
+        <v>5832.724173935717</v>
       </c>
       <c r="E12">
         <v>-3370.55</v>
@@ -2271,37 +2271,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M12">
-        <v>35.07835366600546</v>
+        <v>34.26096366600546</v>
       </c>
       <c r="N12">
-        <v>889.154979667328</v>
+        <v>889.9723696673281</v>
       </c>
       <c r="O12">
-        <v>168.9394461367923</v>
+        <v>169.0947502367923</v>
       </c>
       <c r="P12">
-        <v>720.2155335305357</v>
+        <v>720.8776194305358</v>
       </c>
       <c r="Q12">
-        <v>1073.815533530536</v>
+        <v>1074.477619430536</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08104459437877556</v>
+        <v>0.08103015975924192</v>
       </c>
       <c r="T12">
         <v>0.6452527483115836</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.34768273714655</v>
+        <v>26.97627954494402</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0777739259430099</v>
+        <v>0.07763621994669301</v>
       </c>
       <c r="C13">
-        <v>5975.230518471236</v>
+        <v>5998.567542352149</v>
       </c>
       <c r="D13">
-        <v>5817.465518471236</v>
+        <v>5840.802542352149</v>
       </c>
       <c r="E13">
         <v>-3312.165</v>
@@ -2353,37 +2353,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M13">
-        <v>38.58618903260601</v>
+        <v>37.68706003260601</v>
       </c>
       <c r="N13">
-        <v>885.6471443007274</v>
+        <v>886.5462733007274</v>
       </c>
       <c r="O13">
-        <v>168.2729574171382</v>
+        <v>168.4437919271382</v>
       </c>
       <c r="P13">
-        <v>717.3741868835892</v>
+        <v>718.1024813735892</v>
       </c>
       <c r="Q13">
-        <v>1070.974186883589</v>
+        <v>1071.702481373589</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08137157237012593</v>
+        <v>0.08135700383493841</v>
       </c>
       <c r="T13">
         <v>0.6512390123408632</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.95243885195141</v>
+        <v>24.52389049540366</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07774114736912374</v>
+        <v>0.07759212653407027</v>
       </c>
       <c r="C14">
-        <v>5922.815505119608</v>
+        <v>5948.283319010541</v>
       </c>
       <c r="D14">
-        <v>5823.435505119608</v>
+        <v>5848.903319010541</v>
       </c>
       <c r="E14">
         <v>-3253.78</v>
@@ -2435,37 +2435,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M14">
-        <v>42.09402439920655</v>
+        <v>41.11315639920655</v>
       </c>
       <c r="N14">
-        <v>882.1393089341269</v>
+        <v>883.1201769341269</v>
       </c>
       <c r="O14">
-        <v>167.6064686974841</v>
+        <v>167.7928336174841</v>
       </c>
       <c r="P14">
-        <v>714.5328402366429</v>
+        <v>715.3273433166428</v>
       </c>
       <c r="Q14">
-        <v>1068.132840236643</v>
+        <v>1068.927343316643</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08170598167946151</v>
+        <v>0.08169127618508257</v>
       </c>
       <c r="T14">
         <v>0.6573613278253538</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V14">
         <v>0.19</v>
       </c>
       <c r="W14">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.95640228095546</v>
+        <v>22.48023295412002</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07770836879523761</v>
+        <v>0.07754803312144756</v>
       </c>
       <c r="C15">
-        <v>5870.412757368246</v>
+        <v>5898.021597276283</v>
       </c>
       <c r="D15">
-        <v>5829.417757368246</v>
+        <v>5857.026597276283</v>
       </c>
       <c r="E15">
         <v>-3195.395</v>
@@ -2517,37 +2517,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M15">
-        <v>45.6018597658071</v>
+        <v>44.5392527658071</v>
       </c>
       <c r="N15">
-        <v>878.6314735675263</v>
+        <v>879.6940805675264</v>
       </c>
       <c r="O15">
-        <v>166.93997997783</v>
+        <v>167.14187530783</v>
       </c>
       <c r="P15">
-        <v>711.6914935896963</v>
+        <v>712.5522052596964</v>
       </c>
       <c r="Q15">
-        <v>1065.291493589696</v>
+        <v>1066.152205259697</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08204807855912666</v>
+        <v>0.08203323295706912</v>
       </c>
       <c r="T15">
         <v>0.6636243861945454</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.2674482593435</v>
+        <v>20.75098426534156</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07767559022135148</v>
+        <v>0.07750393970882481</v>
       </c>
       <c r="C16">
-        <v>5818.022313056348</v>
+        <v>5847.782471034181</v>
       </c>
       <c r="D16">
-        <v>5835.412313056348</v>
+        <v>5865.172471034181</v>
       </c>
       <c r="E16">
         <v>-3137.01</v>
@@ -2599,37 +2599,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M16">
-        <v>49.10969513240765</v>
+        <v>47.96534913240765</v>
       </c>
       <c r="N16">
-        <v>875.1236382009258</v>
+        <v>876.2679842009259</v>
       </c>
       <c r="O16">
-        <v>166.2734912581759</v>
+        <v>166.4909169981759</v>
       </c>
       <c r="P16">
-        <v>708.8501469427499</v>
+        <v>709.77706720275</v>
       </c>
       <c r="Q16">
-        <v>1062.45014694275</v>
+        <v>1063.37706720275</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08239813118017937</v>
+        <v>0.08238314221212512</v>
       </c>
       <c r="T16">
         <v>0.6700330970839508</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.8197733836761</v>
+        <v>19.26877110353144</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07764281164746535</v>
+        <v>0.07745984629620209</v>
       </c>
       <c r="C17">
-        <v>5765.644210178914</v>
+        <v>5797.566034692046</v>
       </c>
       <c r="D17">
-        <v>5841.419210178914</v>
+        <v>5873.341034692045</v>
       </c>
       <c r="E17">
         <v>-3078.625</v>
@@ -2681,37 +2681,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M17">
-        <v>52.61753049900819</v>
+        <v>51.39144549900819</v>
       </c>
       <c r="N17">
-        <v>871.6158028343252</v>
+        <v>872.8418878343252</v>
       </c>
       <c r="O17">
-        <v>165.6070025385218</v>
+        <v>165.8399586885218</v>
       </c>
       <c r="P17">
-        <v>706.0088002958034</v>
+        <v>707.0019291458034</v>
       </c>
       <c r="Q17">
-        <v>1059.608800295804</v>
+        <v>1060.601929145803</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08275642033349215</v>
+        <v>0.08274128462612361</v>
       </c>
       <c r="T17">
         <v>0.6765926011707539</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.56512182476436</v>
+        <v>17.98418636329601</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07761003307357919</v>
+        <v>0.07741575288357935</v>
       </c>
       <c r="C18">
-        <v>5713.278486887554</v>
+        <v>5747.372383184374</v>
       </c>
       <c r="D18">
-        <v>5847.438486887554</v>
+        <v>5881.532383184374</v>
       </c>
       <c r="E18">
         <v>-3020.24</v>
@@ -2763,37 +2763,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M18">
-        <v>56.12536586560874</v>
+        <v>54.81754186560873</v>
       </c>
       <c r="N18">
-        <v>868.1079674677247</v>
+        <v>869.4157914677247</v>
       </c>
       <c r="O18">
-        <v>164.9405138188677</v>
+        <v>165.1890003788677</v>
       </c>
       <c r="P18">
-        <v>703.167453648857</v>
+        <v>704.226791088857</v>
       </c>
       <c r="Q18">
-        <v>1056.767453648857</v>
+        <v>1057.826791088857</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0831232401809314</v>
+        <v>0.0831079542404554</v>
       </c>
       <c r="T18">
         <v>0.6833082839262904</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.46730171071659</v>
+        <v>16.86017471559001</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07757725449969308</v>
+        <v>0.07737165947095663</v>
       </c>
       <c r="C19">
-        <v>5660.925181491279</v>
+        <v>5697.201611975996</v>
       </c>
       <c r="D19">
-        <v>5853.470181491279</v>
+        <v>5889.746611975997</v>
       </c>
       <c r="E19">
         <v>-2961.855</v>
@@ -2845,37 +2845,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M19">
-        <v>59.63320123220929</v>
+        <v>58.24363823220929</v>
       </c>
       <c r="N19">
-        <v>864.6001321011241</v>
+        <v>865.9896951011242</v>
       </c>
       <c r="O19">
-        <v>164.2740250992136</v>
+        <v>164.5380420692136</v>
       </c>
       <c r="P19">
-        <v>700.3261070019105</v>
+        <v>701.4516530319106</v>
       </c>
       <c r="Q19">
-        <v>1053.926107001911</v>
+        <v>1055.051653031911</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08349889906083909</v>
+        <v>0.08348345926718073</v>
       </c>
       <c r="T19">
         <v>0.6901857903626831</v>
       </c>
       <c r="U19">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.49863690420385</v>
+        <v>15.86839973232001</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07754447592580693</v>
+        <v>0.07732756605833391</v>
       </c>
       <c r="C20">
-        <v>5608.584332457349</v>
+        <v>5647.053817065811</v>
       </c>
       <c r="D20">
-        <v>5859.514332457349</v>
+        <v>5897.983817065811</v>
       </c>
       <c r="E20">
         <v>-2903.47</v>
@@ -2927,37 +2927,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M20">
-        <v>63.14103659880983</v>
+        <v>61.66973459880983</v>
       </c>
       <c r="N20">
-        <v>861.0922967345236</v>
+        <v>862.5635987345237</v>
       </c>
       <c r="O20">
-        <v>163.6075363795595</v>
+        <v>163.8870837595595</v>
       </c>
       <c r="P20">
-        <v>697.4847603549641</v>
+        <v>698.6765149749642</v>
       </c>
       <c r="Q20">
-        <v>1051.084760354964</v>
+        <v>1052.276514974964</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08388372035245183</v>
+        <v>0.08386812295309448</v>
       </c>
       <c r="T20">
         <v>0.6972310408585001</v>
       </c>
       <c r="U20">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.63760152063697</v>
+        <v>14.98682196941335</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0775116973519208</v>
+        <v>0.07728347264571117</v>
       </c>
       <c r="C21">
-        <v>5556.255978412053</v>
+        <v>5596.929094990506</v>
       </c>
       <c r="D21">
-        <v>5865.570978412053</v>
+        <v>5906.244094990506</v>
       </c>
       <c r="E21">
         <v>-2845.085</v>
@@ -3009,37 +3009,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M21">
-        <v>66.64887196541038</v>
+        <v>65.09583096541037</v>
       </c>
       <c r="N21">
-        <v>857.584461367923</v>
+        <v>859.137502367923</v>
       </c>
       <c r="O21">
-        <v>162.9410476599054</v>
+        <v>163.2361254499054</v>
       </c>
       <c r="P21">
-        <v>694.6434137080176</v>
+        <v>695.9013769180176</v>
       </c>
       <c r="Q21">
-        <v>1048.243413708018</v>
+        <v>1049.501376918018</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08427804340435131</v>
+        <v>0.08426228450779621</v>
       </c>
       <c r="T21">
         <v>0.704450248156683</v>
       </c>
       <c r="U21">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V21">
         <v>0.19</v>
       </c>
       <c r="W21">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.86720144060344</v>
+        <v>14.19804186576001</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07747891877803467</v>
+        <v>0.07723937923308846</v>
       </c>
       <c r="C22">
-        <v>5503.940158141554</v>
+        <v>5546.82754282833</v>
       </c>
       <c r="D22">
-        <v>5871.640158141554</v>
+        <v>5914.527542828329</v>
       </c>
       <c r="E22">
         <v>-2786.7</v>
@@ -3091,37 +3091,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M22">
-        <v>70.15670733201092</v>
+        <v>68.52192733201092</v>
       </c>
       <c r="N22">
-        <v>854.0766260013226</v>
+        <v>855.7114060013225</v>
       </c>
       <c r="O22">
-        <v>162.2745589402513</v>
+        <v>162.5851671402513</v>
       </c>
       <c r="P22">
-        <v>691.8020670610713</v>
+        <v>693.1262388610712</v>
       </c>
       <c r="Q22">
-        <v>1045.402067061071</v>
+        <v>1046.726238861071</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08468222453254828</v>
+        <v>0.08466630010136551</v>
       </c>
       <c r="T22">
         <v>0.7118499356373205</v>
       </c>
       <c r="U22">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.04866569575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.17384136857327</v>
+        <v>13.48813977247201</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07763325020414853</v>
+        <v>0.07719528582046573</v>
       </c>
       <c r="C23">
-        <v>5417.088740373278</v>
+        <v>5496.749258202918</v>
       </c>
       <c r="D23">
-        <v>5843.173740373278</v>
+        <v>5922.834258202918</v>
       </c>
       <c r="E23">
         <v>-2728.315</v>
@@ -3173,45 +3173,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M23">
-        <v>75.01323619861147</v>
+        <v>71.94802369861146</v>
       </c>
       <c r="N23">
-        <v>849.220097134722</v>
+        <v>852.285309634722</v>
       </c>
       <c r="O23">
-        <v>161.3518184555972</v>
+        <v>161.9342088305972</v>
       </c>
       <c r="P23">
-        <v>687.8682786791248</v>
+        <v>690.3511008041248</v>
       </c>
       <c r="Q23">
-        <v>1041.468278679125</v>
+        <v>1043.951100804125</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08509663809437049</v>
+        <v>0.08508054393780998</v>
       </c>
       <c r="T23">
         <v>0.7194369569782272</v>
       </c>
       <c r="U23">
-        <v>0.06118110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V23">
         <v>0.19</v>
       </c>
       <c r="W23">
-        <v>0.04955669575998017</v>
+        <v>0.04753169575998017</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.32093667957818</v>
+        <v>12.8458474023543</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07760938163026239</v>
+        <v>0.07741849240784299</v>
       </c>
       <c r="C24">
-        <v>5363.088240071284</v>
+        <v>5396.552788974021</v>
       </c>
       <c r="D24">
-        <v>5847.558240071285</v>
+        <v>5881.022788974022</v>
       </c>
       <c r="E24">
         <v>-2669.93</v>
@@ -3255,37 +3255,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M24">
-        <v>78.58529506521201</v>
+        <v>77.30082506521201</v>
       </c>
       <c r="N24">
-        <v>845.6480382681215</v>
+        <v>846.9325082681214</v>
       </c>
       <c r="O24">
-        <v>160.6731272709431</v>
+        <v>160.9171765709431</v>
       </c>
       <c r="P24">
-        <v>684.9749109971784</v>
+        <v>686.0153316971783</v>
       </c>
       <c r="Q24">
-        <v>1038.574910997178</v>
+        <v>1039.615331697178</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08552167764495737</v>
+        <v>0.08550540941108634</v>
       </c>
       <c r="T24">
         <v>0.7272185173278751</v>
       </c>
       <c r="U24">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.04955669575998017</v>
+        <v>0.04874669575998017</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.76089410323372</v>
+        <v>11.9563191279477</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07758551305637625</v>
+        <v>0.07738654899522027</v>
       </c>
       <c r="C25">
-        <v>5309.094324640506</v>
+        <v>5344.115255334473</v>
       </c>
       <c r="D25">
-        <v>5851.949324640506</v>
+        <v>5886.970255334473</v>
       </c>
       <c r="E25">
         <v>-2611.545</v>
@@ -3337,37 +3337,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M25">
-        <v>82.15735393181255</v>
+        <v>80.81449893181255</v>
       </c>
       <c r="N25">
-        <v>842.075979401521</v>
+        <v>843.4188344015209</v>
       </c>
       <c r="O25">
-        <v>159.994436086289</v>
+        <v>160.249578536289</v>
       </c>
       <c r="P25">
-        <v>682.081543315232</v>
+        <v>683.1692558652319</v>
       </c>
       <c r="Q25">
-        <v>1035.681543315232</v>
+        <v>1036.769255865232</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08595775718387116</v>
+        <v>0.08594131035120106</v>
       </c>
       <c r="T25">
         <v>0.7352021961281632</v>
       </c>
       <c r="U25">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.04955669575998017</v>
+        <v>0.04874669575998017</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.24955088135399</v>
+        <v>11.43647916586302</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0775616444824901</v>
+        <v>0.07735460558259752</v>
       </c>
       <c r="C26">
-        <v>5255.107008926349</v>
+        <v>5291.689763193691</v>
       </c>
       <c r="D26">
-        <v>5856.347008926349</v>
+        <v>5892.929763193691</v>
       </c>
       <c r="E26">
         <v>-2553.16</v>
@@ -3419,37 +3419,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M26">
-        <v>85.72941279841309</v>
+        <v>84.32817279841309</v>
       </c>
       <c r="N26">
-        <v>838.5039205349203</v>
+        <v>839.9051605349204</v>
       </c>
       <c r="O26">
-        <v>159.3157449016349</v>
+        <v>159.5819805016349</v>
       </c>
       <c r="P26">
-        <v>679.1881756332855</v>
+        <v>680.3231800332856</v>
       </c>
       <c r="Q26">
-        <v>1032.788175633285</v>
+        <v>1033.923180033285</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08640531250012483</v>
+        <v>0.08638868236868721</v>
       </c>
       <c r="T26">
         <v>0.7433959717389853</v>
       </c>
       <c r="U26">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V26">
         <v>0.19</v>
       </c>
       <c r="W26">
-        <v>0.04955669575998017</v>
+        <v>0.04874669575998017</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.78081959463091</v>
+        <v>10.95995920061873</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07753777590860397</v>
+        <v>0.0773226621699748</v>
       </c>
       <c r="C27">
-        <v>5201.12630781887</v>
+        <v>5239.276349158334</v>
       </c>
       <c r="D27">
-        <v>5860.75130781887</v>
+        <v>5898.901349158334</v>
       </c>
       <c r="E27">
         <v>-2494.775</v>
@@ -3501,37 +3501,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M27">
-        <v>89.30147166501365</v>
+        <v>87.84184666501365</v>
       </c>
       <c r="N27">
-        <v>834.9318616683198</v>
+        <v>836.3914866683198</v>
       </c>
       <c r="O27">
-        <v>158.6370537169808</v>
+        <v>158.9143824669808</v>
       </c>
       <c r="P27">
-        <v>676.2948079513391</v>
+        <v>677.477104201339</v>
       </c>
       <c r="Q27">
-        <v>1029.894807951339</v>
+        <v>1031.077104201339</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0868648026248119</v>
+        <v>0.08684798430663966</v>
       </c>
       <c r="T27">
         <v>0.7518082480327625</v>
       </c>
       <c r="U27">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.04955669575998017</v>
+        <v>0.04874669575998017</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.34958681084567</v>
+        <v>10.52156083259398</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07751390733471784</v>
+        <v>0.07729071875735206</v>
       </c>
       <c r="C28">
-        <v>5147.152236252963</v>
+        <v>5186.875049983611</v>
       </c>
       <c r="D28">
-        <v>5865.162236252963</v>
+        <v>5904.885049983612</v>
       </c>
       <c r="E28">
         <v>-2436.39</v>
@@ -3583,37 +3583,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M28">
-        <v>92.87353053161419</v>
+        <v>91.35552053161419</v>
       </c>
       <c r="N28">
-        <v>831.3598028017193</v>
+        <v>832.8778128017193</v>
       </c>
       <c r="O28">
-        <v>157.9583625323267</v>
+        <v>158.2467844323267</v>
       </c>
       <c r="P28">
-        <v>673.4014402693927</v>
+        <v>674.6310283693927</v>
       </c>
       <c r="Q28">
-        <v>1027.001440269393</v>
+        <v>1028.231028369393</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08733671140151755</v>
+        <v>0.08731969981048272</v>
       </c>
       <c r="T28">
         <v>0.7604478831452905</v>
       </c>
       <c r="U28">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V28">
         <v>0.19</v>
       </c>
       <c r="W28">
-        <v>0.04955669575998017</v>
+        <v>0.04874669575998017</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.951525779659297</v>
+        <v>10.11688541595575</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07797117876083169</v>
+        <v>0.07763056534472934</v>
       </c>
       <c r="C29">
-        <v>5005.401590247298</v>
+        <v>5065.445142946661</v>
       </c>
       <c r="D29">
-        <v>5781.796590247299</v>
+        <v>5841.840142946661</v>
       </c>
       <c r="E29">
         <v>-2378.005</v>
@@ -3665,37 +3665,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M29">
-        <v>99.91365839821475</v>
+        <v>97.54906589821475</v>
       </c>
       <c r="N29">
-        <v>824.3196749351187</v>
+        <v>826.6842674351187</v>
       </c>
       <c r="O29">
-        <v>156.6207382376726</v>
+        <v>157.0700108126726</v>
       </c>
       <c r="P29">
-        <v>667.6989366974461</v>
+        <v>669.6142566224462</v>
       </c>
       <c r="Q29">
-        <v>1021.298936697446</v>
+        <v>1023.214256622446</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08782154918580418</v>
+        <v>0.08780433902675985</v>
       </c>
       <c r="T29">
         <v>0.7693242205896687</v>
       </c>
       <c r="U29">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V29">
         <v>0.19</v>
       </c>
       <c r="W29">
-        <v>0.05133869575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.250320207971161</v>
+        <v>9.474548267819424</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07796513018694555</v>
+        <v>0.07761239193210659</v>
       </c>
       <c r="C30">
-        <v>4948.103842923332</v>
+        <v>5010.397401321339</v>
       </c>
       <c r="D30">
-        <v>5782.883842923333</v>
+        <v>5845.177401321339</v>
       </c>
       <c r="E30">
         <v>-2319.62</v>
@@ -3747,37 +3747,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M30">
-        <v>103.6141642648153</v>
+        <v>101.1619942648153</v>
       </c>
       <c r="N30">
-        <v>820.6191690685182</v>
+        <v>823.0713390685182</v>
       </c>
       <c r="O30">
-        <v>155.9176421230185</v>
+        <v>156.3835544230185</v>
       </c>
       <c r="P30">
-        <v>664.7015269454997</v>
+        <v>666.6877846454997</v>
       </c>
       <c r="Q30">
-        <v>1018.3015269455</v>
+        <v>1020.2877846455</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08831985468632098</v>
+        <v>0.08830244044348909</v>
       </c>
       <c r="T30">
         <v>0.7784471229630572</v>
       </c>
       <c r="U30">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.05133869575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.919951629115049</v>
+        <v>9.136171543968732</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07795908161305942</v>
+        <v>0.07759421851948388</v>
       </c>
       <c r="C31">
-        <v>4890.806504586674</v>
+        <v>4955.353474815631</v>
       </c>
       <c r="D31">
-        <v>5783.971504586674</v>
+        <v>5848.518474815631</v>
       </c>
       <c r="E31">
         <v>-2261.235</v>
@@ -3829,37 +3829,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M31">
-        <v>107.3146701314158</v>
+        <v>104.7749226314158</v>
       </c>
       <c r="N31">
-        <v>816.9186632019176</v>
+        <v>819.4584107019176</v>
       </c>
       <c r="O31">
-        <v>155.2145460083644</v>
+        <v>155.6970980333643</v>
       </c>
       <c r="P31">
-        <v>661.7041171935533</v>
+        <v>663.7613126685533</v>
       </c>
       <c r="Q31">
-        <v>1015.304117193553</v>
+        <v>1017.361312668553</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08883219696150024</v>
+        <v>0.08881457288604172</v>
       </c>
       <c r="T31">
         <v>0.7878270085018935</v>
       </c>
       <c r="U31">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V31">
         <v>0.19</v>
       </c>
       <c r="W31">
-        <v>0.05133869575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.612367090180047</v>
+        <v>8.821131145900846</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07795303303917328</v>
+        <v>0.07757604510686113</v>
       </c>
       <c r="C32">
-        <v>4833.509575468143</v>
+        <v>4900.313369975402</v>
       </c>
       <c r="D32">
-        <v>5785.059575468144</v>
+        <v>5851.863369975402</v>
       </c>
       <c r="E32">
         <v>-2202.85</v>
@@ -3911,37 +3911,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M32">
-        <v>111.0151759980164</v>
+        <v>108.3878509980164</v>
       </c>
       <c r="N32">
-        <v>813.2181573353171</v>
+        <v>815.8454823353171</v>
       </c>
       <c r="O32">
-        <v>154.5114498937102</v>
+        <v>155.0106416437102</v>
       </c>
       <c r="P32">
-        <v>658.7067074416068</v>
+        <v>660.8348406916068</v>
       </c>
       <c r="Q32">
-        <v>1012.306707441607</v>
+        <v>1014.434840691607</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08935917758739891</v>
+        <v>0.08934133768409584</v>
       </c>
       <c r="T32">
         <v>0.7974748907704107</v>
       </c>
       <c r="U32">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.05133869575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.325288187174046</v>
+        <v>8.527093441037483</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07794698446528714</v>
+        <v>0.0775578716942384</v>
       </c>
       <c r="C33">
-        <v>4776.213055798724</v>
+        <v>4845.277093361474</v>
       </c>
       <c r="D33">
-        <v>5786.148055798724</v>
+        <v>5855.212093361473</v>
       </c>
       <c r="E33">
         <v>-2144.465</v>
@@ -3993,37 +3993,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M33">
-        <v>114.7156818646169</v>
+        <v>112.0007793646169</v>
       </c>
       <c r="N33">
-        <v>809.5176514687165</v>
+        <v>812.2325539687165</v>
       </c>
       <c r="O33">
-        <v>153.8083537790561</v>
+        <v>154.3241852540561</v>
       </c>
       <c r="P33">
-        <v>655.7092976896604</v>
+        <v>657.9083687146604</v>
       </c>
       <c r="Q33">
-        <v>1009.30929768966</v>
+        <v>1011.50836871466</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08990143301404825</v>
+        <v>0.0898833710270211</v>
       </c>
       <c r="T33">
         <v>0.8074024218003342</v>
       </c>
       <c r="U33">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V33">
         <v>0.19</v>
       </c>
       <c r="W33">
-        <v>0.05133869575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.056730503716819</v>
+        <v>8.252025910681436</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.077940935891401</v>
+        <v>0.07753969828161567</v>
       </c>
       <c r="C34">
-        <v>4718.916945809578</v>
+        <v>4790.244651549714</v>
       </c>
       <c r="D34">
-        <v>5787.236945809578</v>
+        <v>5858.564651549714</v>
       </c>
       <c r="E34">
         <v>-2086.08</v>
@@ -4075,37 +4075,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M34">
-        <v>118.4161877312175</v>
+        <v>115.6137077312175</v>
       </c>
       <c r="N34">
-        <v>805.8171456021159</v>
+        <v>808.619625602116</v>
       </c>
       <c r="O34">
-        <v>153.105257664402</v>
+        <v>153.637728864402</v>
       </c>
       <c r="P34">
-        <v>652.711887937714</v>
+        <v>654.9818967377139</v>
       </c>
       <c r="Q34">
-        <v>1006.311887937714</v>
+        <v>1008.581896737714</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09045963712971669</v>
+        <v>0.09044134652709121</v>
       </c>
       <c r="T34">
         <v>0.8176219390370202</v>
       </c>
       <c r="U34">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.05133869575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.804957675475668</v>
+        <v>7.994150100972641</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07833583731751488</v>
+        <v>0.07752152486899296</v>
       </c>
       <c r="C35">
-        <v>4590.289766367377</v>
+        <v>4735.216051131043</v>
       </c>
       <c r="D35">
-        <v>5716.994766367377</v>
+        <v>5861.921051131043</v>
       </c>
       <c r="E35">
         <v>-2027.695</v>
@@ -4157,45 +4157,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M35">
-        <v>125.006751097818</v>
+        <v>119.226636097818</v>
       </c>
       <c r="N35">
-        <v>799.2265822355155</v>
+        <v>805.0066972355155</v>
       </c>
       <c r="O35">
-        <v>151.8530506247479</v>
+        <v>152.951272474748</v>
       </c>
       <c r="P35">
-        <v>647.3735316107675</v>
+        <v>652.0554247607676</v>
       </c>
       <c r="Q35">
-        <v>1000.973531610768</v>
+        <v>1005.655424760768</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09103450405480809</v>
+        <v>0.09101597801223806</v>
       </c>
       <c r="T35">
         <v>0.8281465164897266</v>
       </c>
       <c r="U35">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V35">
         <v>0.19</v>
       </c>
       <c r="W35">
-        <v>0.05255369575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.393467354496072</v>
+        <v>7.751903128215894</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07834193874362874</v>
+        <v>0.07772367145637023</v>
       </c>
       <c r="C36">
-        <v>4530.83286277137</v>
+        <v>4639.712283711681</v>
       </c>
       <c r="D36">
-        <v>5715.92286277137</v>
+        <v>5824.802283711681</v>
       </c>
       <c r="E36">
         <v>-1969.31</v>
@@ -4239,37 +4239,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M36">
-        <v>128.7948344644186</v>
+        <v>124.4276364644186</v>
       </c>
       <c r="N36">
-        <v>795.4384988689148</v>
+        <v>799.8056968689149</v>
       </c>
       <c r="O36">
-        <v>151.1333147850938</v>
+        <v>151.9630824050938</v>
       </c>
       <c r="P36">
-        <v>644.305184083821</v>
+        <v>647.8426144638211</v>
       </c>
       <c r="Q36">
-        <v>997.905184083821</v>
+        <v>1001.442614463821</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09162679118975073</v>
+        <v>0.09160802257269238</v>
       </c>
       <c r="T36">
         <v>0.8389900205319091</v>
       </c>
       <c r="U36">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.05255369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.176012432305011</v>
+        <v>7.427878239876621</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07834804016974259</v>
+        <v>0.07771197804374749</v>
       </c>
       <c r="C37">
-        <v>4471.37636105152</v>
+        <v>4583.461648947704</v>
       </c>
       <c r="D37">
-        <v>5714.85136105152</v>
+        <v>5826.936648947704</v>
       </c>
       <c r="E37">
         <v>-1910.925</v>
@@ -4321,37 +4321,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M37">
-        <v>132.5829178310191</v>
+        <v>128.0872728310191</v>
       </c>
       <c r="N37">
-        <v>791.6504155023143</v>
+        <v>796.1460605023143</v>
       </c>
       <c r="O37">
-        <v>150.4135789454397</v>
+        <v>151.2677514954397</v>
       </c>
       <c r="P37">
-        <v>641.2368365568746</v>
+        <v>644.8783090068746</v>
       </c>
       <c r="Q37">
-        <v>994.8368365568746</v>
+        <v>998.4783090068746</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09223730254423006</v>
+        <v>0.09221828388885298</v>
       </c>
       <c r="T37">
         <v>0.8501671708523123</v>
       </c>
       <c r="U37">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.05255369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.970983505667725</v>
+        <v>7.215653147308716</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07835414159585646</v>
+        <v>0.07770028463112476</v>
       </c>
       <c r="C38">
-        <v>4411.920260981853</v>
+        <v>4527.212578935494</v>
       </c>
       <c r="D38">
-        <v>5713.780260981854</v>
+        <v>5829.072578935495</v>
       </c>
       <c r="E38">
         <v>-1852.54</v>
@@ -4403,37 +4403,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M38">
-        <v>136.3710011976196</v>
+        <v>131.7469091976197</v>
       </c>
       <c r="N38">
-        <v>787.8623321357138</v>
+        <v>792.4864241357138</v>
       </c>
       <c r="O38">
-        <v>149.6938431057856</v>
+        <v>150.5724205857856</v>
       </c>
       <c r="P38">
-        <v>638.1684890299282</v>
+        <v>641.9140035499282</v>
       </c>
       <c r="Q38">
-        <v>991.7684890299282</v>
+        <v>995.5140035499282</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09286689237853687</v>
+        <v>0.0928476158711436</v>
       </c>
       <c r="T38">
         <v>0.8616936071202282</v>
       </c>
       <c r="U38">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V38">
         <v>0.19</v>
       </c>
       <c r="W38">
-        <v>0.05255369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.777345074954733</v>
+        <v>7.015218337661252</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07836024302197032</v>
+        <v>0.07768859121850204</v>
       </c>
       <c r="C39">
-        <v>4352.464562336586</v>
+        <v>4470.965075396414</v>
       </c>
       <c r="D39">
-        <v>5712.709562336586</v>
+        <v>5831.210075396414</v>
       </c>
       <c r="E39">
         <v>-1794.155</v>
@@ -4485,37 +4485,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M39">
-        <v>140.1590845642202</v>
+        <v>135.4065455642202</v>
       </c>
       <c r="N39">
-        <v>784.0742487691133</v>
+        <v>788.8267877691133</v>
       </c>
       <c r="O39">
-        <v>148.9741072661315</v>
+        <v>149.8770896761315</v>
       </c>
       <c r="P39">
-        <v>635.1001415029817</v>
+        <v>638.9496980929817</v>
       </c>
       <c r="Q39">
-        <v>988.7001415029818</v>
+        <v>992.5496980929818</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09351646919171057</v>
+        <v>0.09349692664652282</v>
       </c>
       <c r="T39">
         <v>0.8735859619998242</v>
       </c>
       <c r="U39">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V39">
         <v>0.19</v>
       </c>
       <c r="W39">
-        <v>0.05255369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.594173586442443</v>
+        <v>6.825617842048787</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07836634444808419</v>
+        <v>0.0776768978058793</v>
       </c>
       <c r="C40">
-        <v>4293.009264890088</v>
+        <v>4414.71914005436</v>
       </c>
       <c r="D40">
-        <v>5711.639264890088</v>
+        <v>5833.34914005436</v>
       </c>
       <c r="E40">
         <v>-1735.77</v>
@@ -4567,37 +4567,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M40">
-        <v>143.9471679308207</v>
+        <v>139.0661819308208</v>
       </c>
       <c r="N40">
-        <v>780.2861654025128</v>
+        <v>785.1671514025127</v>
       </c>
       <c r="O40">
-        <v>148.2543714264774</v>
+        <v>149.1817587664774</v>
       </c>
       <c r="P40">
-        <v>632.0317939760354</v>
+        <v>635.9853926360353</v>
       </c>
       <c r="Q40">
-        <v>985.6317939760354</v>
+        <v>989.5853926360353</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.0941870000956318</v>
+        <v>0.09416718293078521</v>
       </c>
       <c r="T40">
         <v>0.8858619412303748</v>
       </c>
       <c r="U40">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V40">
         <v>0.19</v>
       </c>
       <c r="W40">
-        <v>0.05255369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.420642702588695</v>
+        <v>6.645996319889607</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07837244587419805</v>
+        <v>0.07766520439325657</v>
       </c>
       <c r="C41">
-        <v>4233.554368416906</v>
+        <v>4358.474774635746</v>
       </c>
       <c r="D41">
-        <v>5710.569368416905</v>
+        <v>5835.489774635746</v>
       </c>
       <c r="E41">
         <v>-1677.385</v>
@@ -4649,37 +4649,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M41">
-        <v>147.7352512974213</v>
+        <v>142.7258182974213</v>
       </c>
       <c r="N41">
-        <v>776.4980820359121</v>
+        <v>781.5075150359122</v>
       </c>
       <c r="O41">
-        <v>147.5346355868233</v>
+        <v>148.4864278568233</v>
       </c>
       <c r="P41">
-        <v>628.9634464490889</v>
+        <v>633.0210871790889</v>
       </c>
       <c r="Q41">
-        <v>982.5634464490889</v>
+        <v>986.6210871790889</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09487951561935373</v>
+        <v>0.09485941483092508</v>
       </c>
       <c r="T41">
         <v>0.8985404115832385</v>
       </c>
       <c r="U41">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V41">
         <v>0.19</v>
       </c>
       <c r="W41">
-        <v>0.05255369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.256010838419753</v>
+        <v>6.475586157841158</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07883214730031191</v>
+        <v>0.07765351098063385</v>
       </c>
       <c r="C42">
-        <v>4095.696579115116</v>
+        <v>4302.231980869525</v>
       </c>
       <c r="D42">
-        <v>5631.096579115116</v>
+        <v>5837.631980869524</v>
       </c>
       <c r="E42">
         <v>-1619</v>
@@ -4731,45 +4731,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M42">
-        <v>154.7928946640218</v>
+        <v>146.3854546640219</v>
       </c>
       <c r="N42">
-        <v>769.4404386693116</v>
+        <v>777.8478786693116</v>
       </c>
       <c r="O42">
-        <v>146.1936833471692</v>
+        <v>147.7910969471692</v>
       </c>
       <c r="P42">
-        <v>623.2467553221423</v>
+        <v>630.0567817221424</v>
       </c>
       <c r="Q42">
-        <v>976.8467553221424</v>
+        <v>983.6567817221425</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.0955951149938664</v>
+        <v>0.0955747211277363</v>
       </c>
       <c r="T42">
         <v>0.9116414976145309</v>
       </c>
       <c r="U42">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V42">
         <v>0.19</v>
       </c>
       <c r="W42">
-        <v>0.05368769575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>5.970773628462617</v>
+        <v>6.313696503895128</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07884958872642578</v>
+        <v>0.07764181756801111</v>
       </c>
       <c r="C43">
-        <v>4034.339852122149</v>
+        <v>4245.990760487199</v>
       </c>
       <c r="D43">
-        <v>5628.12485212215</v>
+        <v>5839.775760487199</v>
       </c>
       <c r="E43">
         <v>-1560.615</v>
@@ -4813,45 +4813,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M43">
-        <v>158.6627170306224</v>
+        <v>150.0450910306224</v>
       </c>
       <c r="N43">
-        <v>765.5706163027111</v>
+        <v>774.188242302711</v>
       </c>
       <c r="O43">
-        <v>145.4584170975151</v>
+        <v>147.0957660375151</v>
       </c>
       <c r="P43">
-        <v>620.112199205196</v>
+        <v>627.092476265196</v>
       </c>
       <c r="Q43">
-        <v>973.712199205196</v>
+        <v>980.692476265196</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09633497197429475</v>
+        <v>0.09631427509562583</v>
       </c>
       <c r="T43">
         <v>0.9251866882570537</v>
       </c>
       <c r="U43">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.05368769575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>5.825145003378164</v>
+        <v>6.159703906239148</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07886703015253964</v>
+        <v>0.07797032415538839</v>
       </c>
       <c r="C44">
-        <v>3972.986260043725</v>
+        <v>4127.973013336129</v>
       </c>
       <c r="D44">
-        <v>5625.156260043726</v>
+        <v>5780.143013336129</v>
       </c>
       <c r="E44">
         <v>-1502.23</v>
@@ -4895,37 +4895,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M44">
-        <v>162.5325393972229</v>
+        <v>156.156897397223</v>
       </c>
       <c r="N44">
-        <v>761.7007939361106</v>
+        <v>768.0764359361106</v>
       </c>
       <c r="O44">
-        <v>144.723150847861</v>
+        <v>145.934522827861</v>
       </c>
       <c r="P44">
-        <v>616.9776430882496</v>
+        <v>622.1419131082496</v>
       </c>
       <c r="Q44">
-        <v>970.5776430882496</v>
+        <v>975.7419131082496</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09710034126439304</v>
+        <v>0.09707933092447708</v>
       </c>
       <c r="T44">
         <v>0.9391989544389737</v>
       </c>
       <c r="U44">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V44">
         <v>0.19</v>
       </c>
       <c r="W44">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.686451074726303</v>
+        <v>5.918619982454708</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0788844715786535</v>
+        <v>0.07796673074276565</v>
       </c>
       <c r="C45">
-        <v>3911.63579792186</v>
+        <v>4070.233725175216</v>
       </c>
       <c r="D45">
-        <v>5622.190797921859</v>
+        <v>5780.788725175216</v>
       </c>
       <c r="E45">
         <v>-1443.845</v>
@@ -4977,37 +4977,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M45">
-        <v>166.4023617638234</v>
+        <v>159.8749187638235</v>
       </c>
       <c r="N45">
-        <v>757.83097156951</v>
+        <v>764.3584145695099</v>
       </c>
       <c r="O45">
-        <v>143.9878845982069</v>
+        <v>145.2280987682069</v>
       </c>
       <c r="P45">
-        <v>613.8430869713031</v>
+        <v>619.130315801303</v>
       </c>
       <c r="Q45">
-        <v>967.4430869713032</v>
+        <v>972.730315801303</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09789256561730179</v>
+        <v>0.09787123081749854</v>
       </c>
       <c r="T45">
         <v>0.9537028790834173</v>
       </c>
       <c r="U45">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V45">
         <v>0.19</v>
       </c>
       <c r="W45">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.554208026476855</v>
+        <v>5.780977657281344</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07890191300476737</v>
+        <v>0.07796313733014293</v>
       </c>
       <c r="C46">
-        <v>3850.288460809018</v>
+        <v>4012.494581298055</v>
       </c>
       <c r="D46">
-        <v>5619.228460809018</v>
+        <v>5781.434581298055</v>
       </c>
       <c r="E46">
         <v>-1385.46</v>
@@ -5059,37 +5059,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M46">
-        <v>170.272184130424</v>
+        <v>163.592940130424</v>
       </c>
       <c r="N46">
-        <v>753.9611492029094</v>
+        <v>760.6403932029094</v>
       </c>
       <c r="O46">
-        <v>143.2526183485528</v>
+        <v>144.5216747085528</v>
       </c>
       <c r="P46">
-        <v>610.7085308543566</v>
+        <v>616.1187184943567</v>
       </c>
       <c r="Q46">
-        <v>964.3085308543566</v>
+        <v>969.7187184943567</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09871308369710016</v>
+        <v>0.09869141284955651</v>
       </c>
       <c r="T46">
         <v>0.9687248010365912</v>
       </c>
       <c r="U46">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.427976025875107</v>
+        <v>5.64959180143404</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07891935443088122</v>
+        <v>0.07795954391752019</v>
       </c>
       <c r="C47">
-        <v>3788.9442437681</v>
+        <v>3954.755581753012</v>
       </c>
       <c r="D47">
-        <v>5616.269243768101</v>
+        <v>5782.080581753013</v>
       </c>
       <c r="E47">
         <v>-1327.075</v>
@@ -5141,37 +5141,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M47">
-        <v>174.1420064970246</v>
+        <v>167.3109614970246</v>
       </c>
       <c r="N47">
-        <v>750.0913268363089</v>
+        <v>756.9223718363089</v>
       </c>
       <c r="O47">
-        <v>142.5173520988987</v>
+        <v>143.8152506488987</v>
       </c>
       <c r="P47">
-        <v>607.5739747374103</v>
+        <v>613.1071211874103</v>
       </c>
       <c r="Q47">
-        <v>961.1739747374103</v>
+        <v>966.7071211874103</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09956343879798207</v>
+        <v>0.0995414196827802</v>
       </c>
       <c r="T47">
         <v>0.9842929746971528</v>
       </c>
       <c r="U47">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V47">
         <v>0.19</v>
       </c>
       <c r="W47">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.307354336411215</v>
+        <v>5.524045316957728</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07893679585699509</v>
+        <v>0.07795595050489747</v>
       </c>
       <c r="C48">
-        <v>3727.603141872385</v>
+        <v>3897.016726588474</v>
       </c>
       <c r="D48">
-        <v>5613.313141872385</v>
+        <v>5782.726726588474</v>
       </c>
       <c r="E48">
         <v>-1268.69</v>
@@ -5223,37 +5223,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M48">
-        <v>178.0118288636251</v>
+        <v>171.0289828636251</v>
       </c>
       <c r="N48">
-        <v>746.2215044697084</v>
+        <v>753.2043504697083</v>
       </c>
       <c r="O48">
-        <v>141.7820858492446</v>
+        <v>143.1088265892446</v>
       </c>
       <c r="P48">
-        <v>604.4394186204638</v>
+        <v>610.0955238804637</v>
       </c>
       <c r="Q48">
-        <v>958.0394186204638</v>
+        <v>963.6955238804637</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.10044528853223</v>
+        <v>0.1004229082505677</v>
       </c>
       <c r="T48">
         <v>1.00043774738218</v>
       </c>
       <c r="U48">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V48">
         <v>0.19</v>
       </c>
       <c r="W48">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.191977068228364</v>
+        <v>5.403957375284734</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07895423728310896</v>
+        <v>0.07795235709227474</v>
       </c>
       <c r="C49">
-        <v>3666.26515020553</v>
+        <v>3839.278015852849</v>
       </c>
       <c r="D49">
-        <v>5610.36015020553</v>
+        <v>5783.373015852849</v>
       </c>
       <c r="E49">
         <v>-1210.305</v>
@@ -5305,37 +5305,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M49">
-        <v>181.8816512302257</v>
+        <v>174.7470042302257</v>
       </c>
       <c r="N49">
-        <v>742.3516821031078</v>
+        <v>749.4863291031078</v>
       </c>
       <c r="O49">
-        <v>141.0468195995905</v>
+        <v>142.4024025295905</v>
       </c>
       <c r="P49">
-        <v>601.3048625035174</v>
+        <v>607.0839265735173</v>
       </c>
       <c r="Q49">
-        <v>954.9048625035174</v>
+        <v>960.6839265735173</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1013604156149401</v>
+        <v>0.1013376605378944</v>
       </c>
       <c r="T49">
         <v>1.017191756772303</v>
       </c>
       <c r="U49">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V49">
         <v>0.19</v>
       </c>
       <c r="W49">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.081509471032016</v>
+        <v>5.288979558789314</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07897167870922281</v>
+        <v>0.07794876367965201</v>
       </c>
       <c r="C50">
-        <v>3604.93026386153</v>
+        <v>3781.539449594571</v>
       </c>
       <c r="D50">
-        <v>5607.41026386153</v>
+        <v>5784.019449594571</v>
       </c>
       <c r="E50">
         <v>-1151.92</v>
@@ -5387,37 +5387,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M50">
-        <v>185.7514735968262</v>
+        <v>178.4650255968262</v>
       </c>
       <c r="N50">
-        <v>738.4818597365072</v>
+        <v>745.7683077365073</v>
       </c>
       <c r="O50">
-        <v>140.3115533499364</v>
+        <v>141.6959784699364</v>
       </c>
       <c r="P50">
-        <v>598.1703063865708</v>
+        <v>604.0723292665709</v>
       </c>
       <c r="Q50">
-        <v>951.7703063865708</v>
+        <v>957.672329266571</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1023107398931391</v>
+        <v>0.1022875956055029</v>
       </c>
       <c r="T50">
         <v>1.034590151138968</v>
       </c>
       <c r="U50">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V50">
         <v>0.19</v>
       </c>
       <c r="W50">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.975644690385515</v>
+        <v>5.178792484647871</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07898912013533667</v>
+        <v>0.07794517026702927</v>
       </c>
       <c r="C51">
-        <v>3543.598477944687</v>
+        <v>3723.80102786209</v>
       </c>
       <c r="D51">
-        <v>5604.463477944687</v>
+        <v>5784.666027862089</v>
       </c>
       <c r="E51">
         <v>-1093.535</v>
@@ -5469,37 +5469,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M51">
-        <v>189.6212959634267</v>
+        <v>182.1830469634268</v>
       </c>
       <c r="N51">
-        <v>734.6120373699067</v>
+        <v>742.0502863699066</v>
       </c>
       <c r="O51">
-        <v>139.5762871002823</v>
+        <v>140.9895544102823</v>
       </c>
       <c r="P51">
-        <v>595.0357502696245</v>
+        <v>601.0607319596244</v>
       </c>
       <c r="Q51">
-        <v>948.6357502696245</v>
+        <v>954.6607319596244</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.103298331790091</v>
+        <v>0.1032747830287039</v>
       </c>
       <c r="T51">
         <v>1.052670835480797</v>
       </c>
       <c r="U51">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.874100921193975</v>
+        <v>5.073102842104036</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07900656156145053</v>
+        <v>0.07794157685440654</v>
       </c>
       <c r="C52">
-        <v>3482.269787569593</v>
+        <v>3666.062750703874</v>
       </c>
       <c r="D52">
-        <v>5601.519787569593</v>
+        <v>5785.312750703874</v>
       </c>
       <c r="E52">
         <v>-1035.15</v>
@@ -5551,37 +5551,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M52">
-        <v>193.4911183300273</v>
+        <v>185.9010683300273</v>
       </c>
       <c r="N52">
-        <v>730.7422150033062</v>
+        <v>738.3322650033061</v>
       </c>
       <c r="O52">
-        <v>138.8410208506282</v>
+        <v>140.2831303506282</v>
       </c>
       <c r="P52">
-        <v>591.901194152678</v>
+        <v>598.0491346526779</v>
       </c>
       <c r="Q52">
-        <v>945.5011941526781</v>
+        <v>951.649134652678</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1043254273629209</v>
+        <v>0.1043014579488329</v>
       </c>
       <c r="T52">
         <v>1.071474747196299</v>
       </c>
       <c r="U52">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V52">
         <v>0.19</v>
       </c>
       <c r="W52">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.776618902770094</v>
+        <v>4.971640785261956</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.0790240029875644</v>
+        <v>0.07793798344178382</v>
       </c>
       <c r="C53">
-        <v>3420.944187861098</v>
+        <v>3608.324618168425</v>
       </c>
       <c r="D53">
-        <v>5598.579187861098</v>
+        <v>5785.959618168426</v>
       </c>
       <c r="E53">
         <v>-976.7649999999999</v>
@@ -5633,37 +5633,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M53">
-        <v>197.3609406966278</v>
+        <v>189.6190896966279</v>
       </c>
       <c r="N53">
-        <v>726.8723926367056</v>
+        <v>734.6142436367056</v>
       </c>
       <c r="O53">
-        <v>138.1057546009741</v>
+        <v>139.5767062909741</v>
       </c>
       <c r="P53">
-        <v>588.7666380357316</v>
+        <v>595.0375373457316</v>
       </c>
       <c r="Q53">
-        <v>942.3666380357316</v>
+        <v>948.6375373457316</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1053944452040296</v>
+        <v>0.1053700379677427</v>
       </c>
       <c r="T53">
         <v>1.091046165512434</v>
       </c>
       <c r="U53">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V53">
         <v>0.19</v>
       </c>
       <c r="W53">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.682959708598132</v>
+        <v>4.87415763260976</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07904144441367826</v>
+        <v>0.07793439002916108</v>
       </c>
       <c r="C54">
-        <v>3359.621673954287</v>
+        <v>3550.586630304264</v>
       </c>
       <c r="D54">
-        <v>5595.641673954286</v>
+        <v>5786.606630304263</v>
       </c>
       <c r="E54">
         <v>-918.3800000000001</v>
@@ -5715,37 +5715,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M54">
-        <v>201.2307630632284</v>
+        <v>193.3371110632284</v>
       </c>
       <c r="N54">
-        <v>723.002570270105</v>
+        <v>730.896222270105</v>
       </c>
       <c r="O54">
-        <v>137.3704883513199</v>
+        <v>138.8702822313199</v>
       </c>
       <c r="P54">
-        <v>585.632081918785</v>
+        <v>592.0259400387851</v>
       </c>
       <c r="Q54">
-        <v>939.2320819187851</v>
+        <v>945.6259400387851</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1065080054551845</v>
+        <v>0.1064831421541071</v>
       </c>
       <c r="T54">
         <v>1.111433059591741</v>
       </c>
       <c r="U54">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V54">
         <v>0.19</v>
       </c>
       <c r="W54">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.59290279112509</v>
+        <v>4.780423831982649</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07905888583979213</v>
+        <v>0.07793079661653836</v>
       </c>
       <c r="C55">
-        <v>3298.302240994442</v>
+        <v>3492.848787159919</v>
       </c>
       <c r="D55">
-        <v>5592.707240994442</v>
+        <v>5787.253787159919</v>
       </c>
       <c r="E55">
         <v>-859.9949999999999</v>
@@ -5797,37 +5797,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M55">
-        <v>205.100585429829</v>
+        <v>197.055132429829</v>
       </c>
       <c r="N55">
-        <v>719.1327479035045</v>
+        <v>727.1782009035045</v>
       </c>
       <c r="O55">
-        <v>136.6352221016659</v>
+        <v>138.1638581716659</v>
       </c>
       <c r="P55">
-        <v>582.4975258018387</v>
+        <v>589.0143427318386</v>
       </c>
       <c r="Q55">
-        <v>936.0975258018387</v>
+        <v>942.6143427318386</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1076689512489418</v>
+        <v>0.1076436124760614</v>
       </c>
       <c r="T55">
         <v>1.132687481078679</v>
       </c>
       <c r="U55">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.05368769575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.506244247896316</v>
+        <v>4.690227155907505</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08021356726590599</v>
+        <v>0.07792720320391562</v>
       </c>
       <c r="C56">
-        <v>3052.264646801842</v>
+        <v>3435.111088783959</v>
       </c>
       <c r="D56">
-        <v>5405.054646801843</v>
+        <v>5787.901088783959</v>
       </c>
       <c r="E56">
         <v>-801.6099999999997</v>
@@ -5879,45 +5879,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M56">
-        <v>217.1676617964295</v>
+        <v>200.7731537964295</v>
       </c>
       <c r="N56">
-        <v>707.065671536904</v>
+        <v>723.460179536904</v>
       </c>
       <c r="O56">
-        <v>134.3424775920118</v>
+        <v>137.4574341120118</v>
       </c>
       <c r="P56">
-        <v>572.7231939448923</v>
+        <v>586.0027454248923</v>
       </c>
       <c r="Q56">
-        <v>926.3231939448923</v>
+        <v>939.6027454248923</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1088803729467754</v>
+        <v>0.1088545380294051</v>
       </c>
       <c r="T56">
         <v>1.154866007847657</v>
       </c>
       <c r="U56">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.05579369575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.255851565044244</v>
+        <v>4.603371097464773</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08025206869201984</v>
+        <v>0.0779236097912929</v>
       </c>
       <c r="C57">
-        <v>2987.839303797031</v>
+        <v>3377.373535224961</v>
       </c>
       <c r="D57">
-        <v>5399.014303797031</v>
+        <v>5788.548535224961</v>
       </c>
       <c r="E57">
         <v>-743.2249999999999</v>
@@ -5961,45 +5961,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M57">
-        <v>221.18928516303</v>
+        <v>204.4911751630301</v>
       </c>
       <c r="N57">
-        <v>703.0440481703034</v>
+        <v>719.7421581703034</v>
       </c>
       <c r="O57">
-        <v>133.5783691523577</v>
+        <v>136.7510100523576</v>
       </c>
       <c r="P57">
-        <v>569.4656790179458</v>
+        <v>582.9911481179457</v>
       </c>
       <c r="Q57">
-        <v>923.0656790179459</v>
+        <v>936.5911481179457</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1101456356089572</v>
+        <v>0.1101192824962307</v>
       </c>
       <c r="T57">
         <v>1.178030246917478</v>
       </c>
       <c r="U57">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V57">
         <v>0.19</v>
       </c>
       <c r="W57">
-        <v>0.05579369575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.178472445679803</v>
+        <v>4.519673441147232</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0802905701181337</v>
+        <v>0.07905401637867016</v>
       </c>
       <c r="C58">
-        <v>2923.427446322846</v>
+        <v>3122.217915969226</v>
       </c>
       <c r="D58">
-        <v>5392.987446322846</v>
+        <v>5591.777915969226</v>
       </c>
       <c r="E58">
         <v>-684.8399999999997</v>
@@ -6043,37 +6043,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M58">
-        <v>225.2109085296306</v>
+        <v>216.3830965296306</v>
       </c>
       <c r="N58">
-        <v>699.022424803703</v>
+        <v>707.8502368037028</v>
       </c>
       <c r="O58">
-        <v>132.8142607127036</v>
+        <v>134.4915449927036</v>
       </c>
       <c r="P58">
-        <v>566.2081640909994</v>
+        <v>573.3586918109993</v>
       </c>
       <c r="Q58">
-        <v>919.8081640909994</v>
+        <v>926.9586918109993</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1114684102103291</v>
+        <v>0.111441515347912</v>
       </c>
       <c r="T58">
         <v>1.202247405945019</v>
       </c>
       <c r="U58">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V58">
         <v>0.19</v>
       </c>
       <c r="W58">
-        <v>0.05579369575998017</v>
+        <v>0.05360669575998017</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.103856866292665</v>
+        <v>4.271282499216721</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08032907154424758</v>
+        <v>0.07907067296604743</v>
       </c>
       <c r="C59">
-        <v>2859.029029268421</v>
+        <v>3061.033455388831</v>
       </c>
       <c r="D59">
-        <v>5386.974029268421</v>
+        <v>5588.978455388831</v>
       </c>
       <c r="E59">
         <v>-626.4549999999999</v>
@@ -6125,37 +6125,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M59">
-        <v>229.2325318962311</v>
+        <v>220.2470803962311</v>
       </c>
       <c r="N59">
-        <v>695.0008014371024</v>
+        <v>703.9862529371023</v>
       </c>
       <c r="O59">
-        <v>132.0501522730495</v>
+        <v>133.7573880580495</v>
       </c>
       <c r="P59">
-        <v>562.9506491640529</v>
+        <v>570.2288648790529</v>
       </c>
       <c r="Q59">
-        <v>916.550649164053</v>
+        <v>923.828864879053</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1128527092117649</v>
+        <v>0.1128252474019971</v>
       </c>
       <c r="T59">
         <v>1.227590944462213</v>
       </c>
       <c r="U59">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V59">
         <v>0.19</v>
       </c>
       <c r="W59">
-        <v>0.05579369575998017</v>
+        <v>0.05360669575998017</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.031859377410337</v>
+        <v>4.196347718528709</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08163603297036144</v>
+        <v>0.07908732955342471</v>
       </c>
       <c r="C60">
-        <v>2604.177883990736</v>
+        <v>2999.851796442596</v>
       </c>
       <c r="D60">
-        <v>5190.507883990736</v>
+        <v>5586.181796442595</v>
       </c>
       <c r="E60">
         <v>-568.0700000000002</v>
@@ -6207,45 +6207,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M60">
-        <v>242.3972462628317</v>
+        <v>224.1110642628316</v>
       </c>
       <c r="N60">
-        <v>681.8360870705018</v>
+        <v>700.1222690705018</v>
       </c>
       <c r="O60">
-        <v>129.5488565433953</v>
+        <v>133.0232311233954</v>
       </c>
       <c r="P60">
-        <v>552.2872305271064</v>
+        <v>567.0990379471065</v>
       </c>
       <c r="Q60">
-        <v>905.8872305271065</v>
+        <v>920.6990379471065</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1143029272132689</v>
+        <v>0.1142748714586576</v>
       </c>
       <c r="T60">
         <v>1.254141318146892</v>
       </c>
       <c r="U60">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V60">
         <v>0.19</v>
       </c>
       <c r="W60">
-        <v>0.05798069575998017</v>
+        <v>0.05360669575998017</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.812887099926812</v>
+        <v>4.123996895795456</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0816964043964753</v>
+        <v>0.07910398614080197</v>
       </c>
       <c r="C61">
-        <v>2537.063364461406</v>
+        <v>2938.672934926909</v>
       </c>
       <c r="D61">
-        <v>5181.778364461406</v>
+        <v>5583.387934926909</v>
       </c>
       <c r="E61">
         <v>-509.6850000000004</v>
@@ -6289,45 +6289,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M61">
-        <v>246.5765091294322</v>
+        <v>227.9750481294322</v>
       </c>
       <c r="N61">
-        <v>677.6568242039014</v>
+        <v>696.2582852039013</v>
       </c>
       <c r="O61">
-        <v>128.7547965987413</v>
+        <v>132.2890741887412</v>
       </c>
       <c r="P61">
-        <v>548.9020276051601</v>
+        <v>563.9692110151601</v>
       </c>
       <c r="Q61">
-        <v>902.5020276051602</v>
+        <v>917.5692110151601</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1158238875563097</v>
+        <v>0.1157952088839358</v>
       </c>
       <c r="T61">
         <v>1.281986832011311</v>
       </c>
       <c r="U61">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V61">
         <v>0.19</v>
       </c>
       <c r="W61">
-        <v>0.05798069575998017</v>
+        <v>0.05360669575998017</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.748261894843307</v>
+        <v>4.054098643324346</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08175677582258917</v>
+        <v>0.08082164272817924</v>
       </c>
       <c r="C62">
-        <v>2469.978158658415</v>
+        <v>2606.447466027564</v>
       </c>
       <c r="D62">
-        <v>5173.078158658415</v>
+        <v>5309.547466027564</v>
       </c>
       <c r="E62">
         <v>-451.3000000000002</v>
@@ -6371,37 +6371,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M62">
-        <v>250.7557719960327</v>
+        <v>244.0998819960327</v>
       </c>
       <c r="N62">
-        <v>673.4775613373007</v>
+        <v>680.1334513373007</v>
       </c>
       <c r="O62">
-        <v>127.9607366540871</v>
+        <v>129.2253557540871</v>
       </c>
       <c r="P62">
-        <v>545.5168246832136</v>
+        <v>550.9080955832136</v>
       </c>
       <c r="Q62">
-        <v>899.1168246832136</v>
+        <v>904.5080955832136</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1174208959165026</v>
+        <v>0.1173915631804778</v>
       </c>
       <c r="T62">
         <v>1.311224621568952</v>
       </c>
       <c r="U62">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V62">
         <v>0.19</v>
       </c>
       <c r="W62">
-        <v>0.05798069575998017</v>
+        <v>0.05644169575998017</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.685790863262585</v>
+        <v>3.786291602338237</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08181714724870302</v>
+        <v>0.08086664931555651</v>
       </c>
       <c r="C63">
-        <v>2402.922119176022</v>
+        <v>2541.247882466609</v>
       </c>
       <c r="D63">
-        <v>5164.407119176022</v>
+        <v>5302.732882466609</v>
       </c>
       <c r="E63">
         <v>-392.915</v>
@@ -6453,37 +6453,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M63">
-        <v>254.9350348626333</v>
+        <v>248.1682133626333</v>
       </c>
       <c r="N63">
-        <v>669.2982984707002</v>
+        <v>676.0651199707002</v>
       </c>
       <c r="O63">
-        <v>127.166676709433</v>
+        <v>128.452372794433</v>
       </c>
       <c r="P63">
-        <v>542.1316217612671</v>
+        <v>547.6127471762671</v>
       </c>
       <c r="Q63">
-        <v>895.7316217612671</v>
+        <v>901.2127471762672</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1190998021413208</v>
+        <v>0.1190697817999195</v>
       </c>
       <c r="T63">
         <v>1.341961784950061</v>
       </c>
       <c r="U63">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V63">
         <v>0.19</v>
       </c>
       <c r="W63">
-        <v>0.05798069575998017</v>
+        <v>0.05644169575998017</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.625368062225493</v>
+        <v>3.724221248201545</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08187751867481688</v>
+        <v>0.08091165590293378</v>
       </c>
       <c r="C64">
-        <v>2335.895099595145</v>
+        <v>2476.065768953284</v>
       </c>
       <c r="D64">
-        <v>5155.765099595145</v>
+        <v>5295.935768953284</v>
       </c>
       <c r="E64">
         <v>-334.5300000000002</v>
@@ -6535,37 +6535,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M64">
-        <v>259.1142977292338</v>
+        <v>252.2365447292338</v>
       </c>
       <c r="N64">
-        <v>665.1190356040996</v>
+        <v>671.9967886040996</v>
       </c>
       <c r="O64">
-        <v>126.3726167647789</v>
+        <v>127.6793898347789</v>
       </c>
       <c r="P64">
-        <v>538.7464188393207</v>
+        <v>544.3173987693207</v>
       </c>
       <c r="Q64">
-        <v>892.3464188393207</v>
+        <v>897.9173987693207</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1208670718516557</v>
+        <v>0.1208363277151213</v>
       </c>
       <c r="T64">
         <v>1.374316693772282</v>
       </c>
       <c r="U64">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V64">
         <v>0.19</v>
       </c>
       <c r="W64">
-        <v>0.05798069575998017</v>
+        <v>0.05644169575998017</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.566894383802501</v>
+        <v>3.664153163553133</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08193789010093075</v>
+        <v>0.08095666249031104</v>
       </c>
       <c r="C65">
-        <v>2268.896954475125</v>
+        <v>2410.901058393573</v>
       </c>
       <c r="D65">
-        <v>5147.151954475125</v>
+        <v>5289.156058393573</v>
       </c>
       <c r="E65">
         <v>-276.145</v>
@@ -6617,37 +6617,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M65">
-        <v>263.2935605958344</v>
+        <v>256.3048760958344</v>
       </c>
       <c r="N65">
-        <v>660.9397727374991</v>
+        <v>667.9284572374991</v>
       </c>
       <c r="O65">
-        <v>125.5785568201248</v>
+        <v>126.9064068751248</v>
       </c>
       <c r="P65">
-        <v>535.3612159173742</v>
+        <v>541.0220503623742</v>
       </c>
       <c r="Q65">
-        <v>888.9612159173743</v>
+        <v>894.6220503623742</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1227298696544412</v>
+        <v>0.1226983625987123</v>
       </c>
       <c r="T65">
         <v>1.408420516584892</v>
       </c>
       <c r="U65">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.05798069575998017</v>
+        <v>0.05644169575998017</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.510277012631033</v>
+        <v>3.605992002226893</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08443474152704462</v>
+        <v>0.08100166907768833</v>
       </c>
       <c r="C66">
-        <v>1877.866434148303</v>
+        <v>2345.753684036583</v>
       </c>
       <c r="D66">
-        <v>4814.506434148303</v>
+        <v>5282.393684036583</v>
       </c>
       <c r="E66">
         <v>-217.7600000000002</v>
@@ -6699,45 +6699,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M66">
-        <v>285.035031462435</v>
+        <v>260.3732074624349</v>
       </c>
       <c r="N66">
-        <v>639.1983018708985</v>
+        <v>663.8601258708985</v>
       </c>
       <c r="O66">
-        <v>121.4476773554707</v>
+        <v>126.1334239154707</v>
       </c>
       <c r="P66">
-        <v>517.7506245154277</v>
+        <v>537.7267019554278</v>
       </c>
       <c r="Q66">
-        <v>871.3506245154277</v>
+        <v>891.3267019554278</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1246961562240481</v>
+        <v>0.124663843864725</v>
       </c>
       <c r="T66">
         <v>1.444418996220426</v>
       </c>
       <c r="U66">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V66">
         <v>0.19</v>
       </c>
       <c r="W66">
-        <v>0.06178769575998018</v>
+        <v>0.05644169575998017</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.242525413775811</v>
+        <v>3.549648377192097</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08453318295315848</v>
+        <v>0.08252087566506558</v>
       </c>
       <c r="C67">
-        <v>1807.245236571019</v>
+        <v>2068.826856355088</v>
       </c>
       <c r="D67">
-        <v>4802.270236571019</v>
+        <v>5063.851856355088</v>
       </c>
       <c r="E67">
         <v>-159.375</v>
@@ -6781,37 +6781,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M67">
-        <v>289.4887038290355</v>
+        <v>275.0676088290355</v>
       </c>
       <c r="N67">
-        <v>634.744629504298</v>
+        <v>649.1657245042979</v>
       </c>
       <c r="O67">
-        <v>120.6014796058166</v>
+        <v>123.3414876558166</v>
       </c>
       <c r="P67">
-        <v>514.1431498984814</v>
+        <v>525.8242368484813</v>
       </c>
       <c r="Q67">
-        <v>867.7431498984814</v>
+        <v>879.4242368484813</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1267748020262039</v>
+        <v>0.1267416383459385</v>
       </c>
       <c r="T67">
         <v>1.482474531835132</v>
       </c>
       <c r="U67">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V67">
         <v>0.19</v>
       </c>
       <c r="W67">
-        <v>0.06178769575998018</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.192640407410031</v>
+        <v>3.360022422370269</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08463162437927235</v>
+        <v>0.08258856225244285</v>
       </c>
       <c r="C68">
-        <v>1736.686078568899</v>
+        <v>2001.124970068835</v>
       </c>
       <c r="D68">
-        <v>4790.096078568899</v>
+        <v>5054.534970068836</v>
       </c>
       <c r="E68">
         <v>-100.9899999999998</v>
@@ -6863,37 +6863,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M68">
-        <v>293.9423761956361</v>
+        <v>279.299418195636</v>
       </c>
       <c r="N68">
-        <v>630.2909571376974</v>
+        <v>644.9339151376975</v>
       </c>
       <c r="O68">
-        <v>119.7552818561625</v>
+        <v>122.5374438761625</v>
       </c>
       <c r="P68">
-        <v>510.5356752815349</v>
+        <v>522.396471261535</v>
       </c>
       <c r="Q68">
-        <v>864.135675281535</v>
+        <v>875.996471261535</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1289757211108395</v>
+        <v>0.1289416560319293</v>
       </c>
       <c r="T68">
         <v>1.522768628368351</v>
       </c>
       <c r="U68">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V68">
         <v>0.19</v>
       </c>
       <c r="W68">
-        <v>0.06178769575998018</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.144267067903817</v>
+        <v>3.309112991728296</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.0847300658053862</v>
+        <v>0.08265624883982012</v>
       </c>
       <c r="C69">
-        <v>1666.188489508457</v>
+        <v>1933.457304749586</v>
       </c>
       <c r="D69">
-        <v>4777.983489508457</v>
+        <v>5045.252304749586</v>
       </c>
       <c r="E69">
         <v>-42.60500000000002</v>
@@ -6945,37 +6945,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M69">
-        <v>298.3960485622366</v>
+        <v>283.5312275622366</v>
       </c>
       <c r="N69">
-        <v>625.8372847710968</v>
+        <v>640.702105771097</v>
       </c>
       <c r="O69">
-        <v>118.9090841065084</v>
+        <v>121.7334000965084</v>
       </c>
       <c r="P69">
-        <v>506.9282006645884</v>
+        <v>518.9687056745886</v>
       </c>
       <c r="Q69">
-        <v>860.5282006645884</v>
+        <v>872.5687056745886</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1313100292309075</v>
+        <v>0.1312750081231316</v>
       </c>
       <c r="T69">
         <v>1.565504791358129</v>
       </c>
       <c r="U69">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V69">
         <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.06178769575998018</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.097337708681372</v>
+        <v>3.259723245583098</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08482850723150007</v>
+        <v>0.0827239354271974</v>
       </c>
       <c r="C70">
-        <v>1595.7520035045</v>
+        <v>1865.8236722023</v>
       </c>
       <c r="D70">
-        <v>4765.9320035045</v>
+        <v>5036.003672202301</v>
       </c>
       <c r="E70">
         <v>15.7800000000002</v>
@@ -7027,37 +7027,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M70">
-        <v>302.8497209288371</v>
+        <v>287.7630369288371</v>
       </c>
       <c r="N70">
-        <v>621.3836124044963</v>
+        <v>636.4702964044964</v>
       </c>
       <c r="O70">
-        <v>118.0628863568543</v>
+        <v>120.9293563168543</v>
       </c>
       <c r="P70">
-        <v>503.320726047642</v>
+        <v>515.5409400876421</v>
       </c>
       <c r="Q70">
-        <v>856.920726047642</v>
+        <v>869.1409400876421</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1337902316084799</v>
+        <v>0.133754194720034</v>
       </c>
       <c r="T70">
         <v>1.610911964534768</v>
       </c>
       <c r="U70">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V70">
         <v>0.19</v>
       </c>
       <c r="W70">
-        <v>0.06178769575998018</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.051788624730176</v>
+        <v>3.211786139030405</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08492694865761394</v>
+        <v>0.08279162201457467</v>
       </c>
       <c r="C71">
-        <v>1525.376159360423</v>
+        <v>1798.223885609366</v>
       </c>
       <c r="D71">
-        <v>4753.941159360424</v>
+        <v>5026.788885609367</v>
       </c>
       <c r="E71">
         <v>74.16500000000042</v>
@@ -7109,37 +7109,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M71">
-        <v>307.3033932954377</v>
+        <v>291.9948462954377</v>
       </c>
       <c r="N71">
-        <v>616.9299400378957</v>
+        <v>632.2384870378958</v>
       </c>
       <c r="O71">
-        <v>117.2166886072002</v>
+        <v>120.1253125372002</v>
       </c>
       <c r="P71">
-        <v>499.7132514306955</v>
+        <v>512.1131745006955</v>
       </c>
       <c r="Q71">
-        <v>853.3132514306956</v>
+        <v>865.7131745006956</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1364304470426697</v>
+        <v>0.1363933288393173</v>
       </c>
       <c r="T71">
         <v>1.659248632755061</v>
       </c>
       <c r="U71">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V71">
         <v>0.19</v>
       </c>
       <c r="W71">
-        <v>0.06178769575998018</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.007559804081912</v>
+        <v>3.165238513827065</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09029849008372778</v>
+        <v>0.08285930860195193</v>
       </c>
       <c r="C72">
-        <v>893.1291737792494</v>
+        <v>1730.657759518016</v>
       </c>
       <c r="D72">
-        <v>4180.07917377925</v>
+        <v>5017.607759518016</v>
       </c>
       <c r="E72">
         <v>132.5500000000002</v>
@@ -7191,45 +7191,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M72">
-        <v>349.7657006620382</v>
+        <v>296.2266556620382</v>
       </c>
       <c r="N72">
-        <v>574.4676326712952</v>
+        <v>628.0066776712952</v>
       </c>
       <c r="O72">
-        <v>109.1488502075461</v>
+        <v>119.3212687575461</v>
       </c>
       <c r="P72">
-        <v>465.3187824637491</v>
+        <v>508.6854089137491</v>
       </c>
       <c r="Q72">
-        <v>818.918782463749</v>
+        <v>862.2854089137491</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1392466768391389</v>
+        <v>0.1392084052332194</v>
       </c>
       <c r="T72">
         <v>1.710807745523373</v>
       </c>
       <c r="U72">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V72">
         <v>0.19</v>
       </c>
       <c r="W72">
-        <v>0.06932069575998016</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.642435583546185</v>
+        <v>3.120020820772393</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09047226150984164</v>
+        <v>0.08292699518932921</v>
       </c>
       <c r="C73">
-        <v>818.4840093114981</v>
+        <v>1663.125109827874</v>
       </c>
       <c r="D73">
-        <v>4163.819009311498</v>
+        <v>5008.460109827874</v>
       </c>
       <c r="E73">
         <v>190.9349999999999</v>
@@ -7273,45 +7273,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M73">
-        <v>354.7623535286388</v>
+        <v>300.4584650286387</v>
       </c>
       <c r="N73">
-        <v>569.4709798046947</v>
+        <v>623.7748683046948</v>
       </c>
       <c r="O73">
-        <v>108.199486162892</v>
+        <v>118.517224977892</v>
       </c>
       <c r="P73">
-        <v>461.2714936418027</v>
+        <v>505.2576433268028</v>
       </c>
       <c r="Q73">
-        <v>814.8714936418028</v>
+        <v>858.8576433268029</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1422571293801922</v>
+        <v>0.142217624826701</v>
       </c>
       <c r="T73">
         <v>1.765922659172259</v>
       </c>
       <c r="U73">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V73">
         <v>0.19</v>
       </c>
       <c r="W73">
-        <v>0.06932069575998016</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.605218180961028</v>
+        <v>3.076076865550247</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09064603293595551</v>
+        <v>0.08299468177670648</v>
       </c>
       <c r="C74">
-        <v>743.964856077444</v>
+        <v>1595.625753778678</v>
       </c>
       <c r="D74">
-        <v>4147.684856077444</v>
+        <v>4999.345753778678</v>
       </c>
       <c r="E74">
         <v>249.3200000000002</v>
@@ -7355,45 +7355,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M74">
-        <v>359.7590063952393</v>
+        <v>304.6902743952393</v>
       </c>
       <c r="N74">
-        <v>564.4743269380942</v>
+        <v>619.5430589380942</v>
       </c>
       <c r="O74">
-        <v>107.2501221182379</v>
+        <v>117.7131811982379</v>
       </c>
       <c r="P74">
-        <v>457.2242048198563</v>
+        <v>501.8298777398563</v>
       </c>
       <c r="Q74">
-        <v>810.8242048198563</v>
+        <v>855.4298777398564</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1454826142456064</v>
+        <v>0.1454417886768598</v>
       </c>
       <c r="T74">
         <v>1.824974352367493</v>
       </c>
       <c r="U74">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V74">
         <v>0.19</v>
       </c>
       <c r="W74">
-        <v>0.06932069575998016</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.569034595114347</v>
+        <v>3.033353575750938</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09081980436206938</v>
+        <v>0.08767450836408376</v>
       </c>
       <c r="C75">
-        <v>669.5702549091484</v>
+        <v>978.5220465736948</v>
       </c>
       <c r="D75">
-        <v>4131.675254909148</v>
+        <v>4440.627046573694</v>
       </c>
       <c r="E75">
         <v>307.7049999999995</v>
@@ -7437,37 +7437,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M75">
-        <v>364.7556592618398</v>
+        <v>342.1665027618399</v>
       </c>
       <c r="N75">
-        <v>559.4776740714937</v>
+        <v>582.0668305714936</v>
       </c>
       <c r="O75">
-        <v>106.3007580735838</v>
+        <v>110.5926978085838</v>
       </c>
       <c r="P75">
-        <v>453.1769159979099</v>
+        <v>471.4741327629098</v>
       </c>
       <c r="Q75">
-        <v>806.7769159979099</v>
+        <v>825.0741327629098</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1489470239158661</v>
+        <v>0.1489047794788823</v>
       </c>
       <c r="T75">
         <v>1.888400245058671</v>
       </c>
       <c r="U75">
-        <v>0.08558110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V75">
         <v>0.19</v>
       </c>
       <c r="W75">
-        <v>0.06932069575998016</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.533842340386754</v>
+        <v>2.701121605631376</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09381075578818324</v>
+        <v>0.08780537495146103</v>
       </c>
       <c r="C76">
-        <v>353.7920980417566</v>
+        <v>906.3023954588834</v>
       </c>
       <c r="D76">
-        <v>3874.282098041757</v>
+        <v>4426.792395458883</v>
       </c>
       <c r="E76">
         <v>366.0899999999997</v>
@@ -7519,45 +7519,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M76">
-        <v>390.0586151284404</v>
+        <v>346.8537151284404</v>
       </c>
       <c r="N76">
-        <v>534.1747182048931</v>
+        <v>577.3796182048931</v>
       </c>
       <c r="O76">
-        <v>101.4931964589297</v>
+        <v>109.7021274589297</v>
       </c>
       <c r="P76">
-        <v>432.6815217459634</v>
+        <v>467.6774907459634</v>
       </c>
       <c r="Q76">
-        <v>786.2815217459635</v>
+        <v>821.2774907459634</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1526779266376843</v>
+        <v>0.1526341541887526</v>
       </c>
       <c r="T76">
         <v>1.956705052572247</v>
       </c>
       <c r="U76">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V76">
         <v>0.19</v>
       </c>
       <c r="W76">
-        <v>0.07312769575998017</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.369472939417061</v>
+        <v>2.664619962312033</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09402259721429709</v>
+        <v>0.08793624153883831</v>
       </c>
       <c r="C77">
-        <v>278.3874124124395</v>
+        <v>834.1686795633887</v>
       </c>
       <c r="D77">
-        <v>3857.262412412439</v>
+        <v>4413.043679563389</v>
       </c>
       <c r="E77">
         <v>424.4749999999999</v>
@@ -7601,45 +7601,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M77">
-        <v>395.3296774950409</v>
+        <v>351.540927495041</v>
       </c>
       <c r="N77">
-        <v>528.9036558382925</v>
+        <v>572.6924058382924</v>
       </c>
       <c r="O77">
-        <v>100.4916946092756</v>
+        <v>108.8115571092756</v>
       </c>
       <c r="P77">
-        <v>428.4119612290169</v>
+        <v>463.8808487290169</v>
       </c>
       <c r="Q77">
-        <v>782.0119612290169</v>
+        <v>817.4808487290169</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1567073015772479</v>
+        <v>0.1566618788754126</v>
       </c>
       <c r="T77">
         <v>2.03047424468691</v>
       </c>
       <c r="U77">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V77">
         <v>0.19</v>
       </c>
       <c r="W77">
-        <v>0.07312769575998017</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.337879966891499</v>
+        <v>2.629091696147872</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09423443864041098</v>
+        <v>0.08806710812621557</v>
       </c>
       <c r="C78">
-        <v>203.1316073968692</v>
+        <v>762.1201006744168</v>
       </c>
       <c r="D78">
-        <v>3840.391607396869</v>
+        <v>4399.380100674417</v>
       </c>
       <c r="E78">
         <v>482.8600000000001</v>
@@ -7683,45 +7683,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M78">
-        <v>400.6007398616414</v>
+        <v>356.2281398616416</v>
       </c>
       <c r="N78">
-        <v>523.632593471692</v>
+        <v>568.0051934716919</v>
       </c>
       <c r="O78">
-        <v>99.49019275962148</v>
+        <v>107.9209867596215</v>
       </c>
       <c r="P78">
-        <v>424.1424007120705</v>
+        <v>460.0842067120705</v>
       </c>
       <c r="Q78">
-        <v>777.7424007120705</v>
+        <v>813.6842067120705</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1610724577617752</v>
+        <v>0.161025247285961</v>
       </c>
       <c r="T78">
         <v>2.110390869477794</v>
       </c>
       <c r="U78">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V78">
         <v>0.19</v>
       </c>
       <c r="W78">
-        <v>0.07312769575998017</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.307118388379769</v>
+        <v>2.594498384356452</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09444628006652483</v>
+        <v>0.08819797471359284</v>
       </c>
       <c r="C79">
-        <v>128.0227379903263</v>
+        <v>690.1558704342951</v>
       </c>
       <c r="D79">
-        <v>3823.667737990327</v>
+        <v>4385.800870434296</v>
       </c>
       <c r="E79">
         <v>541.2450000000003</v>
@@ -7765,45 +7765,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M79">
-        <v>405.871802228242</v>
+        <v>360.9153522282421</v>
       </c>
       <c r="N79">
-        <v>518.3615311050914</v>
+        <v>563.3179811050913</v>
       </c>
       <c r="O79">
-        <v>98.48869090996737</v>
+        <v>107.0304164099674</v>
       </c>
       <c r="P79">
-        <v>419.8728401951241</v>
+        <v>456.287564695124</v>
       </c>
       <c r="Q79">
-        <v>773.472840195124</v>
+        <v>809.887564695124</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.165817192744957</v>
+        <v>0.165768039036557</v>
       </c>
       <c r="T79">
         <v>2.197256765989625</v>
       </c>
       <c r="U79">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V79">
         <v>0.19</v>
       </c>
       <c r="W79">
-        <v>0.07312769575998017</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.277155811907305</v>
+        <v>2.560803600144031</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09465812149263869</v>
+        <v>0.08832884130097012</v>
       </c>
       <c r="C80">
-        <v>53.05889292107076</v>
+        <v>618.2752101888582</v>
       </c>
       <c r="D80">
-        <v>3807.08889292107</v>
+        <v>4372.305210188858</v>
       </c>
       <c r="E80">
         <v>599.6299999999997</v>
@@ -7847,45 +7847,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M80">
-        <v>411.1428645948425</v>
+        <v>365.6025645948426</v>
       </c>
       <c r="N80">
-        <v>513.0904687384909</v>
+        <v>558.6307687384908</v>
       </c>
       <c r="O80">
-        <v>97.48718906031328</v>
+        <v>106.1398460603133</v>
       </c>
       <c r="P80">
-        <v>415.6032796781776</v>
+        <v>452.4909226781775</v>
       </c>
       <c r="Q80">
-        <v>769.2032796781776</v>
+        <v>806.0909226781775</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1709932672720644</v>
+        <v>0.1709419936735708</v>
       </c>
       <c r="T80">
         <v>2.29201956218435</v>
       </c>
       <c r="U80">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V80">
         <v>0.19</v>
       </c>
       <c r="W80">
-        <v>0.07312769575998017</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.247961506626442</v>
+        <v>2.527972784757569</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09486996291875255</v>
+        <v>0.09095531788834738</v>
       </c>
       <c r="C81">
-        <v>-21.7618060778068</v>
+        <v>305.5733809767644</v>
       </c>
       <c r="D81">
-        <v>3790.653193922194</v>
+        <v>4117.988380976764</v>
       </c>
       <c r="E81">
         <v>658.0149999999999</v>
@@ -7929,37 +7929,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M81">
-        <v>416.4139269614431</v>
+        <v>388.2781954614431</v>
       </c>
       <c r="N81">
-        <v>507.8194063718904</v>
+        <v>535.9551378718904</v>
       </c>
       <c r="O81">
-        <v>96.48568721065917</v>
+        <v>101.8314761956592</v>
       </c>
       <c r="P81">
-        <v>411.3337191612312</v>
+        <v>434.1236616762312</v>
       </c>
       <c r="Q81">
-        <v>764.9337191612312</v>
+        <v>787.7236616762312</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1766623012779439</v>
+        <v>0.1766087058950621</v>
       </c>
       <c r="T81">
         <v>2.395807386588095</v>
       </c>
       <c r="U81">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V81">
         <v>0.19</v>
       </c>
       <c r="W81">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.219506297681804</v>
+        <v>2.38033797451578</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09508180434486641</v>
+        <v>0.09111777447572464</v>
       </c>
       <c r="C82">
-        <v>-96.44120497773565</v>
+        <v>232.4260863369182</v>
       </c>
       <c r="D82">
-        <v>3774.358795022265</v>
+        <v>4103.226086336918</v>
       </c>
       <c r="E82">
         <v>716.4000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M82">
-        <v>421.6849893280436</v>
+        <v>393.1931093280436</v>
       </c>
       <c r="N82">
-        <v>502.5483440052898</v>
+        <v>531.0402240052898</v>
       </c>
       <c r="O82">
-        <v>95.48418536100507</v>
+        <v>100.8976425610051</v>
       </c>
       <c r="P82">
-        <v>407.0641586442848</v>
+        <v>430.1425814442848</v>
       </c>
       <c r="Q82">
-        <v>760.6641586442847</v>
+        <v>783.7425814442847</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1828982386844114</v>
+        <v>0.1828420893387026</v>
       </c>
       <c r="T82">
         <v>2.509973993432216</v>
       </c>
       <c r="U82">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V82">
         <v>0.19</v>
       </c>
       <c r="W82">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.191762468960781</v>
+        <v>2.350583749834333</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09529364577098029</v>
+        <v>0.0912802310631019</v>
       </c>
       <c r="C83">
-        <v>-170.9811181458381</v>
+        <v>159.3842543103001</v>
       </c>
       <c r="D83">
-        <v>3758.203881854162</v>
+        <v>4088.5692543103</v>
       </c>
       <c r="E83">
         <v>774.7850000000003</v>
@@ -8093,37 +8093,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M83">
-        <v>426.9560516946442</v>
+        <v>398.1080231946443</v>
       </c>
       <c r="N83">
-        <v>497.2772816386893</v>
+        <v>526.1253101386892</v>
       </c>
       <c r="O83">
-        <v>94.48268351135096</v>
+        <v>99.96380892635095</v>
       </c>
       <c r="P83">
-        <v>402.7945981273383</v>
+        <v>426.1615012123382</v>
       </c>
       <c r="Q83">
-        <v>756.3945981273383</v>
+        <v>779.7615012123383</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1897905905547176</v>
+        <v>0.1897316184079894</v>
       </c>
       <c r="T83">
         <v>2.636158137838875</v>
       </c>
       <c r="U83">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V83">
         <v>0.19</v>
       </c>
       <c r="W83">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.164703673047685</v>
+        <v>2.321564197367241</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09550548719709415</v>
+        <v>0.09144268765047918</v>
       </c>
       <c r="C84">
-        <v>-245.3833290183866</v>
+        <v>86.44675877372447</v>
       </c>
       <c r="D84">
-        <v>3742.186670981614</v>
+        <v>4074.016758773725</v>
       </c>
       <c r="E84">
         <v>833.1700000000005</v>
@@ -8175,37 +8175,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M84">
-        <v>432.2271140612448</v>
+        <v>403.0229370612448</v>
       </c>
       <c r="N84">
-        <v>492.0062192720887</v>
+        <v>521.2103962720887</v>
       </c>
       <c r="O84">
-        <v>93.48118166169685</v>
+        <v>99.02997529169686</v>
       </c>
       <c r="P84">
-        <v>398.5250376103918</v>
+        <v>422.1804209803918</v>
       </c>
       <c r="Q84">
-        <v>752.1250376103919</v>
+        <v>775.7804209803919</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1974487592995023</v>
+        <v>0.1973866507071969</v>
       </c>
       <c r="T84">
         <v>2.776362742735163</v>
       </c>
       <c r="U84">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V84">
         <v>0.19</v>
       </c>
       <c r="W84">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.138304847766615</v>
+        <v>2.293252438862763</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.095717328623208</v>
+        <v>0.09160514423785646</v>
       </c>
       <c r="C85">
-        <v>-319.6495907571507</v>
+        <v>13.61248958004217</v>
       </c>
       <c r="D85">
-        <v>3726.305409242851</v>
+        <v>4059.567489580043</v>
       </c>
       <c r="E85">
         <v>891.5550000000007</v>
@@ -8257,37 +8257,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M85">
-        <v>437.4981764278454</v>
+        <v>407.9378509278454</v>
       </c>
       <c r="N85">
-        <v>486.7351569054881</v>
+        <v>516.2954824054881</v>
       </c>
       <c r="O85">
-        <v>92.47967981204275</v>
+        <v>98.09614165704274</v>
       </c>
       <c r="P85">
-        <v>394.2554770934454</v>
+        <v>418.1993407484454</v>
       </c>
       <c r="Q85">
-        <v>747.8554770934454</v>
+        <v>771.7993407484454</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2060078890730851</v>
+        <v>0.2059422750416054</v>
       </c>
       <c r="T85">
         <v>2.933062007031015</v>
       </c>
       <c r="U85">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V85">
         <v>0.19</v>
       </c>
       <c r="W85">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.112542138757379</v>
+        <v>2.265622891406585</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09592917004932186</v>
+        <v>0.09176760082523372</v>
       </c>
       <c r="C86">
-        <v>-393.7816268890683</v>
+        <v>-59.11964772416923</v>
       </c>
       <c r="D86">
-        <v>3710.558373110932</v>
+        <v>4045.220352275831</v>
       </c>
       <c r="E86">
         <v>949.9400000000001</v>
@@ -8339,37 +8339,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M86">
-        <v>442.7692387944458</v>
+        <v>412.8527647944459</v>
       </c>
       <c r="N86">
-        <v>481.4640945388877</v>
+        <v>511.3805685388876</v>
       </c>
       <c r="O86">
-        <v>91.47817796238866</v>
+        <v>97.16230802238864</v>
       </c>
       <c r="P86">
-        <v>389.985916576499</v>
+        <v>414.218260516499</v>
       </c>
       <c r="Q86">
-        <v>743.585916576499</v>
+        <v>767.818260516499</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2156369100683657</v>
+        <v>0.2155673524178148</v>
       </c>
       <c r="T86">
         <v>3.109348679363846</v>
       </c>
       <c r="U86">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V86">
         <v>0.19</v>
       </c>
       <c r="W86">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.087392827581696</v>
+        <v>2.238651190318412</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.09614101147543573</v>
+        <v>0.09193005741261098</v>
       </c>
       <c r="C87">
-        <v>-467.7811319297971</v>
+        <v>-131.7507321749572</v>
       </c>
       <c r="D87">
-        <v>3694.943868070203</v>
+        <v>4030.974267825042</v>
       </c>
       <c r="E87">
         <v>1008.324999999999</v>
@@ -8421,37 +8421,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M87">
-        <v>448.0403011610463</v>
+        <v>417.7676786610463</v>
       </c>
       <c r="N87">
-        <v>476.1930321722871</v>
+        <v>506.4656546722871</v>
       </c>
       <c r="O87">
-        <v>90.47667611273455</v>
+        <v>96.22847438773456</v>
       </c>
       <c r="P87">
-        <v>385.7163560595526</v>
+        <v>410.2371802845526</v>
       </c>
       <c r="Q87">
-        <v>739.3163560595526</v>
+        <v>763.8371802845526</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2265498005296839</v>
+        <v>0.2264757734441856</v>
       </c>
       <c r="T87">
         <v>3.309140241341057</v>
       </c>
       <c r="U87">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V87">
         <v>0.19</v>
       </c>
       <c r="W87">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.062835264904264</v>
+        <v>2.212314117491137</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09635285290154959</v>
+        <v>0.09209251399998826</v>
       </c>
       <c r="C88">
-        <v>-541.649771991556</v>
+        <v>-204.2818276615117</v>
       </c>
       <c r="D88">
-        <v>3679.460228008444</v>
+        <v>4016.828172338488</v>
       </c>
       <c r="E88">
         <v>1066.71</v>
@@ -8503,37 +8503,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M88">
-        <v>453.3113635276469</v>
+        <v>422.6825925276469</v>
       </c>
       <c r="N88">
-        <v>470.9219698056866</v>
+        <v>501.5507408056865</v>
       </c>
       <c r="O88">
-        <v>89.47517426308045</v>
+        <v>95.29464075308044</v>
       </c>
       <c r="P88">
-        <v>381.4467955426061</v>
+        <v>406.2561000526061</v>
       </c>
       <c r="Q88">
-        <v>735.0467955426061</v>
+        <v>759.8561000526061</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2390216753426189</v>
+        <v>0.2389425403314665</v>
       </c>
       <c r="T88">
         <v>3.537473455029298</v>
       </c>
       <c r="U88">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V88">
         <v>0.19</v>
       </c>
       <c r="W88">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.03884880833561</v>
+        <v>2.186589534729611</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09656469432766346</v>
+        <v>0.09225497058736552</v>
       </c>
       <c r="C89">
-        <v>-615.3891853757768</v>
+        <v>-276.713983191009</v>
       </c>
       <c r="D89">
-        <v>3664.105814624223</v>
+        <v>4002.78101680899</v>
       </c>
       <c r="E89">
         <v>1125.095</v>
@@ -8585,37 +8585,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M89">
-        <v>458.5824258942474</v>
+        <v>427.5975063942475</v>
       </c>
       <c r="N89">
-        <v>465.650907439086</v>
+        <v>496.635826939086</v>
       </c>
       <c r="O89">
-        <v>88.47367241342634</v>
+        <v>94.36080711842634</v>
       </c>
       <c r="P89">
-        <v>377.1772350256597</v>
+        <v>402.2750198206596</v>
       </c>
       <c r="Q89">
-        <v>730.7772350256597</v>
+        <v>755.8750198206596</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2534123001267746</v>
+        <v>0.2533272713552521</v>
       </c>
       <c r="T89">
         <v>3.800934855438806</v>
       </c>
       <c r="U89">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V89">
         <v>0.19</v>
       </c>
       <c r="W89">
-        <v>0.07312769575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.015413764561638</v>
+        <v>2.161456321686742</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1083951757537773</v>
+        <v>0.0924174271747428</v>
       </c>
       <c r="C90">
-        <v>-1366.289786797535</v>
+        <v>-349.048233147937</v>
       </c>
       <c r="D90">
-        <v>2971.590213202465</v>
+        <v>3988.831766852064</v>
       </c>
       <c r="E90">
         <v>1183.48</v>
@@ -8667,45 +8667,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M90">
-        <v>547.600932260848</v>
+        <v>432.512420260848</v>
       </c>
       <c r="N90">
-        <v>376.6324010724854</v>
+        <v>491.7209130724854</v>
       </c>
       <c r="O90">
-        <v>71.56015620377224</v>
+        <v>93.42697348377223</v>
       </c>
       <c r="P90">
-        <v>305.0722448687132</v>
+        <v>398.2939395887132</v>
       </c>
       <c r="Q90">
-        <v>658.6722448687133</v>
+        <v>751.8939395887132</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2702013623749564</v>
+        <v>0.2701094575496688</v>
       </c>
       <c r="T90">
         <v>4.1083064892499</v>
       </c>
       <c r="U90">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V90">
         <v>0.19</v>
       </c>
       <c r="W90">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.687786267122492</v>
+        <v>2.136894318031211</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1087390471798912</v>
+        <v>0.09257988376212006</v>
       </c>
       <c r="C91">
-        <v>-1440.910256036833</v>
+        <v>-421.2855975479861</v>
       </c>
       <c r="D91">
-        <v>2955.354743963167</v>
+        <v>3974.979402452015</v>
       </c>
       <c r="E91">
         <v>1241.865</v>
@@ -8749,45 +8749,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M91">
-        <v>553.8236701274486</v>
+        <v>437.4273341274486</v>
       </c>
       <c r="N91">
-        <v>370.4096632058848</v>
+        <v>486.8059992058849</v>
       </c>
       <c r="O91">
-        <v>70.37783600911813</v>
+        <v>92.49313984911812</v>
       </c>
       <c r="P91">
-        <v>300.0318271967667</v>
+        <v>394.3128593567668</v>
       </c>
       <c r="Q91">
-        <v>653.6318271967667</v>
+        <v>747.9128593567668</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2900429813955348</v>
+        <v>0.2899429503248883</v>
       </c>
       <c r="T91">
         <v>4.471563874663009</v>
       </c>
       <c r="U91">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V91">
         <v>0.19</v>
       </c>
       <c r="W91">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.668822376480666</v>
+        <v>2.112884269514006</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.109082918606005</v>
+        <v>0.09274234034949733</v>
       </c>
       <c r="C92">
-        <v>-1515.354282277487</v>
+        <v>-493.4270822866974</v>
       </c>
       <c r="D92">
-        <v>2939.295717722513</v>
+        <v>3961.222917713303</v>
       </c>
       <c r="E92">
         <v>1300.25</v>
@@ -8831,45 +8831,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M92">
-        <v>560.0464079940492</v>
+        <v>442.3422479940492</v>
       </c>
       <c r="N92">
-        <v>364.1869253392842</v>
+        <v>481.8910853392843</v>
       </c>
       <c r="O92">
-        <v>69.195515814464</v>
+        <v>91.55930621446402</v>
       </c>
       <c r="P92">
-        <v>294.9914095248203</v>
+        <v>390.3317791248203</v>
       </c>
       <c r="Q92">
-        <v>648.5914095248203</v>
+        <v>743.9317791248203</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3138529242202289</v>
+        <v>0.3137431416551519</v>
       </c>
       <c r="T92">
         <v>4.907472737158742</v>
       </c>
       <c r="U92">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V92">
         <v>0.19</v>
       </c>
       <c r="W92">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.650279905630881</v>
+        <v>2.089407777630517</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1094267900321189</v>
+        <v>0.09290479693687462</v>
       </c>
       <c r="C93">
-        <v>-1589.624726281709</v>
+        <v>-565.4736793829506</v>
       </c>
       <c r="D93">
-        <v>2923.410273718291</v>
+        <v>3947.56132061705</v>
       </c>
       <c r="E93">
         <v>1358.635</v>
@@ -8913,45 +8913,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M93">
-        <v>566.2691458606497</v>
+        <v>447.2571618606497</v>
       </c>
       <c r="N93">
-        <v>357.9641874726838</v>
+        <v>476.9761714726838</v>
       </c>
       <c r="O93">
-        <v>68.01319561980992</v>
+        <v>90.62547257980992</v>
       </c>
       <c r="P93">
-        <v>289.9509918528738</v>
+        <v>386.3506988928739</v>
       </c>
       <c r="Q93">
-        <v>643.5509918528738</v>
+        <v>739.9506988928739</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3429539654504107</v>
+        <v>0.3428322643921407</v>
       </c>
       <c r="T93">
         <v>5.440250235764638</v>
       </c>
       <c r="U93">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V93">
         <v>0.19</v>
       </c>
       <c r="W93">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.63214496161296</v>
+        <v>2.066447252601611</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1097706614582328</v>
+        <v>0.09306725352425188</v>
       </c>
       <c r="C94">
-        <v>-1663.724387300117</v>
+        <v>-637.4263672174229</v>
       </c>
       <c r="D94">
-        <v>2907.695612699883</v>
+        <v>3933.993632782577</v>
       </c>
       <c r="E94">
         <v>1417.02</v>
@@ -8995,45 +8995,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M94">
-        <v>572.4918837272502</v>
+        <v>452.1720757272502</v>
       </c>
       <c r="N94">
-        <v>351.7414496060833</v>
+        <v>472.0612576060832</v>
       </c>
       <c r="O94">
-        <v>66.83087542515582</v>
+        <v>89.69163894515582</v>
       </c>
       <c r="P94">
-        <v>284.9105741809275</v>
+        <v>382.3696186609274</v>
       </c>
       <c r="Q94">
-        <v>638.5105741809275</v>
+        <v>735.9696186609274</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3793302669881378</v>
+        <v>0.3791936678133767</v>
       </c>
       <c r="T94">
         <v>6.106222109022008</v>
       </c>
       <c r="U94">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V94">
         <v>0.19</v>
       </c>
       <c r="W94">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.614404255508471</v>
+        <v>2.043985869421158</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1101145328843466</v>
+        <v>0.09322971011162914</v>
       </c>
       <c r="C95">
-        <v>-1737.656004716155</v>
+        <v>-709.2861107661729</v>
       </c>
       <c r="D95">
-        <v>2892.148995283845</v>
+        <v>3920.518889233827</v>
       </c>
       <c r="E95">
         <v>1475.405</v>
@@ -9077,45 +9077,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M95">
-        <v>578.7146215938508</v>
+        <v>457.0869895938508</v>
       </c>
       <c r="N95">
-        <v>345.5187117394827</v>
+        <v>467.1463437394827</v>
       </c>
       <c r="O95">
-        <v>65.64855523050171</v>
+        <v>88.75780531050171</v>
       </c>
       <c r="P95">
-        <v>279.870156508981</v>
+        <v>378.388538428981</v>
       </c>
       <c r="Q95">
-        <v>633.4701565089811</v>
+        <v>731.988538428981</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4260997975366441</v>
+        <v>0.4259440436406801</v>
       </c>
       <c r="T95">
         <v>6.962471660352911</v>
       </c>
       <c r="U95">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V95">
         <v>0.19</v>
       </c>
       <c r="W95">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.597045069965369</v>
+        <v>2.022007526739211</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1104584043104605</v>
+        <v>0.09339216669900641</v>
       </c>
       <c r="C96">
-        <v>-1811.422259638049</v>
+        <v>-781.053861829414</v>
       </c>
       <c r="D96">
-        <v>2876.767740361952</v>
+        <v>3907.136138170587</v>
       </c>
       <c r="E96">
         <v>1533.79</v>
@@ -9159,45 +9159,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M96">
-        <v>584.9373594604514</v>
+        <v>462.0019034604513</v>
       </c>
       <c r="N96">
-        <v>339.2959738728821</v>
+        <v>462.2314298728821</v>
       </c>
       <c r="O96">
-        <v>64.4662350358476</v>
+        <v>87.8239716758476</v>
       </c>
       <c r="P96">
-        <v>274.8297388370345</v>
+        <v>374.4074581970345</v>
       </c>
       <c r="Q96">
-        <v>628.4297388370345</v>
+        <v>728.0074581970346</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4884591716013194</v>
+        <v>0.4882778780770847</v>
       </c>
       <c r="T96">
         <v>8.104137728794118</v>
       </c>
       <c r="U96">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V96">
         <v>0.19</v>
       </c>
       <c r="W96">
-        <v>0.08633069575998017</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.580055228795525</v>
+        <v>2.000496808369644</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1108022757365744</v>
+        <v>0.1044815232863837</v>
       </c>
       <c r="C97">
-        <v>-1885.025776440223</v>
+        <v>-1577.790960498527</v>
       </c>
       <c r="D97">
-        <v>2861.549223559778</v>
+        <v>3168.784039501474</v>
       </c>
       <c r="E97">
         <v>1592.175000000001</v>
@@ -9241,37 +9241,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M97">
-        <v>591.160097327052</v>
+        <v>545.6781823270519</v>
       </c>
       <c r="N97">
-        <v>333.0732360062815</v>
+        <v>378.5551510062816</v>
       </c>
       <c r="O97">
-        <v>63.28391484119349</v>
+        <v>71.9254786911935</v>
       </c>
       <c r="P97">
-        <v>269.789321165088</v>
+        <v>306.629672315088</v>
       </c>
       <c r="Q97">
-        <v>623.3893211650879</v>
+        <v>660.229672315088</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5757622952918645</v>
+        <v>0.5755452462880511</v>
       </c>
       <c r="T97">
         <v>9.702470224611806</v>
       </c>
       <c r="U97">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V97">
         <v>0.19</v>
       </c>
       <c r="W97">
-        <v>0.08633069575998017</v>
+        <v>0.07968869575998018</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.563423068492414</v>
+        <v>1.69373334552598</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1111461471626882</v>
+        <v>0.104758999873761</v>
       </c>
       <c r="C98">
-        <v>-1958.469124256058</v>
+        <v>-1651.089093070298</v>
       </c>
       <c r="D98">
-        <v>2846.490875743943</v>
+        <v>3153.870906929702</v>
       </c>
       <c r="E98">
         <v>1650.56</v>
@@ -9323,37 +9323,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M98">
-        <v>597.3828351936525</v>
+        <v>551.4221631936524</v>
       </c>
       <c r="N98">
-        <v>326.850498139681</v>
+        <v>372.8111701396811</v>
       </c>
       <c r="O98">
-        <v>62.10159464653939</v>
+        <v>70.8341223265394</v>
       </c>
       <c r="P98">
-        <v>264.7489034931416</v>
+        <v>301.9770478131417</v>
       </c>
       <c r="Q98">
-        <v>618.3489034931416</v>
+        <v>655.5770478131417</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7067169808276808</v>
+        <v>0.7064462986044993</v>
       </c>
       <c r="T98">
         <v>12.09996896833831</v>
       </c>
       <c r="U98">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V98">
         <v>0.19</v>
       </c>
       <c r="W98">
-        <v>0.08633069575998017</v>
+        <v>0.07968869575998018</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.547137411528951</v>
+        <v>1.676090289843418</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1114900185888021</v>
+        <v>0.1050364764611382</v>
       </c>
       <c r="C99">
-        <v>-2031.754818423756</v>
+        <v>-1724.247512904907</v>
       </c>
       <c r="D99">
-        <v>2831.590181576245</v>
+        <v>3139.097487095094</v>
       </c>
       <c r="E99">
         <v>1708.945</v>
@@ -9405,37 +9405,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M99">
-        <v>603.6055730602529</v>
+        <v>557.166144060253</v>
       </c>
       <c r="N99">
-        <v>320.6277602730805</v>
+        <v>367.0671892730804</v>
       </c>
       <c r="O99">
-        <v>60.9192744518853</v>
+        <v>69.74276596188528</v>
       </c>
       <c r="P99">
-        <v>259.7084858211952</v>
+        <v>297.3244233111951</v>
       </c>
       <c r="Q99">
-        <v>613.3084858211953</v>
+        <v>650.9244233111951</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9249747900540432</v>
+        <v>0.9246147191319147</v>
       </c>
       <c r="T99">
         <v>16.09580020788252</v>
       </c>
       <c r="U99">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V99">
         <v>0.19</v>
       </c>
       <c r="W99">
-        <v>0.08633069575998017</v>
+        <v>0.07968869575998018</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.531187541307003</v>
+        <v>1.658811008504826</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1118338900149159</v>
+        <v>0.1053139530485155</v>
       </c>
       <c r="C100">
-        <v>-2104.885321887033</v>
+        <v>-1797.268174183424</v>
       </c>
       <c r="D100">
-        <v>2816.844678112967</v>
+        <v>3124.461825816575</v>
       </c>
       <c r="E100">
         <v>1767.329999999999</v>
@@ -9487,37 +9487,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M100">
-        <v>609.8283109268534</v>
+        <v>562.9101249268534</v>
       </c>
       <c r="N100">
-        <v>314.40502240648</v>
+        <v>361.32320840648</v>
       </c>
       <c r="O100">
-        <v>59.73695425723121</v>
+        <v>68.65140959723121</v>
       </c>
       <c r="P100">
-        <v>254.6680681492488</v>
+        <v>292.6717988092488</v>
       </c>
       <c r="Q100">
-        <v>608.2680681492488</v>
+        <v>646.2717988092488</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.361490408506768</v>
+        <v>1.360951560186745</v>
       </c>
       <c r="T100">
         <v>24.08746268697093</v>
       </c>
       <c r="U100">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V100">
         <v>0.19</v>
       </c>
       <c r="W100">
-        <v>0.08633069575998017</v>
+        <v>0.07968869575998018</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.515563178640606</v>
+        <v>1.641884365560899</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1121777614410298</v>
+        <v>0.1055914296358928</v>
       </c>
       <c r="C101">
-        <v>-2177.863046552273</v>
+        <v>-1870.152994811525</v>
       </c>
       <c r="D101">
-        <v>2802.251953447726</v>
+        <v>3109.962005188475</v>
       </c>
       <c r="E101">
         <v>1825.715</v>
@@ -9569,37 +9569,37 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M101">
-        <v>616.051048793454</v>
+        <v>568.6541057934541</v>
       </c>
       <c r="N101">
-        <v>308.1822845398794</v>
+        <v>355.5792275398794</v>
       </c>
       <c r="O101">
-        <v>58.55463406257709</v>
+        <v>67.56005323257709</v>
       </c>
       <c r="P101">
-        <v>249.6276504773024</v>
+        <v>288.0191743073023</v>
       </c>
       <c r="Q101">
-        <v>603.2276504773024</v>
+        <v>641.6191743073023</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.671037263864942</v>
+        <v>2.669962083351238</v>
       </c>
       <c r="T101">
         <v>48.06245012423618</v>
       </c>
       <c r="U101">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V101">
         <v>0.19</v>
       </c>
       <c r="W101">
-        <v>0.08633069575998017</v>
+        <v>0.07968869575998018</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>1.500254459664438</v>
+        <v>1.625299674999678</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/poland/poland_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_cable_tv.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07812124748554304</v>
+        <v>0.07807715407292032</v>
       </c>
       <c r="C2">
-        <v>6553.152766974722</v>
+        <v>6502.627076325932</v>
       </c>
       <c r="D2">
-        <v>5753.152766974722</v>
+        <v>5761.012076325932</v>
       </c>
       <c r="E2">
-        <v>-3954.4</v>
+        <v>-3896.015</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>58.385</v>
       </c>
       <c r="G2">
         <v>800</v>
@@ -1451,28 +1451,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.426096366600546</v>
       </c>
       <c r="N2">
-        <v>924.2333333333335</v>
+        <v>920.8072369667329</v>
       </c>
       <c r="O2">
-        <v>175.6043333333334</v>
+        <v>174.9533750236793</v>
       </c>
       <c r="P2">
-        <v>748.6290000000001</v>
+        <v>745.8538619430537</v>
       </c>
       <c r="Q2">
-        <v>1102.229</v>
+        <v>1099.453861943054</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07812124748554304</v>
+        <v>0.07838569405587931</v>
       </c>
       <c r="T2">
-        <v>0.5919749984509941</v>
+        <v>0.5968184302565023</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>269.7627954494403</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07807715407292032</v>
+        <v>0.07803306066029758</v>
       </c>
       <c r="C3">
-        <v>6502.627076325932</v>
+        <v>6452.12288805781</v>
       </c>
       <c r="D3">
-        <v>5761.012076325932</v>
+        <v>5768.892888057811</v>
       </c>
       <c r="E3">
-        <v>-3896.015</v>
+        <v>-3837.63</v>
       </c>
       <c r="F3">
-        <v>58.385</v>
+        <v>116.77</v>
       </c>
       <c r="G3">
         <v>800</v>
@@ -1533,28 +1533,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M3">
-        <v>3.426096366600546</v>
+        <v>6.852192733201091</v>
       </c>
       <c r="N3">
-        <v>920.8072369667329</v>
+        <v>917.3811406001324</v>
       </c>
       <c r="O3">
-        <v>174.9533750236793</v>
+        <v>174.3024167140252</v>
       </c>
       <c r="P3">
-        <v>745.8538619430537</v>
+        <v>743.0787238861072</v>
       </c>
       <c r="Q3">
-        <v>1099.453861943054</v>
+        <v>1096.678723886107</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07838569405587931</v>
+        <v>0.07865553749499794</v>
       </c>
       <c r="T3">
-        <v>0.5968184302565023</v>
+        <v>0.6017607076090616</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>269.7627954494403</v>
+        <v>134.8813977247201</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07803306066029758</v>
+        <v>0.07798896724767486</v>
       </c>
       <c r="C4">
-        <v>6452.12288805781</v>
+        <v>6401.640290534169</v>
       </c>
       <c r="D4">
-        <v>5768.892888057811</v>
+        <v>5776.795290534169</v>
       </c>
       <c r="E4">
-        <v>-3837.63</v>
+        <v>-3779.245</v>
       </c>
       <c r="F4">
-        <v>116.77</v>
+        <v>175.155</v>
       </c>
       <c r="G4">
         <v>800</v>
@@ -1615,28 +1615,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M4">
-        <v>6.852192733201091</v>
+        <v>10.27828909980164</v>
       </c>
       <c r="N4">
-        <v>917.3811406001324</v>
+        <v>913.9550442335318</v>
       </c>
       <c r="O4">
-        <v>174.3024167140252</v>
+        <v>173.6514584043711</v>
       </c>
       <c r="P4">
-        <v>743.0787238861072</v>
+        <v>740.3035858291607</v>
       </c>
       <c r="Q4">
-        <v>1096.678723886107</v>
+        <v>1093.903585829161</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07865553749499794</v>
+        <v>0.07893094471636644</v>
       </c>
       <c r="T4">
-        <v>0.6017607076090616</v>
+        <v>0.6068048875874469</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>134.8813977247201</v>
+        <v>89.92093181648008</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07798896724767486</v>
+        <v>0.07794487383505212</v>
       </c>
       <c r="C5">
-        <v>6401.640290534169</v>
+        <v>6351.179372603666</v>
       </c>
       <c r="D5">
-        <v>5776.795290534169</v>
+        <v>5784.719372603666</v>
       </c>
       <c r="E5">
-        <v>-3779.245</v>
+        <v>-3720.86</v>
       </c>
       <c r="F5">
-        <v>175.155</v>
+        <v>233.54</v>
       </c>
       <c r="G5">
         <v>800</v>
@@ -1697,28 +1697,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M5">
-        <v>10.27828909980164</v>
+        <v>13.70438546640218</v>
       </c>
       <c r="N5">
-        <v>913.9550442335318</v>
+        <v>910.5289478669313</v>
       </c>
       <c r="O5">
-        <v>173.6514584043711</v>
+        <v>173.000500094717</v>
       </c>
       <c r="P5">
-        <v>740.3035858291607</v>
+        <v>737.5284477722143</v>
       </c>
       <c r="Q5">
-        <v>1093.903585829161</v>
+        <v>1091.128447772214</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07893094471636644</v>
+        <v>0.07921208958818013</v>
       </c>
       <c r="T5">
-        <v>0.6068048875874469</v>
+        <v>0.6119541546487152</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>89.92093181648008</v>
+        <v>67.44069886236007</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07794487383505212</v>
+        <v>0.0779007804224294</v>
       </c>
       <c r="C6">
-        <v>6351.179372603666</v>
+        <v>6300.740223603121</v>
       </c>
       <c r="D6">
-        <v>5784.719372603666</v>
+        <v>5792.665223603121</v>
       </c>
       <c r="E6">
-        <v>-3720.86</v>
+        <v>-3662.475</v>
       </c>
       <c r="F6">
-        <v>233.54</v>
+        <v>291.925</v>
       </c>
       <c r="G6">
         <v>800</v>
@@ -1779,28 +1779,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M6">
-        <v>13.70438546640218</v>
+        <v>17.13048183300273</v>
       </c>
       <c r="N6">
-        <v>910.5289478669313</v>
+        <v>907.1028515003308</v>
       </c>
       <c r="O6">
-        <v>173.000500094717</v>
+        <v>172.3495417850629</v>
       </c>
       <c r="P6">
-        <v>737.5284477722143</v>
+        <v>734.753309715268</v>
       </c>
       <c r="Q6">
-        <v>1091.128447772214</v>
+        <v>1088.353309715268</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07921208958818013</v>
+        <v>0.07949915329940041</v>
       </c>
       <c r="T6">
-        <v>0.6119541546487152</v>
+        <v>0.6172118273323259</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>67.44069886236007</v>
+        <v>53.95255908988805</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0779007804224294</v>
+        <v>0.07785668700980666</v>
       </c>
       <c r="C7">
-        <v>6300.740223603121</v>
+        <v>6250.322933360889</v>
       </c>
       <c r="D7">
-        <v>5792.665223603121</v>
+        <v>5800.632933360889</v>
       </c>
       <c r="E7">
-        <v>-3662.475</v>
+        <v>-3604.09</v>
       </c>
       <c r="F7">
-        <v>291.925</v>
+        <v>350.31</v>
       </c>
       <c r="G7">
         <v>800</v>
@@ -1861,28 +1861,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M7">
-        <v>17.13048183300273</v>
+        <v>20.55657819960328</v>
       </c>
       <c r="N7">
-        <v>907.1028515003308</v>
+        <v>903.6767551337302</v>
       </c>
       <c r="O7">
-        <v>172.3495417850629</v>
+        <v>171.6985834754088</v>
       </c>
       <c r="P7">
-        <v>734.753309715268</v>
+        <v>731.9781716583215</v>
       </c>
       <c r="Q7">
-        <v>1088.353309715268</v>
+        <v>1085.578171658321</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07949915329940041</v>
+        <v>0.07979232474915729</v>
       </c>
       <c r="T7">
-        <v>0.6172118273323259</v>
+        <v>0.6225813653921838</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>53.95255908988805</v>
+        <v>44.96046590824004</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07785668700980666</v>
+        <v>0.07781259359718394</v>
       </c>
       <c r="C8">
-        <v>6250.322933360889</v>
+        <v>6199.927592200219</v>
       </c>
       <c r="D8">
-        <v>5800.632933360889</v>
+        <v>5808.622592200219</v>
       </c>
       <c r="E8">
-        <v>-3604.09</v>
+        <v>-3545.705</v>
       </c>
       <c r="F8">
-        <v>350.31</v>
+        <v>408.6949999999999</v>
       </c>
       <c r="G8">
         <v>800</v>
@@ -1943,28 +1943,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M8">
-        <v>20.55657819960328</v>
+        <v>23.98267456620382</v>
       </c>
       <c r="N8">
-        <v>903.6767551337302</v>
+        <v>900.2506587671296</v>
       </c>
       <c r="O8">
-        <v>171.6985834754088</v>
+        <v>171.0476251657546</v>
       </c>
       <c r="P8">
-        <v>731.9781716583215</v>
+        <v>729.203033601375</v>
       </c>
       <c r="Q8">
-        <v>1085.578171658321</v>
+        <v>1082.803033601375</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07979232474915729</v>
+        <v>0.08009180096127454</v>
       </c>
       <c r="T8">
-        <v>0.6225813653921838</v>
+        <v>0.6280663773888128</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.96046590824004</v>
+        <v>38.53754220706289</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07781259359718393</v>
+        <v>0.07776850018456122</v>
       </c>
       <c r="C9">
-        <v>6199.927592200223</v>
+        <v>6149.554290942697</v>
       </c>
       <c r="D9">
-        <v>5808.622592200222</v>
+        <v>5816.634290942697</v>
       </c>
       <c r="E9">
-        <v>-3545.705</v>
+        <v>-3487.32</v>
       </c>
       <c r="F9">
-        <v>408.6950000000001</v>
+        <v>467.08</v>
       </c>
       <c r="G9">
         <v>800</v>
@@ -2025,28 +2025,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M9">
-        <v>23.98267456620383</v>
+        <v>27.40877093280437</v>
       </c>
       <c r="N9">
-        <v>900.2506587671296</v>
+        <v>896.8245624005291</v>
       </c>
       <c r="O9">
-        <v>171.0476251657546</v>
+        <v>170.3966668561005</v>
       </c>
       <c r="P9">
-        <v>729.203033601375</v>
+        <v>726.4278955444286</v>
       </c>
       <c r="Q9">
-        <v>1082.803033601375</v>
+        <v>1080.027895544429</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08009180096127454</v>
+        <v>0.08039778752582913</v>
       </c>
       <c r="T9">
-        <v>0.6280663773888128</v>
+        <v>0.6336706287766729</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.53754220706288</v>
+        <v>33.72034943118003</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07776850018456122</v>
+        <v>0.07772440677193848</v>
       </c>
       <c r="C10">
-        <v>6149.554290942697</v>
+        <v>6099.20312091167</v>
       </c>
       <c r="D10">
-        <v>5816.634290942697</v>
+        <v>5824.66812091167</v>
       </c>
       <c r="E10">
-        <v>-3487.32</v>
+        <v>-3428.935</v>
       </c>
       <c r="F10">
-        <v>467.08</v>
+        <v>525.465</v>
       </c>
       <c r="G10">
         <v>800</v>
@@ -2107,28 +2107,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M10">
-        <v>27.40877093280437</v>
+        <v>30.83486729940492</v>
       </c>
       <c r="N10">
-        <v>896.8245624005291</v>
+        <v>893.3984660339286</v>
       </c>
       <c r="O10">
-        <v>170.3966668561005</v>
+        <v>169.7457085464464</v>
       </c>
       <c r="P10">
-        <v>726.4278955444286</v>
+        <v>723.6527574874822</v>
       </c>
       <c r="Q10">
-        <v>1080.027895544429</v>
+        <v>1077.252757487482</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08039778752582913</v>
+        <v>0.08071049906982446</v>
       </c>
       <c r="T10">
-        <v>0.6336706287766729</v>
+        <v>0.6393980505247056</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.72034943118003</v>
+        <v>29.97364393882669</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07772440677193848</v>
+        <v>0.07768031335931574</v>
       </c>
       <c r="C11">
-        <v>6099.20312091167</v>
+        <v>6048.874173935717</v>
       </c>
       <c r="D11">
-        <v>5824.66812091167</v>
+        <v>5832.724173935717</v>
       </c>
       <c r="E11">
-        <v>-3428.935</v>
+        <v>-3370.55</v>
       </c>
       <c r="F11">
-        <v>525.465</v>
+        <v>583.8499999999999</v>
       </c>
       <c r="G11">
         <v>800</v>
@@ -2189,28 +2189,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M11">
-        <v>30.83486729940492</v>
+        <v>34.26096366600545</v>
       </c>
       <c r="N11">
-        <v>893.3984660339286</v>
+        <v>889.9723696673281</v>
       </c>
       <c r="O11">
-        <v>169.7457085464464</v>
+        <v>169.0947502367923</v>
       </c>
       <c r="P11">
-        <v>723.6527574874822</v>
+        <v>720.8776194305358</v>
       </c>
       <c r="Q11">
-        <v>1077.252757487482</v>
+        <v>1074.477619430536</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08071049906982446</v>
+        <v>0.08103015975924192</v>
       </c>
       <c r="T11">
-        <v>0.6393980505247056</v>
+        <v>0.6452527483115836</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.97364393882669</v>
+        <v>26.97627954494403</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07768031335931574</v>
+        <v>0.07763621994669301</v>
       </c>
       <c r="C12">
-        <v>6048.874173935716</v>
+        <v>5998.567542352149</v>
       </c>
       <c r="D12">
-        <v>5832.724173935717</v>
+        <v>5840.802542352149</v>
       </c>
       <c r="E12">
-        <v>-3370.55</v>
+        <v>-3312.165</v>
       </c>
       <c r="F12">
-        <v>583.85</v>
+        <v>642.235</v>
       </c>
       <c r="G12">
         <v>800</v>
@@ -2271,28 +2271,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M12">
-        <v>34.26096366600546</v>
+        <v>37.68706003260601</v>
       </c>
       <c r="N12">
-        <v>889.9723696673281</v>
+        <v>886.5462733007274</v>
       </c>
       <c r="O12">
-        <v>169.0947502367923</v>
+        <v>168.4437919271382</v>
       </c>
       <c r="P12">
-        <v>720.8776194305358</v>
+        <v>718.1024813735892</v>
       </c>
       <c r="Q12">
-        <v>1074.477619430536</v>
+        <v>1071.702481373589</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08103015975924192</v>
+        <v>0.08135700383493841</v>
       </c>
       <c r="T12">
-        <v>0.6452527483115836</v>
+        <v>0.6512390123408632</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.97627954494402</v>
+        <v>24.52389049540366</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07763621994669301</v>
+        <v>0.07759212653407027</v>
       </c>
       <c r="C13">
-        <v>5998.567542352149</v>
+        <v>5948.283319010541</v>
       </c>
       <c r="D13">
-        <v>5840.802542352149</v>
+        <v>5848.903319010541</v>
       </c>
       <c r="E13">
-        <v>-3312.165</v>
+        <v>-3253.78</v>
       </c>
       <c r="F13">
-        <v>642.235</v>
+        <v>700.62</v>
       </c>
       <c r="G13">
         <v>800</v>
@@ -2353,28 +2353,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M13">
-        <v>37.68706003260601</v>
+        <v>41.11315639920655</v>
       </c>
       <c r="N13">
-        <v>886.5462733007274</v>
+        <v>883.1201769341269</v>
       </c>
       <c r="O13">
-        <v>168.4437919271382</v>
+        <v>167.7928336174841</v>
       </c>
       <c r="P13">
-        <v>718.1024813735892</v>
+        <v>715.3273433166428</v>
       </c>
       <c r="Q13">
-        <v>1071.702481373589</v>
+        <v>1068.927343316643</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08135700383493841</v>
+        <v>0.08169127618508257</v>
       </c>
       <c r="T13">
-        <v>0.6512390123408632</v>
+        <v>0.6573613278253538</v>
       </c>
       <c r="U13">
         <v>0.05868110587651873</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.52389049540366</v>
+        <v>22.48023295412002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07759212653407027</v>
+        <v>0.07754803312144756</v>
       </c>
       <c r="C14">
-        <v>5948.283319010541</v>
+        <v>5898.021597276283</v>
       </c>
       <c r="D14">
-        <v>5848.903319010541</v>
+        <v>5857.026597276283</v>
       </c>
       <c r="E14">
-        <v>-3253.78</v>
+        <v>-3195.395</v>
       </c>
       <c r="F14">
-        <v>700.62</v>
+        <v>759.005</v>
       </c>
       <c r="G14">
         <v>800</v>
@@ -2435,28 +2435,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M14">
-        <v>41.11315639920655</v>
+        <v>44.5392527658071</v>
       </c>
       <c r="N14">
-        <v>883.1201769341269</v>
+        <v>879.6940805675264</v>
       </c>
       <c r="O14">
-        <v>167.7928336174841</v>
+        <v>167.14187530783</v>
       </c>
       <c r="P14">
-        <v>715.3273433166428</v>
+        <v>712.5522052596964</v>
       </c>
       <c r="Q14">
-        <v>1068.927343316643</v>
+        <v>1066.152205259697</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08169127618508257</v>
+        <v>0.08203323295706912</v>
       </c>
       <c r="T14">
-        <v>0.6573613278253538</v>
+        <v>0.6636243861945454</v>
       </c>
       <c r="U14">
         <v>0.05868110587651873</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.48023295412002</v>
+        <v>20.75098426534156</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07754803312144756</v>
+        <v>0.07750393970882481</v>
       </c>
       <c r="C15">
-        <v>5898.021597276283</v>
+        <v>5847.782471034181</v>
       </c>
       <c r="D15">
-        <v>5857.026597276283</v>
+        <v>5865.172471034181</v>
       </c>
       <c r="E15">
-        <v>-3195.395</v>
+        <v>-3137.01</v>
       </c>
       <c r="F15">
-        <v>759.005</v>
+        <v>817.3900000000001</v>
       </c>
       <c r="G15">
         <v>800</v>
@@ -2517,28 +2517,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M15">
-        <v>44.5392527658071</v>
+        <v>47.96534913240765</v>
       </c>
       <c r="N15">
-        <v>879.6940805675264</v>
+        <v>876.2679842009259</v>
       </c>
       <c r="O15">
-        <v>167.14187530783</v>
+        <v>166.4909169981759</v>
       </c>
       <c r="P15">
-        <v>712.5522052596964</v>
+        <v>709.77706720275</v>
       </c>
       <c r="Q15">
-        <v>1066.152205259697</v>
+        <v>1063.37706720275</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08203323295706912</v>
+        <v>0.08238314221212512</v>
       </c>
       <c r="T15">
-        <v>0.6636243861945454</v>
+        <v>0.6700330970839508</v>
       </c>
       <c r="U15">
         <v>0.05868110587651873</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.75098426534156</v>
+        <v>19.26877110353144</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07750393970882481</v>
+        <v>0.07745984629620209</v>
       </c>
       <c r="C16">
-        <v>5847.782471034181</v>
+        <v>5797.566034692045</v>
       </c>
       <c r="D16">
-        <v>5865.172471034181</v>
+        <v>5873.341034692045</v>
       </c>
       <c r="E16">
-        <v>-3137.01</v>
+        <v>-3078.625</v>
       </c>
       <c r="F16">
-        <v>817.3900000000001</v>
+        <v>875.7750000000001</v>
       </c>
       <c r="G16">
         <v>800</v>
@@ -2599,28 +2599,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M16">
-        <v>47.96534913240765</v>
+        <v>51.3914454990082</v>
       </c>
       <c r="N16">
-        <v>876.2679842009259</v>
+        <v>872.8418878343252</v>
       </c>
       <c r="O16">
-        <v>166.4909169981759</v>
+        <v>165.8399586885218</v>
       </c>
       <c r="P16">
-        <v>709.77706720275</v>
+        <v>707.0019291458034</v>
       </c>
       <c r="Q16">
-        <v>1063.37706720275</v>
+        <v>1060.601929145803</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08238314221212512</v>
+        <v>0.08274128462612361</v>
       </c>
       <c r="T16">
-        <v>0.6700330970839508</v>
+        <v>0.6765926011707539</v>
       </c>
       <c r="U16">
         <v>0.05868110587651873</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.26877110353144</v>
+        <v>17.98418636329601</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07745984629620209</v>
+        <v>0.07741575288357935</v>
       </c>
       <c r="C17">
-        <v>5797.566034692046</v>
+        <v>5747.372383184374</v>
       </c>
       <c r="D17">
-        <v>5873.341034692045</v>
+        <v>5881.532383184374</v>
       </c>
       <c r="E17">
-        <v>-3078.625</v>
+        <v>-3020.24</v>
       </c>
       <c r="F17">
-        <v>875.775</v>
+        <v>934.16</v>
       </c>
       <c r="G17">
         <v>800</v>
@@ -2681,28 +2681,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M17">
-        <v>51.39144549900819</v>
+        <v>54.81754186560873</v>
       </c>
       <c r="N17">
-        <v>872.8418878343252</v>
+        <v>869.4157914677247</v>
       </c>
       <c r="O17">
-        <v>165.8399586885218</v>
+        <v>165.1890003788677</v>
       </c>
       <c r="P17">
-        <v>707.0019291458034</v>
+        <v>704.226791088857</v>
       </c>
       <c r="Q17">
-        <v>1060.601929145803</v>
+        <v>1057.826791088857</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08274128462612361</v>
+        <v>0.0831079542404554</v>
       </c>
       <c r="T17">
-        <v>0.6765926011707539</v>
+        <v>0.6833082839262904</v>
       </c>
       <c r="U17">
         <v>0.05868110587651873</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.98418636329601</v>
+        <v>16.86017471559001</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07741575288357935</v>
+        <v>0.07737165947095663</v>
       </c>
       <c r="C18">
-        <v>5747.372383184374</v>
+        <v>5697.201611975996</v>
       </c>
       <c r="D18">
-        <v>5881.532383184374</v>
+        <v>5889.746611975997</v>
       </c>
       <c r="E18">
-        <v>-3020.24</v>
+        <v>-2961.855</v>
       </c>
       <c r="F18">
-        <v>934.16</v>
+        <v>992.5450000000001</v>
       </c>
       <c r="G18">
         <v>800</v>
@@ -2763,28 +2763,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M18">
-        <v>54.81754186560873</v>
+        <v>58.24363823220929</v>
       </c>
       <c r="N18">
-        <v>869.4157914677247</v>
+        <v>865.9896951011242</v>
       </c>
       <c r="O18">
-        <v>165.1890003788677</v>
+        <v>164.5380420692136</v>
       </c>
       <c r="P18">
-        <v>704.226791088857</v>
+        <v>701.4516530319106</v>
       </c>
       <c r="Q18">
-        <v>1057.826791088857</v>
+        <v>1055.051653031911</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0831079542404554</v>
+        <v>0.08348345926718073</v>
       </c>
       <c r="T18">
-        <v>0.6833082839262904</v>
+        <v>0.6901857903626831</v>
       </c>
       <c r="U18">
         <v>0.05868110587651873</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.86017471559001</v>
+        <v>15.86839973232001</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07737165947095663</v>
+        <v>0.07732756605833389</v>
       </c>
       <c r="C19">
-        <v>5697.201611975996</v>
+        <v>5647.053817065813</v>
       </c>
       <c r="D19">
-        <v>5889.746611975997</v>
+        <v>5897.983817065813</v>
       </c>
       <c r="E19">
-        <v>-2961.855</v>
+        <v>-2903.47</v>
       </c>
       <c r="F19">
-        <v>992.5450000000001</v>
+        <v>1050.93</v>
       </c>
       <c r="G19">
         <v>800</v>
@@ -2845,28 +2845,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M19">
-        <v>58.24363823220929</v>
+        <v>61.66973459880983</v>
       </c>
       <c r="N19">
-        <v>865.9896951011242</v>
+        <v>862.5635987345237</v>
       </c>
       <c r="O19">
-        <v>164.5380420692136</v>
+        <v>163.8870837595595</v>
       </c>
       <c r="P19">
-        <v>701.4516530319106</v>
+        <v>698.6765149749642</v>
       </c>
       <c r="Q19">
-        <v>1055.051653031911</v>
+        <v>1052.276514974964</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08348345926718073</v>
+        <v>0.08386812295309448</v>
       </c>
       <c r="T19">
-        <v>0.6901857903626831</v>
+        <v>0.6972310408585001</v>
       </c>
       <c r="U19">
         <v>0.05868110587651873</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.86839973232001</v>
+        <v>14.98682196941335</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07732756605833391</v>
+        <v>0.07728347264571117</v>
       </c>
       <c r="C20">
-        <v>5647.053817065811</v>
+        <v>5596.929094990506</v>
       </c>
       <c r="D20">
-        <v>5897.983817065811</v>
+        <v>5906.244094990506</v>
       </c>
       <c r="E20">
-        <v>-2903.47</v>
+        <v>-2845.085</v>
       </c>
       <c r="F20">
-        <v>1050.93</v>
+        <v>1109.315</v>
       </c>
       <c r="G20">
         <v>800</v>
@@ -2927,28 +2927,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M20">
-        <v>61.66973459880983</v>
+        <v>65.09583096541037</v>
       </c>
       <c r="N20">
-        <v>862.5635987345237</v>
+        <v>859.137502367923</v>
       </c>
       <c r="O20">
-        <v>163.8870837595595</v>
+        <v>163.2361254499054</v>
       </c>
       <c r="P20">
-        <v>698.6765149749642</v>
+        <v>695.9013769180176</v>
       </c>
       <c r="Q20">
-        <v>1052.276514974964</v>
+        <v>1049.501376918018</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08386812295309448</v>
+        <v>0.08426228450779621</v>
       </c>
       <c r="T20">
-        <v>0.6972310408585001</v>
+        <v>0.704450248156683</v>
       </c>
       <c r="U20">
         <v>0.05868110587651873</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.98682196941335</v>
+        <v>14.19804186576001</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07728347264571117</v>
+        <v>0.07723937923308846</v>
       </c>
       <c r="C21">
-        <v>5596.929094990506</v>
+        <v>5546.82754282833</v>
       </c>
       <c r="D21">
-        <v>5906.244094990506</v>
+        <v>5914.527542828329</v>
       </c>
       <c r="E21">
-        <v>-2845.085</v>
+        <v>-2786.7</v>
       </c>
       <c r="F21">
-        <v>1109.315</v>
+        <v>1167.7</v>
       </c>
       <c r="G21">
         <v>800</v>
@@ -3009,28 +3009,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M21">
-        <v>65.09583096541037</v>
+        <v>68.52192733201092</v>
       </c>
       <c r="N21">
-        <v>859.137502367923</v>
+        <v>855.7114060013225</v>
       </c>
       <c r="O21">
-        <v>163.2361254499054</v>
+        <v>162.5851671402513</v>
       </c>
       <c r="P21">
-        <v>695.9013769180176</v>
+        <v>693.1262388610712</v>
       </c>
       <c r="Q21">
-        <v>1049.501376918018</v>
+        <v>1046.726238861071</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08426228450779621</v>
+        <v>0.08466630010136551</v>
       </c>
       <c r="T21">
-        <v>0.704450248156683</v>
+        <v>0.7118499356373205</v>
       </c>
       <c r="U21">
         <v>0.05868110587651873</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.19804186576001</v>
+        <v>13.48813977247201</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07723937923308846</v>
+        <v>0.07719528582046573</v>
       </c>
       <c r="C22">
-        <v>5546.82754282833</v>
+        <v>5496.749258202918</v>
       </c>
       <c r="D22">
-        <v>5914.527542828329</v>
+        <v>5922.834258202918</v>
       </c>
       <c r="E22">
-        <v>-2786.7</v>
+        <v>-2728.315</v>
       </c>
       <c r="F22">
-        <v>1167.7</v>
+        <v>1226.085</v>
       </c>
       <c r="G22">
         <v>800</v>
@@ -3091,28 +3091,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M22">
-        <v>68.52192733201092</v>
+        <v>71.94802369861146</v>
       </c>
       <c r="N22">
-        <v>855.7114060013225</v>
+        <v>852.285309634722</v>
       </c>
       <c r="O22">
-        <v>162.5851671402513</v>
+        <v>161.9342088305972</v>
       </c>
       <c r="P22">
-        <v>693.1262388610712</v>
+        <v>690.3511008041248</v>
       </c>
       <c r="Q22">
-        <v>1046.726238861071</v>
+        <v>1043.951100804125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08466630010136551</v>
+        <v>0.08508054393780998</v>
       </c>
       <c r="T22">
-        <v>0.7118499356373205</v>
+        <v>0.7194369569782272</v>
       </c>
       <c r="U22">
         <v>0.05868110587651873</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.48813977247201</v>
+        <v>12.8458474023543</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07719528582046573</v>
+        <v>0.07741849240784299</v>
       </c>
       <c r="C23">
-        <v>5496.749258202918</v>
+        <v>5396.552788974021</v>
       </c>
       <c r="D23">
-        <v>5922.834258202918</v>
+        <v>5881.022788974022</v>
       </c>
       <c r="E23">
-        <v>-2728.315</v>
+        <v>-2669.93</v>
       </c>
       <c r="F23">
-        <v>1226.085</v>
+        <v>1284.47</v>
       </c>
       <c r="G23">
         <v>800</v>
@@ -3173,45 +3173,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M23">
-        <v>71.94802369861146</v>
+        <v>77.30082506521201</v>
       </c>
       <c r="N23">
-        <v>852.285309634722</v>
+        <v>846.9325082681214</v>
       </c>
       <c r="O23">
-        <v>161.9342088305972</v>
+        <v>160.9171765709431</v>
       </c>
       <c r="P23">
-        <v>690.3511008041248</v>
+        <v>686.0153316971783</v>
       </c>
       <c r="Q23">
-        <v>1043.951100804125</v>
+        <v>1039.615331697178</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08508054393780998</v>
+        <v>0.08550540941108634</v>
       </c>
       <c r="T23">
-        <v>0.7194369569782272</v>
+        <v>0.7272185173278751</v>
       </c>
       <c r="U23">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V23">
         <v>0.19</v>
       </c>
       <c r="W23">
-        <v>0.04753169575998017</v>
+        <v>0.04874669575998017</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.8458474023543</v>
+        <v>11.9563191279477</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07741849240784299</v>
+        <v>0.07738654899522027</v>
       </c>
       <c r="C24">
-        <v>5396.552788974021</v>
+        <v>5344.115255334473</v>
       </c>
       <c r="D24">
-        <v>5881.022788974022</v>
+        <v>5886.970255334473</v>
       </c>
       <c r="E24">
-        <v>-2669.93</v>
+        <v>-2611.545</v>
       </c>
       <c r="F24">
-        <v>1284.47</v>
+        <v>1342.855</v>
       </c>
       <c r="G24">
         <v>800</v>
@@ -3255,28 +3255,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M24">
-        <v>77.30082506521201</v>
+        <v>80.81449893181255</v>
       </c>
       <c r="N24">
-        <v>846.9325082681214</v>
+        <v>843.4188344015209</v>
       </c>
       <c r="O24">
-        <v>160.9171765709431</v>
+        <v>160.249578536289</v>
       </c>
       <c r="P24">
-        <v>686.0153316971783</v>
+        <v>683.1692558652319</v>
       </c>
       <c r="Q24">
-        <v>1039.615331697178</v>
+        <v>1036.769255865232</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08550540941108634</v>
+        <v>0.08594131035120106</v>
       </c>
       <c r="T24">
-        <v>0.7272185173278751</v>
+        <v>0.7352021961281632</v>
       </c>
       <c r="U24">
         <v>0.06018110587651872</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.9563191279477</v>
+        <v>11.43647916586302</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07738654899522027</v>
+        <v>0.07735460558259752</v>
       </c>
       <c r="C25">
-        <v>5344.115255334473</v>
+        <v>5291.689763193691</v>
       </c>
       <c r="D25">
-        <v>5886.970255334473</v>
+        <v>5892.929763193691</v>
       </c>
       <c r="E25">
-        <v>-2611.545</v>
+        <v>-2553.16</v>
       </c>
       <c r="F25">
-        <v>1342.855</v>
+        <v>1401.24</v>
       </c>
       <c r="G25">
         <v>800</v>
@@ -3337,28 +3337,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M25">
-        <v>80.81449893181255</v>
+        <v>84.32817279841309</v>
       </c>
       <c r="N25">
-        <v>843.4188344015209</v>
+        <v>839.9051605349204</v>
       </c>
       <c r="O25">
-        <v>160.249578536289</v>
+        <v>159.5819805016349</v>
       </c>
       <c r="P25">
-        <v>683.1692558652319</v>
+        <v>680.3231800332856</v>
       </c>
       <c r="Q25">
-        <v>1036.769255865232</v>
+        <v>1033.923180033285</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08594131035120106</v>
+        <v>0.08638868236868721</v>
       </c>
       <c r="T25">
-        <v>0.7352021961281632</v>
+        <v>0.7433959717389853</v>
       </c>
       <c r="U25">
         <v>0.06018110587651872</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.43647916586302</v>
+        <v>10.95995920061873</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07735460558259752</v>
+        <v>0.0773226621699748</v>
       </c>
       <c r="C26">
-        <v>5291.689763193691</v>
+        <v>5239.276349158334</v>
       </c>
       <c r="D26">
-        <v>5892.929763193691</v>
+        <v>5898.901349158334</v>
       </c>
       <c r="E26">
-        <v>-2553.16</v>
+        <v>-2494.775</v>
       </c>
       <c r="F26">
-        <v>1401.24</v>
+        <v>1459.625</v>
       </c>
       <c r="G26">
         <v>800</v>
@@ -3419,28 +3419,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M26">
-        <v>84.32817279841309</v>
+        <v>87.84184666501365</v>
       </c>
       <c r="N26">
-        <v>839.9051605349204</v>
+        <v>836.3914866683198</v>
       </c>
       <c r="O26">
-        <v>159.5819805016349</v>
+        <v>158.9143824669808</v>
       </c>
       <c r="P26">
-        <v>680.3231800332856</v>
+        <v>677.477104201339</v>
       </c>
       <c r="Q26">
-        <v>1033.923180033285</v>
+        <v>1031.077104201339</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08638868236868721</v>
+        <v>0.08684798430663966</v>
       </c>
       <c r="T26">
-        <v>0.7433959717389853</v>
+        <v>0.7518082480327625</v>
       </c>
       <c r="U26">
         <v>0.06018110587651872</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.95995920061873</v>
+        <v>10.52156083259398</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0773226621699748</v>
+        <v>0.07729071875735206</v>
       </c>
       <c r="C27">
-        <v>5239.276349158334</v>
+        <v>5186.875049983611</v>
       </c>
       <c r="D27">
-        <v>5898.901349158334</v>
+        <v>5904.885049983612</v>
       </c>
       <c r="E27">
-        <v>-2494.775</v>
+        <v>-2436.39</v>
       </c>
       <c r="F27">
-        <v>1459.625</v>
+        <v>1518.01</v>
       </c>
       <c r="G27">
         <v>800</v>
@@ -3501,28 +3501,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M27">
-        <v>87.84184666501365</v>
+        <v>91.35552053161419</v>
       </c>
       <c r="N27">
-        <v>836.3914866683198</v>
+        <v>832.8778128017193</v>
       </c>
       <c r="O27">
-        <v>158.9143824669808</v>
+        <v>158.2467844323267</v>
       </c>
       <c r="P27">
-        <v>677.477104201339</v>
+        <v>674.6310283693927</v>
       </c>
       <c r="Q27">
-        <v>1031.077104201339</v>
+        <v>1028.231028369393</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08684798430663966</v>
+        <v>0.08731969981048272</v>
       </c>
       <c r="T27">
-        <v>0.7518082480327625</v>
+        <v>0.7604478831452905</v>
       </c>
       <c r="U27">
         <v>0.06018110587651872</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.52156083259398</v>
+        <v>10.11688541595575</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07729071875735206</v>
+        <v>0.07763056534472934</v>
       </c>
       <c r="C28">
-        <v>5186.875049983611</v>
+        <v>5065.445142946661</v>
       </c>
       <c r="D28">
-        <v>5904.885049983612</v>
+        <v>5841.840142946661</v>
       </c>
       <c r="E28">
-        <v>-2436.39</v>
+        <v>-2378.005</v>
       </c>
       <c r="F28">
-        <v>1518.01</v>
+        <v>1576.395</v>
       </c>
       <c r="G28">
         <v>800</v>
@@ -3583,45 +3583,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M28">
-        <v>91.35552053161419</v>
+        <v>97.54906589821475</v>
       </c>
       <c r="N28">
-        <v>832.8778128017193</v>
+        <v>826.6842674351187</v>
       </c>
       <c r="O28">
-        <v>158.2467844323267</v>
+        <v>157.0700108126726</v>
       </c>
       <c r="P28">
-        <v>674.6310283693927</v>
+        <v>669.6142566224462</v>
       </c>
       <c r="Q28">
-        <v>1028.231028369393</v>
+        <v>1023.214256622446</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08731969981048272</v>
+        <v>0.08780433902675985</v>
       </c>
       <c r="T28">
-        <v>0.7604478831452905</v>
+        <v>0.7693242205896687</v>
       </c>
       <c r="U28">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V28">
         <v>0.19</v>
       </c>
       <c r="W28">
-        <v>0.04874669575998017</v>
+        <v>0.05012369575998017</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.11688541595575</v>
+        <v>9.474548267819424</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07763056534472934</v>
+        <v>0.07761239193210659</v>
       </c>
       <c r="C29">
-        <v>5065.445142946661</v>
+        <v>5010.397401321339</v>
       </c>
       <c r="D29">
-        <v>5841.840142946661</v>
+        <v>5845.177401321339</v>
       </c>
       <c r="E29">
-        <v>-2378.005</v>
+        <v>-2319.62</v>
       </c>
       <c r="F29">
-        <v>1576.395</v>
+        <v>1634.78</v>
       </c>
       <c r="G29">
         <v>800</v>
@@ -3665,28 +3665,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M29">
-        <v>97.54906589821475</v>
+        <v>101.1619942648153</v>
       </c>
       <c r="N29">
-        <v>826.6842674351187</v>
+        <v>823.0713390685182</v>
       </c>
       <c r="O29">
-        <v>157.0700108126726</v>
+        <v>156.3835544230185</v>
       </c>
       <c r="P29">
-        <v>669.6142566224462</v>
+        <v>666.6877846454997</v>
       </c>
       <c r="Q29">
-        <v>1023.214256622446</v>
+        <v>1020.2877846455</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08780433902675985</v>
+        <v>0.08830244044348909</v>
       </c>
       <c r="T29">
-        <v>0.7693242205896687</v>
+        <v>0.7784471229630572</v>
       </c>
       <c r="U29">
         <v>0.06188110587651872</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.474548267819424</v>
+        <v>9.136171543968732</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07761239193210659</v>
+        <v>0.07759421851948388</v>
       </c>
       <c r="C30">
-        <v>5010.397401321339</v>
+        <v>4955.353474815631</v>
       </c>
       <c r="D30">
-        <v>5845.177401321339</v>
+        <v>5848.518474815631</v>
       </c>
       <c r="E30">
-        <v>-2319.62</v>
+        <v>-2261.235</v>
       </c>
       <c r="F30">
-        <v>1634.78</v>
+        <v>1693.165</v>
       </c>
       <c r="G30">
         <v>800</v>
@@ -3747,28 +3747,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M30">
-        <v>101.1619942648153</v>
+        <v>104.7749226314158</v>
       </c>
       <c r="N30">
-        <v>823.0713390685182</v>
+        <v>819.4584107019176</v>
       </c>
       <c r="O30">
-        <v>156.3835544230185</v>
+        <v>155.6970980333643</v>
       </c>
       <c r="P30">
-        <v>666.6877846454997</v>
+        <v>663.7613126685533</v>
       </c>
       <c r="Q30">
-        <v>1020.2877846455</v>
+        <v>1017.361312668553</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08830244044348909</v>
+        <v>0.08881457288604172</v>
       </c>
       <c r="T30">
-        <v>0.7784471229630572</v>
+        <v>0.7878270085018936</v>
       </c>
       <c r="U30">
         <v>0.06188110587651872</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.136171543968732</v>
+        <v>8.821131145900845</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07759421851948388</v>
+        <v>0.07757604510686113</v>
       </c>
       <c r="C31">
-        <v>4955.353474815631</v>
+        <v>4900.313369975402</v>
       </c>
       <c r="D31">
-        <v>5848.518474815631</v>
+        <v>5851.863369975402</v>
       </c>
       <c r="E31">
-        <v>-2261.235</v>
+        <v>-2202.85</v>
       </c>
       <c r="F31">
-        <v>1693.165</v>
+        <v>1751.55</v>
       </c>
       <c r="G31">
         <v>800</v>
@@ -3829,28 +3829,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M31">
-        <v>104.7749226314158</v>
+        <v>108.3878509980164</v>
       </c>
       <c r="N31">
-        <v>819.4584107019176</v>
+        <v>815.8454823353171</v>
       </c>
       <c r="O31">
-        <v>155.6970980333643</v>
+        <v>155.0106416437102</v>
       </c>
       <c r="P31">
-        <v>663.7613126685533</v>
+        <v>660.8348406916068</v>
       </c>
       <c r="Q31">
-        <v>1017.361312668553</v>
+        <v>1014.434840691607</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08881457288604172</v>
+        <v>0.08934133768409584</v>
       </c>
       <c r="T31">
-        <v>0.7878270085018935</v>
+        <v>0.7974748907704107</v>
       </c>
       <c r="U31">
         <v>0.06188110587651872</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.821131145900846</v>
+        <v>8.527093441037483</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07757604510686113</v>
+        <v>0.0775578716942384</v>
       </c>
       <c r="C32">
-        <v>4900.313369975402</v>
+        <v>4845.277093361474</v>
       </c>
       <c r="D32">
-        <v>5851.863369975402</v>
+        <v>5855.212093361473</v>
       </c>
       <c r="E32">
-        <v>-2202.85</v>
+        <v>-2144.465</v>
       </c>
       <c r="F32">
-        <v>1751.55</v>
+        <v>1809.935</v>
       </c>
       <c r="G32">
         <v>800</v>
@@ -3911,28 +3911,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M32">
-        <v>108.3878509980164</v>
+        <v>112.0007793646169</v>
       </c>
       <c r="N32">
-        <v>815.8454823353171</v>
+        <v>812.2325539687165</v>
       </c>
       <c r="O32">
-        <v>155.0106416437102</v>
+        <v>154.3241852540561</v>
       </c>
       <c r="P32">
-        <v>660.8348406916068</v>
+        <v>657.9083687146604</v>
       </c>
       <c r="Q32">
-        <v>1014.434840691607</v>
+        <v>1011.50836871466</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08934133768409584</v>
+        <v>0.0898833710270211</v>
       </c>
       <c r="T32">
-        <v>0.7974748907704107</v>
+        <v>0.8074024218003342</v>
       </c>
       <c r="U32">
         <v>0.06188110587651872</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.527093441037483</v>
+        <v>8.252025910681436</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0775578716942384</v>
+        <v>0.07753969828161567</v>
       </c>
       <c r="C33">
-        <v>4845.277093361474</v>
+        <v>4790.244651549714</v>
       </c>
       <c r="D33">
-        <v>5855.212093361473</v>
+        <v>5858.564651549714</v>
       </c>
       <c r="E33">
-        <v>-2144.465</v>
+        <v>-2086.08</v>
       </c>
       <c r="F33">
-        <v>1809.935</v>
+        <v>1868.32</v>
       </c>
       <c r="G33">
         <v>800</v>
@@ -3993,28 +3993,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M33">
-        <v>112.0007793646169</v>
+        <v>115.6137077312175</v>
       </c>
       <c r="N33">
-        <v>812.2325539687165</v>
+        <v>808.619625602116</v>
       </c>
       <c r="O33">
-        <v>154.3241852540561</v>
+        <v>153.637728864402</v>
       </c>
       <c r="P33">
-        <v>657.9083687146604</v>
+        <v>654.9818967377139</v>
       </c>
       <c r="Q33">
-        <v>1011.50836871466</v>
+        <v>1008.581896737714</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0898833710270211</v>
+        <v>0.09044134652709121</v>
       </c>
       <c r="T33">
-        <v>0.8074024218003342</v>
+        <v>0.8176219390370202</v>
       </c>
       <c r="U33">
         <v>0.06188110587651872</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.252025910681436</v>
+        <v>7.994150100972641</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07753969828161567</v>
+        <v>0.07752152486899296</v>
       </c>
       <c r="C34">
-        <v>4790.244651549714</v>
+        <v>4735.216051131043</v>
       </c>
       <c r="D34">
-        <v>5858.564651549714</v>
+        <v>5861.921051131043</v>
       </c>
       <c r="E34">
-        <v>-2086.08</v>
+        <v>-2027.695</v>
       </c>
       <c r="F34">
-        <v>1868.32</v>
+        <v>1926.705</v>
       </c>
       <c r="G34">
         <v>800</v>
@@ -4075,28 +4075,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M34">
-        <v>115.6137077312175</v>
+        <v>119.226636097818</v>
       </c>
       <c r="N34">
-        <v>808.619625602116</v>
+        <v>805.0066972355155</v>
       </c>
       <c r="O34">
-        <v>153.637728864402</v>
+        <v>152.951272474748</v>
       </c>
       <c r="P34">
-        <v>654.9818967377139</v>
+        <v>652.0554247607676</v>
       </c>
       <c r="Q34">
-        <v>1008.581896737714</v>
+        <v>1005.655424760768</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09044134652709121</v>
+        <v>0.09101597801223806</v>
       </c>
       <c r="T34">
-        <v>0.8176219390370202</v>
+        <v>0.8281465164897266</v>
       </c>
       <c r="U34">
         <v>0.06188110587651872</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.994150100972641</v>
+        <v>7.751903128215894</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07752152486899296</v>
+        <v>0.07772367145637023</v>
       </c>
       <c r="C35">
-        <v>4735.216051131043</v>
+        <v>4639.712283711681</v>
       </c>
       <c r="D35">
-        <v>5861.921051131043</v>
+        <v>5824.802283711681</v>
       </c>
       <c r="E35">
-        <v>-2027.695</v>
+        <v>-1969.31</v>
       </c>
       <c r="F35">
-        <v>1926.705</v>
+        <v>1985.09</v>
       </c>
       <c r="G35">
         <v>800</v>
@@ -4157,45 +4157,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M35">
-        <v>119.226636097818</v>
+        <v>124.4276364644186</v>
       </c>
       <c r="N35">
-        <v>805.0066972355155</v>
+        <v>799.8056968689149</v>
       </c>
       <c r="O35">
-        <v>152.951272474748</v>
+        <v>151.9630824050938</v>
       </c>
       <c r="P35">
-        <v>652.0554247607676</v>
+        <v>647.8426144638211</v>
       </c>
       <c r="Q35">
-        <v>1005.655424760768</v>
+        <v>1001.442614463821</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09101597801223806</v>
+        <v>0.09160802257269238</v>
       </c>
       <c r="T35">
-        <v>0.8281465164897266</v>
+        <v>0.8389900205319091</v>
       </c>
       <c r="U35">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V35">
         <v>0.19</v>
       </c>
       <c r="W35">
-        <v>0.05012369575998017</v>
+        <v>0.05077169575998017</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.751903128215894</v>
+        <v>7.427878239876621</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07772367145637023</v>
+        <v>0.07771197804374749</v>
       </c>
       <c r="C36">
-        <v>4639.712283711681</v>
+        <v>4583.461648947704</v>
       </c>
       <c r="D36">
-        <v>5824.802283711681</v>
+        <v>5826.936648947704</v>
       </c>
       <c r="E36">
-        <v>-1969.31</v>
+        <v>-1910.925</v>
       </c>
       <c r="F36">
-        <v>1985.09</v>
+        <v>2043.475</v>
       </c>
       <c r="G36">
         <v>800</v>
@@ -4239,28 +4239,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M36">
-        <v>124.4276364644186</v>
+        <v>128.0872728310191</v>
       </c>
       <c r="N36">
-        <v>799.8056968689149</v>
+        <v>796.1460605023143</v>
       </c>
       <c r="O36">
-        <v>151.9630824050938</v>
+        <v>151.2677514954397</v>
       </c>
       <c r="P36">
-        <v>647.8426144638211</v>
+        <v>644.8783090068746</v>
       </c>
       <c r="Q36">
-        <v>1001.442614463821</v>
+        <v>998.4783090068746</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09160802257269238</v>
+        <v>0.09221828388885298</v>
       </c>
       <c r="T36">
-        <v>0.8389900205319091</v>
+        <v>0.8501671708523123</v>
       </c>
       <c r="U36">
         <v>0.06268110587651873</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.427878239876621</v>
+        <v>7.215653147308716</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07771197804374749</v>
+        <v>0.07770028463112476</v>
       </c>
       <c r="C37">
-        <v>4583.461648947704</v>
+        <v>4527.212578935494</v>
       </c>
       <c r="D37">
-        <v>5826.936648947704</v>
+        <v>5829.072578935495</v>
       </c>
       <c r="E37">
-        <v>-1910.925</v>
+        <v>-1852.54</v>
       </c>
       <c r="F37">
-        <v>2043.475</v>
+        <v>2101.86</v>
       </c>
       <c r="G37">
         <v>800</v>
@@ -4321,28 +4321,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M37">
-        <v>128.0872728310191</v>
+        <v>131.7469091976197</v>
       </c>
       <c r="N37">
-        <v>796.1460605023143</v>
+        <v>792.4864241357138</v>
       </c>
       <c r="O37">
-        <v>151.2677514954397</v>
+        <v>150.5724205857856</v>
       </c>
       <c r="P37">
-        <v>644.8783090068746</v>
+        <v>641.9140035499282</v>
       </c>
       <c r="Q37">
-        <v>998.4783090068746</v>
+        <v>995.5140035499282</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09221828388885298</v>
+        <v>0.0928476158711436</v>
       </c>
       <c r="T37">
-        <v>0.8501671708523123</v>
+        <v>0.8616936071202284</v>
       </c>
       <c r="U37">
         <v>0.06268110587651873</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.215653147308716</v>
+        <v>7.015218337661252</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07770028463112476</v>
+        <v>0.07768859121850204</v>
       </c>
       <c r="C38">
-        <v>4527.212578935494</v>
+        <v>4470.965075396414</v>
       </c>
       <c r="D38">
-        <v>5829.072578935495</v>
+        <v>5831.210075396414</v>
       </c>
       <c r="E38">
-        <v>-1852.54</v>
+        <v>-1794.155</v>
       </c>
       <c r="F38">
-        <v>2101.86</v>
+        <v>2160.245</v>
       </c>
       <c r="G38">
         <v>800</v>
@@ -4403,28 +4403,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M38">
-        <v>131.7469091976197</v>
+        <v>135.4065455642202</v>
       </c>
       <c r="N38">
-        <v>792.4864241357138</v>
+        <v>788.8267877691133</v>
       </c>
       <c r="O38">
-        <v>150.5724205857856</v>
+        <v>149.8770896761315</v>
       </c>
       <c r="P38">
-        <v>641.9140035499282</v>
+        <v>638.9496980929817</v>
       </c>
       <c r="Q38">
-        <v>995.5140035499282</v>
+        <v>992.5496980929818</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0928476158711436</v>
+        <v>0.09349692664652282</v>
       </c>
       <c r="T38">
-        <v>0.8616936071202282</v>
+        <v>0.8735859619998242</v>
       </c>
       <c r="U38">
         <v>0.06268110587651873</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.015218337661252</v>
+        <v>6.825617842048787</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07768859121850204</v>
+        <v>0.0776768978058793</v>
       </c>
       <c r="C39">
-        <v>4470.965075396414</v>
+        <v>4414.71914005436</v>
       </c>
       <c r="D39">
-        <v>5831.210075396414</v>
+        <v>5833.34914005436</v>
       </c>
       <c r="E39">
-        <v>-1794.155</v>
+        <v>-1735.77</v>
       </c>
       <c r="F39">
-        <v>2160.245</v>
+        <v>2218.63</v>
       </c>
       <c r="G39">
         <v>800</v>
@@ -4485,28 +4485,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M39">
-        <v>135.4065455642202</v>
+        <v>139.0661819308208</v>
       </c>
       <c r="N39">
-        <v>788.8267877691133</v>
+        <v>785.1671514025127</v>
       </c>
       <c r="O39">
-        <v>149.8770896761315</v>
+        <v>149.1817587664774</v>
       </c>
       <c r="P39">
-        <v>638.9496980929817</v>
+        <v>635.9853926360353</v>
       </c>
       <c r="Q39">
-        <v>992.5496980929818</v>
+        <v>989.5853926360353</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09349692664652282</v>
+        <v>0.09416718293078521</v>
       </c>
       <c r="T39">
-        <v>0.8735859619998242</v>
+        <v>0.8858619412303748</v>
       </c>
       <c r="U39">
         <v>0.06268110587651873</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.825617842048787</v>
+        <v>6.645996319889607</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0776768978058793</v>
+        <v>0.07766520439325657</v>
       </c>
       <c r="C40">
-        <v>4414.71914005436</v>
+        <v>4358.474774635746</v>
       </c>
       <c r="D40">
-        <v>5833.34914005436</v>
+        <v>5835.489774635746</v>
       </c>
       <c r="E40">
-        <v>-1735.77</v>
+        <v>-1677.385</v>
       </c>
       <c r="F40">
-        <v>2218.63</v>
+        <v>2277.015</v>
       </c>
       <c r="G40">
         <v>800</v>
@@ -4567,28 +4567,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M40">
-        <v>139.0661819308208</v>
+        <v>142.7258182974213</v>
       </c>
       <c r="N40">
-        <v>785.1671514025127</v>
+        <v>781.5075150359122</v>
       </c>
       <c r="O40">
-        <v>149.1817587664774</v>
+        <v>148.4864278568233</v>
       </c>
       <c r="P40">
-        <v>635.9853926360353</v>
+        <v>633.0210871790889</v>
       </c>
       <c r="Q40">
-        <v>989.5853926360353</v>
+        <v>986.6210871790889</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09416718293078521</v>
+        <v>0.09485941483092508</v>
       </c>
       <c r="T40">
-        <v>0.8858619412303748</v>
+        <v>0.8985404115832385</v>
       </c>
       <c r="U40">
         <v>0.06268110587651873</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.645996319889607</v>
+        <v>6.475586157841158</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07766520439325657</v>
+        <v>0.07765351098063385</v>
       </c>
       <c r="C41">
-        <v>4358.474774635746</v>
+        <v>4302.231980869525</v>
       </c>
       <c r="D41">
-        <v>5835.489774635746</v>
+        <v>5837.631980869524</v>
       </c>
       <c r="E41">
-        <v>-1677.385</v>
+        <v>-1619</v>
       </c>
       <c r="F41">
-        <v>2277.015</v>
+        <v>2335.4</v>
       </c>
       <c r="G41">
         <v>800</v>
@@ -4649,28 +4649,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M41">
-        <v>142.7258182974213</v>
+        <v>146.3854546640219</v>
       </c>
       <c r="N41">
-        <v>781.5075150359122</v>
+        <v>777.8478786693116</v>
       </c>
       <c r="O41">
-        <v>148.4864278568233</v>
+        <v>147.7910969471692</v>
       </c>
       <c r="P41">
-        <v>633.0210871790889</v>
+        <v>630.0567817221424</v>
       </c>
       <c r="Q41">
-        <v>986.6210871790889</v>
+        <v>983.6567817221425</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09485941483092508</v>
+        <v>0.0955747211277363</v>
       </c>
       <c r="T41">
-        <v>0.8985404115832385</v>
+        <v>0.9116414976145309</v>
       </c>
       <c r="U41">
         <v>0.06268110587651873</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.475586157841158</v>
+        <v>6.313696503895128</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07765351098063385</v>
+        <v>0.07764181756801111</v>
       </c>
       <c r="C42">
-        <v>4302.231980869525</v>
+        <v>4245.990760487199</v>
       </c>
       <c r="D42">
-        <v>5837.631980869524</v>
+        <v>5839.775760487199</v>
       </c>
       <c r="E42">
-        <v>-1619</v>
+        <v>-1560.615</v>
       </c>
       <c r="F42">
-        <v>2335.4</v>
+        <v>2393.785</v>
       </c>
       <c r="G42">
         <v>800</v>
@@ -4731,28 +4731,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M42">
-        <v>146.3854546640219</v>
+        <v>150.0450910306224</v>
       </c>
       <c r="N42">
-        <v>777.8478786693116</v>
+        <v>774.188242302711</v>
       </c>
       <c r="O42">
-        <v>147.7910969471692</v>
+        <v>147.0957660375151</v>
       </c>
       <c r="P42">
-        <v>630.0567817221424</v>
+        <v>627.092476265196</v>
       </c>
       <c r="Q42">
-        <v>983.6567817221425</v>
+        <v>980.692476265196</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0955747211277363</v>
+        <v>0.09631427509562583</v>
       </c>
       <c r="T42">
-        <v>0.9116414976145309</v>
+        <v>0.9251866882570537</v>
       </c>
       <c r="U42">
         <v>0.06268110587651873</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.313696503895128</v>
+        <v>6.159703906239148</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07764181756801111</v>
+        <v>0.07797032415538839</v>
       </c>
       <c r="C43">
-        <v>4245.990760487199</v>
+        <v>4127.973013336129</v>
       </c>
       <c r="D43">
-        <v>5839.775760487199</v>
+        <v>5780.143013336129</v>
       </c>
       <c r="E43">
-        <v>-1560.615</v>
+        <v>-1502.23</v>
       </c>
       <c r="F43">
-        <v>2393.785</v>
+        <v>2452.17</v>
       </c>
       <c r="G43">
         <v>800</v>
@@ -4813,45 +4813,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M43">
-        <v>150.0450910306224</v>
+        <v>156.156897397223</v>
       </c>
       <c r="N43">
-        <v>774.188242302711</v>
+        <v>768.0764359361106</v>
       </c>
       <c r="O43">
-        <v>147.0957660375151</v>
+        <v>145.934522827861</v>
       </c>
       <c r="P43">
-        <v>627.092476265196</v>
+        <v>622.1419131082496</v>
       </c>
       <c r="Q43">
-        <v>980.692476265196</v>
+        <v>975.7419131082496</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09631427509562583</v>
+        <v>0.0970793309244771</v>
       </c>
       <c r="T43">
-        <v>0.9251866882570537</v>
+        <v>0.9391989544389738</v>
       </c>
       <c r="U43">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.05077169575998017</v>
+        <v>0.05158169575998018</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.159703906239148</v>
+        <v>5.918619982454708</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07797032415538839</v>
+        <v>0.07796673074276565</v>
       </c>
       <c r="C44">
-        <v>4127.973013336129</v>
+        <v>4070.233725175216</v>
       </c>
       <c r="D44">
-        <v>5780.143013336129</v>
+        <v>5780.788725175216</v>
       </c>
       <c r="E44">
-        <v>-1502.23</v>
+        <v>-1443.845</v>
       </c>
       <c r="F44">
-        <v>2452.17</v>
+        <v>2510.555</v>
       </c>
       <c r="G44">
         <v>800</v>
@@ -4895,28 +4895,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M44">
-        <v>156.156897397223</v>
+        <v>159.8749187638235</v>
       </c>
       <c r="N44">
-        <v>768.0764359361106</v>
+        <v>764.3584145695099</v>
       </c>
       <c r="O44">
-        <v>145.934522827861</v>
+        <v>145.2280987682069</v>
       </c>
       <c r="P44">
-        <v>622.1419131082496</v>
+        <v>619.130315801303</v>
       </c>
       <c r="Q44">
-        <v>975.7419131082496</v>
+        <v>972.730315801303</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09707933092447708</v>
+        <v>0.09787123081749854</v>
       </c>
       <c r="T44">
-        <v>0.9391989544389737</v>
+        <v>0.9537028790834173</v>
       </c>
       <c r="U44">
         <v>0.06368110587651873</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.918619982454708</v>
+        <v>5.780977657281344</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07796673074276565</v>
+        <v>0.07796313733014293</v>
       </c>
       <c r="C45">
-        <v>4070.233725175216</v>
+        <v>4012.494581298055</v>
       </c>
       <c r="D45">
-        <v>5780.788725175216</v>
+        <v>5781.434581298055</v>
       </c>
       <c r="E45">
-        <v>-1443.845</v>
+        <v>-1385.46</v>
       </c>
       <c r="F45">
-        <v>2510.555</v>
+        <v>2568.94</v>
       </c>
       <c r="G45">
         <v>800</v>
@@ -4977,28 +4977,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M45">
-        <v>159.8749187638235</v>
+        <v>163.592940130424</v>
       </c>
       <c r="N45">
-        <v>764.3584145695099</v>
+        <v>760.6403932029094</v>
       </c>
       <c r="O45">
-        <v>145.2280987682069</v>
+        <v>144.5216747085528</v>
       </c>
       <c r="P45">
-        <v>619.130315801303</v>
+        <v>616.1187184943567</v>
       </c>
       <c r="Q45">
-        <v>972.730315801303</v>
+        <v>969.7187184943567</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09787123081749854</v>
+        <v>0.09869141284955651</v>
       </c>
       <c r="T45">
-        <v>0.9537028790834173</v>
+        <v>0.9687248010365912</v>
       </c>
       <c r="U45">
         <v>0.06368110587651873</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.780977657281344</v>
+        <v>5.64959180143404</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07796313733014293</v>
+        <v>0.07795954391752019</v>
       </c>
       <c r="C46">
-        <v>4012.494581298055</v>
+        <v>3954.755581753012</v>
       </c>
       <c r="D46">
-        <v>5781.434581298055</v>
+        <v>5782.080581753013</v>
       </c>
       <c r="E46">
-        <v>-1385.46</v>
+        <v>-1327.075</v>
       </c>
       <c r="F46">
-        <v>2568.94</v>
+        <v>2627.325</v>
       </c>
       <c r="G46">
         <v>800</v>
@@ -5059,28 +5059,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M46">
-        <v>163.592940130424</v>
+        <v>167.3109614970246</v>
       </c>
       <c r="N46">
-        <v>760.6403932029094</v>
+        <v>756.9223718363089</v>
       </c>
       <c r="O46">
-        <v>144.5216747085528</v>
+        <v>143.8152506488987</v>
       </c>
       <c r="P46">
-        <v>616.1187184943567</v>
+        <v>613.1071211874103</v>
       </c>
       <c r="Q46">
-        <v>969.7187184943567</v>
+        <v>966.7071211874103</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09869141284955651</v>
+        <v>0.0995414196827802</v>
       </c>
       <c r="T46">
-        <v>0.9687248010365912</v>
+        <v>0.9842929746971528</v>
       </c>
       <c r="U46">
         <v>0.06368110587651873</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.64959180143404</v>
+        <v>5.524045316957728</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07795954391752019</v>
+        <v>0.07795595050489747</v>
       </c>
       <c r="C47">
-        <v>3954.755581753012</v>
+        <v>3897.016726588474</v>
       </c>
       <c r="D47">
-        <v>5782.080581753013</v>
+        <v>5782.726726588474</v>
       </c>
       <c r="E47">
-        <v>-1327.075</v>
+        <v>-1268.69</v>
       </c>
       <c r="F47">
-        <v>2627.325</v>
+        <v>2685.71</v>
       </c>
       <c r="G47">
         <v>800</v>
@@ -5141,28 +5141,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M47">
-        <v>167.3109614970246</v>
+        <v>171.0289828636251</v>
       </c>
       <c r="N47">
-        <v>756.9223718363089</v>
+        <v>753.2043504697083</v>
       </c>
       <c r="O47">
-        <v>143.8152506488987</v>
+        <v>143.1088265892446</v>
       </c>
       <c r="P47">
-        <v>613.1071211874103</v>
+        <v>610.0955238804637</v>
       </c>
       <c r="Q47">
-        <v>966.7071211874103</v>
+        <v>963.6955238804637</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0995414196827802</v>
+        <v>0.1004229082505677</v>
       </c>
       <c r="T47">
-        <v>0.9842929746971528</v>
+        <v>1.00043774738218</v>
       </c>
       <c r="U47">
         <v>0.06368110587651873</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.524045316957728</v>
+        <v>5.403957375284734</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07795595050489747</v>
+        <v>0.07795235709227474</v>
       </c>
       <c r="C48">
-        <v>3897.016726588474</v>
+        <v>3839.278015852849</v>
       </c>
       <c r="D48">
-        <v>5782.726726588474</v>
+        <v>5783.373015852849</v>
       </c>
       <c r="E48">
-        <v>-1268.69</v>
+        <v>-1210.305</v>
       </c>
       <c r="F48">
-        <v>2685.71</v>
+        <v>2744.095</v>
       </c>
       <c r="G48">
         <v>800</v>
@@ -5223,28 +5223,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M48">
-        <v>171.0289828636251</v>
+        <v>174.7470042302257</v>
       </c>
       <c r="N48">
-        <v>753.2043504697083</v>
+        <v>749.4863291031078</v>
       </c>
       <c r="O48">
-        <v>143.1088265892446</v>
+        <v>142.4024025295905</v>
       </c>
       <c r="P48">
-        <v>610.0955238804637</v>
+        <v>607.0839265735173</v>
       </c>
       <c r="Q48">
-        <v>963.6955238804637</v>
+        <v>960.6839265735173</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1004229082505677</v>
+        <v>0.1013376605378944</v>
       </c>
       <c r="T48">
-        <v>1.00043774738218</v>
+        <v>1.017191756772303</v>
       </c>
       <c r="U48">
         <v>0.06368110587651873</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.403957375284734</v>
+        <v>5.288979558789314</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07795235709227474</v>
+        <v>0.07794876367965202</v>
       </c>
       <c r="C49">
-        <v>3839.278015852849</v>
+        <v>3781.539449594568</v>
       </c>
       <c r="D49">
-        <v>5783.373015852849</v>
+        <v>5784.019449594568</v>
       </c>
       <c r="E49">
-        <v>-1210.305</v>
+        <v>-1151.92</v>
       </c>
       <c r="F49">
-        <v>2744.095</v>
+        <v>2802.48</v>
       </c>
       <c r="G49">
         <v>800</v>
@@ -5305,28 +5305,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M49">
-        <v>174.7470042302257</v>
+        <v>178.4650255968262</v>
       </c>
       <c r="N49">
-        <v>749.4863291031078</v>
+        <v>745.7683077365073</v>
       </c>
       <c r="O49">
-        <v>142.4024025295905</v>
+        <v>141.6959784699364</v>
       </c>
       <c r="P49">
-        <v>607.0839265735173</v>
+        <v>604.0723292665709</v>
       </c>
       <c r="Q49">
-        <v>960.6839265735173</v>
+        <v>957.672329266571</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1013376605378944</v>
+        <v>0.1022875956055029</v>
       </c>
       <c r="T49">
-        <v>1.017191756772303</v>
+        <v>1.034590151138968</v>
       </c>
       <c r="U49">
         <v>0.06368110587651873</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.288979558789314</v>
+        <v>5.178792484647871</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07794876367965201</v>
+        <v>0.07794517026702927</v>
       </c>
       <c r="C50">
-        <v>3781.539449594571</v>
+        <v>3723.80102786209</v>
       </c>
       <c r="D50">
-        <v>5784.019449594571</v>
+        <v>5784.666027862089</v>
       </c>
       <c r="E50">
-        <v>-1151.92</v>
+        <v>-1093.535</v>
       </c>
       <c r="F50">
-        <v>2802.48</v>
+        <v>2860.865</v>
       </c>
       <c r="G50">
         <v>800</v>
@@ -5387,28 +5387,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M50">
-        <v>178.4650255968262</v>
+        <v>182.1830469634268</v>
       </c>
       <c r="N50">
-        <v>745.7683077365073</v>
+        <v>742.0502863699066</v>
       </c>
       <c r="O50">
-        <v>141.6959784699364</v>
+        <v>140.9895544102823</v>
       </c>
       <c r="P50">
-        <v>604.0723292665709</v>
+        <v>601.0607319596244</v>
       </c>
       <c r="Q50">
-        <v>957.672329266571</v>
+        <v>954.6607319596244</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1022875956055029</v>
+        <v>0.1032747830287039</v>
       </c>
       <c r="T50">
-        <v>1.034590151138968</v>
+        <v>1.052670835480797</v>
       </c>
       <c r="U50">
         <v>0.06368110587651873</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.178792484647871</v>
+        <v>5.073102842104036</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07794517026702927</v>
+        <v>0.07794157685440654</v>
       </c>
       <c r="C51">
-        <v>3723.80102786209</v>
+        <v>3666.062750703874</v>
       </c>
       <c r="D51">
-        <v>5784.666027862089</v>
+        <v>5785.312750703874</v>
       </c>
       <c r="E51">
-        <v>-1093.535</v>
+        <v>-1035.15</v>
       </c>
       <c r="F51">
-        <v>2860.865</v>
+        <v>2919.25</v>
       </c>
       <c r="G51">
         <v>800</v>
@@ -5469,28 +5469,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M51">
-        <v>182.1830469634268</v>
+        <v>185.9010683300273</v>
       </c>
       <c r="N51">
-        <v>742.0502863699066</v>
+        <v>738.3322650033061</v>
       </c>
       <c r="O51">
-        <v>140.9895544102823</v>
+        <v>140.2831303506282</v>
       </c>
       <c r="P51">
-        <v>601.0607319596244</v>
+        <v>598.0491346526779</v>
       </c>
       <c r="Q51">
-        <v>954.6607319596244</v>
+        <v>951.649134652678</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1032747830287039</v>
+        <v>0.1043014579488329</v>
       </c>
       <c r="T51">
-        <v>1.052670835480797</v>
+        <v>1.071474747196299</v>
       </c>
       <c r="U51">
         <v>0.06368110587651873</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.073102842104036</v>
+        <v>4.971640785261956</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07794157685440654</v>
+        <v>0.07793798344178382</v>
       </c>
       <c r="C52">
-        <v>3666.062750703874</v>
+        <v>3608.324618168425</v>
       </c>
       <c r="D52">
-        <v>5785.312750703874</v>
+        <v>5785.959618168426</v>
       </c>
       <c r="E52">
-        <v>-1035.15</v>
+        <v>-976.7649999999999</v>
       </c>
       <c r="F52">
-        <v>2919.25</v>
+        <v>2977.635</v>
       </c>
       <c r="G52">
         <v>800</v>
@@ -5551,28 +5551,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M52">
-        <v>185.9010683300273</v>
+        <v>189.6190896966279</v>
       </c>
       <c r="N52">
-        <v>738.3322650033061</v>
+        <v>734.6142436367056</v>
       </c>
       <c r="O52">
-        <v>140.2831303506282</v>
+        <v>139.5767062909741</v>
       </c>
       <c r="P52">
-        <v>598.0491346526779</v>
+        <v>595.0375373457316</v>
       </c>
       <c r="Q52">
-        <v>951.649134652678</v>
+        <v>948.6375373457316</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1043014579488329</v>
+        <v>0.1053700379677427</v>
       </c>
       <c r="T52">
-        <v>1.071474747196299</v>
+        <v>1.091046165512434</v>
       </c>
       <c r="U52">
         <v>0.06368110587651873</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.971640785261956</v>
+        <v>4.87415763260976</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07793798344178382</v>
+        <v>0.07793439002916108</v>
       </c>
       <c r="C53">
-        <v>3608.324618168425</v>
+        <v>3550.586630304264</v>
       </c>
       <c r="D53">
-        <v>5785.959618168426</v>
+        <v>5786.606630304263</v>
       </c>
       <c r="E53">
-        <v>-976.7649999999999</v>
+        <v>-918.3800000000001</v>
       </c>
       <c r="F53">
-        <v>2977.635</v>
+        <v>3036.02</v>
       </c>
       <c r="G53">
         <v>800</v>
@@ -5633,28 +5633,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M53">
-        <v>189.6190896966279</v>
+        <v>193.3371110632284</v>
       </c>
       <c r="N53">
-        <v>734.6142436367056</v>
+        <v>730.896222270105</v>
       </c>
       <c r="O53">
-        <v>139.5767062909741</v>
+        <v>138.8702822313199</v>
       </c>
       <c r="P53">
-        <v>595.0375373457316</v>
+        <v>592.0259400387851</v>
       </c>
       <c r="Q53">
-        <v>948.6375373457316</v>
+        <v>945.6259400387851</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1053700379677427</v>
+        <v>0.1064831421541071</v>
       </c>
       <c r="T53">
-        <v>1.091046165512434</v>
+        <v>1.111433059591741</v>
       </c>
       <c r="U53">
         <v>0.06368110587651873</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.87415763260976</v>
+        <v>4.780423831982649</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07793439002916108</v>
+        <v>0.07793079661653836</v>
       </c>
       <c r="C54">
-        <v>3550.586630304264</v>
+        <v>3492.848787159919</v>
       </c>
       <c r="D54">
-        <v>5786.606630304263</v>
+        <v>5787.253787159919</v>
       </c>
       <c r="E54">
-        <v>-918.3800000000001</v>
+        <v>-859.9949999999999</v>
       </c>
       <c r="F54">
-        <v>3036.02</v>
+        <v>3094.405</v>
       </c>
       <c r="G54">
         <v>800</v>
@@ -5715,28 +5715,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M54">
-        <v>193.3371110632284</v>
+        <v>197.055132429829</v>
       </c>
       <c r="N54">
-        <v>730.896222270105</v>
+        <v>727.1782009035045</v>
       </c>
       <c r="O54">
-        <v>138.8702822313199</v>
+        <v>138.1638581716659</v>
       </c>
       <c r="P54">
-        <v>592.0259400387851</v>
+        <v>589.0143427318386</v>
       </c>
       <c r="Q54">
-        <v>945.6259400387851</v>
+        <v>942.6143427318386</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1064831421541071</v>
+        <v>0.1076436124760614</v>
       </c>
       <c r="T54">
-        <v>1.111433059591741</v>
+        <v>1.132687481078679</v>
       </c>
       <c r="U54">
         <v>0.06368110587651873</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.780423831982649</v>
+        <v>4.690227155907505</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07793079661653836</v>
+        <v>0.07792720320391562</v>
       </c>
       <c r="C55">
-        <v>3492.848787159919</v>
+        <v>3435.111088783959</v>
       </c>
       <c r="D55">
-        <v>5787.253787159919</v>
+        <v>5787.901088783959</v>
       </c>
       <c r="E55">
-        <v>-859.9949999999999</v>
+        <v>-801.6099999999997</v>
       </c>
       <c r="F55">
-        <v>3094.405</v>
+        <v>3152.79</v>
       </c>
       <c r="G55">
         <v>800</v>
@@ -5797,28 +5797,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M55">
-        <v>197.055132429829</v>
+        <v>200.7731537964295</v>
       </c>
       <c r="N55">
-        <v>727.1782009035045</v>
+        <v>723.460179536904</v>
       </c>
       <c r="O55">
-        <v>138.1638581716659</v>
+        <v>137.4574341120118</v>
       </c>
       <c r="P55">
-        <v>589.0143427318386</v>
+        <v>586.0027454248923</v>
       </c>
       <c r="Q55">
-        <v>942.6143427318386</v>
+        <v>939.6027454248923</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1076436124760614</v>
+        <v>0.1088545380294051</v>
       </c>
       <c r="T55">
-        <v>1.132687481078679</v>
+        <v>1.154866007847657</v>
       </c>
       <c r="U55">
         <v>0.06368110587651873</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.690227155907505</v>
+        <v>4.603371097464773</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07792720320391562</v>
+        <v>0.0779236097912929</v>
       </c>
       <c r="C56">
-        <v>3435.111088783959</v>
+        <v>3377.373535224961</v>
       </c>
       <c r="D56">
-        <v>5787.901088783959</v>
+        <v>5788.548535224961</v>
       </c>
       <c r="E56">
-        <v>-801.6099999999997</v>
+        <v>-743.2249999999999</v>
       </c>
       <c r="F56">
-        <v>3152.79</v>
+        <v>3211.175</v>
       </c>
       <c r="G56">
         <v>800</v>
@@ -5879,28 +5879,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M56">
-        <v>200.7731537964295</v>
+        <v>204.4911751630301</v>
       </c>
       <c r="N56">
-        <v>723.460179536904</v>
+        <v>719.7421581703034</v>
       </c>
       <c r="O56">
-        <v>137.4574341120118</v>
+        <v>136.7510100523576</v>
       </c>
       <c r="P56">
-        <v>586.0027454248923</v>
+        <v>582.9911481179457</v>
       </c>
       <c r="Q56">
-        <v>939.6027454248923</v>
+        <v>936.5911481179457</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1088545380294051</v>
+        <v>0.1101192824962307</v>
       </c>
       <c r="T56">
-        <v>1.154866007847657</v>
+        <v>1.178030246917478</v>
       </c>
       <c r="U56">
         <v>0.06368110587651873</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.603371097464773</v>
+        <v>4.519673441147232</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0779236097912929</v>
+        <v>0.07905401637867016</v>
       </c>
       <c r="C57">
-        <v>3377.373535224961</v>
+        <v>3122.217915969226</v>
       </c>
       <c r="D57">
-        <v>5788.548535224961</v>
+        <v>5591.777915969226</v>
       </c>
       <c r="E57">
-        <v>-743.2249999999999</v>
+        <v>-684.8399999999997</v>
       </c>
       <c r="F57">
-        <v>3211.175</v>
+        <v>3269.56</v>
       </c>
       <c r="G57">
         <v>800</v>
@@ -5961,45 +5961,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M57">
-        <v>204.4911751630301</v>
+        <v>216.3830965296306</v>
       </c>
       <c r="N57">
-        <v>719.7421581703034</v>
+        <v>707.8502368037028</v>
       </c>
       <c r="O57">
-        <v>136.7510100523576</v>
+        <v>134.4915449927036</v>
       </c>
       <c r="P57">
-        <v>582.9911481179457</v>
+        <v>573.3586918109993</v>
       </c>
       <c r="Q57">
-        <v>936.5911481179457</v>
+        <v>926.9586918109993</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1101192824962307</v>
+        <v>0.111441515347912</v>
       </c>
       <c r="T57">
-        <v>1.178030246917478</v>
+        <v>1.202247405945019</v>
       </c>
       <c r="U57">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V57">
         <v>0.19</v>
       </c>
       <c r="W57">
-        <v>0.05158169575998018</v>
+        <v>0.05360669575998017</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.519673441147232</v>
+        <v>4.271282499216721</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07905401637867016</v>
+        <v>0.07907067296604743</v>
       </c>
       <c r="C58">
-        <v>3122.217915969226</v>
+        <v>3061.033455388831</v>
       </c>
       <c r="D58">
-        <v>5591.777915969226</v>
+        <v>5588.978455388831</v>
       </c>
       <c r="E58">
-        <v>-684.8399999999997</v>
+        <v>-626.4549999999999</v>
       </c>
       <c r="F58">
-        <v>3269.56</v>
+        <v>3327.945</v>
       </c>
       <c r="G58">
         <v>800</v>
@@ -6043,28 +6043,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M58">
-        <v>216.3830965296306</v>
+        <v>220.2470803962311</v>
       </c>
       <c r="N58">
-        <v>707.8502368037028</v>
+        <v>703.9862529371023</v>
       </c>
       <c r="O58">
-        <v>134.4915449927036</v>
+        <v>133.7573880580495</v>
       </c>
       <c r="P58">
-        <v>573.3586918109993</v>
+        <v>570.2288648790529</v>
       </c>
       <c r="Q58">
-        <v>926.9586918109993</v>
+        <v>923.828864879053</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.111441515347912</v>
+        <v>0.1128252474019971</v>
       </c>
       <c r="T58">
-        <v>1.202247405945019</v>
+        <v>1.227590944462213</v>
       </c>
       <c r="U58">
         <v>0.06618110587651872</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.271282499216721</v>
+        <v>4.196347718528709</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07907067296604743</v>
+        <v>0.07908732955342471</v>
       </c>
       <c r="C59">
-        <v>3061.033455388831</v>
+        <v>2999.851796442595</v>
       </c>
       <c r="D59">
-        <v>5588.978455388831</v>
+        <v>5586.181796442595</v>
       </c>
       <c r="E59">
-        <v>-626.4549999999999</v>
+        <v>-568.0699999999997</v>
       </c>
       <c r="F59">
-        <v>3327.945</v>
+        <v>3386.33</v>
       </c>
       <c r="G59">
         <v>800</v>
@@ -6125,28 +6125,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M59">
-        <v>220.2470803962311</v>
+        <v>224.1110642628317</v>
       </c>
       <c r="N59">
-        <v>703.9862529371023</v>
+        <v>700.1222690705018</v>
       </c>
       <c r="O59">
-        <v>133.7573880580495</v>
+        <v>133.0232311233954</v>
       </c>
       <c r="P59">
-        <v>570.2288648790529</v>
+        <v>567.0990379471065</v>
       </c>
       <c r="Q59">
-        <v>923.828864879053</v>
+        <v>920.6990379471065</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1128252474019971</v>
+        <v>0.1142748714586576</v>
       </c>
       <c r="T59">
-        <v>1.227590944462213</v>
+        <v>1.254141318146892</v>
       </c>
       <c r="U59">
         <v>0.06618110587651872</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.196347718528709</v>
+        <v>4.123996895795456</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07908732955342471</v>
+        <v>0.07910398614080197</v>
       </c>
       <c r="C60">
-        <v>2999.851796442596</v>
+        <v>2938.672934926909</v>
       </c>
       <c r="D60">
-        <v>5586.181796442595</v>
+        <v>5583.387934926909</v>
       </c>
       <c r="E60">
-        <v>-568.0700000000002</v>
+        <v>-509.6850000000004</v>
       </c>
       <c r="F60">
-        <v>3386.33</v>
+        <v>3444.715</v>
       </c>
       <c r="G60">
         <v>800</v>
@@ -6207,28 +6207,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M60">
-        <v>224.1110642628316</v>
+        <v>227.9750481294322</v>
       </c>
       <c r="N60">
-        <v>700.1222690705018</v>
+        <v>696.2582852039013</v>
       </c>
       <c r="O60">
-        <v>133.0232311233954</v>
+        <v>132.2890741887412</v>
       </c>
       <c r="P60">
-        <v>567.0990379471065</v>
+        <v>563.9692110151601</v>
       </c>
       <c r="Q60">
-        <v>920.6990379471065</v>
+        <v>917.5692110151601</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1142748714586576</v>
+        <v>0.1157952088839358</v>
       </c>
       <c r="T60">
-        <v>1.254141318146892</v>
+        <v>1.281986832011311</v>
       </c>
       <c r="U60">
         <v>0.06618110587651872</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.123996895795456</v>
+        <v>4.054098643324346</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07910398614080197</v>
+        <v>0.08082164272817924</v>
       </c>
       <c r="C61">
-        <v>2938.672934926909</v>
+        <v>2606.447466027564</v>
       </c>
       <c r="D61">
-        <v>5583.387934926909</v>
+        <v>5309.547466027564</v>
       </c>
       <c r="E61">
-        <v>-509.6850000000004</v>
+        <v>-451.3000000000002</v>
       </c>
       <c r="F61">
-        <v>3444.715</v>
+        <v>3503.1</v>
       </c>
       <c r="G61">
         <v>800</v>
@@ -6289,45 +6289,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M61">
-        <v>227.9750481294322</v>
+        <v>244.0998819960327</v>
       </c>
       <c r="N61">
-        <v>696.2582852039013</v>
+        <v>680.1334513373007</v>
       </c>
       <c r="O61">
-        <v>132.2890741887412</v>
+        <v>129.2253557540871</v>
       </c>
       <c r="P61">
-        <v>563.9692110151601</v>
+        <v>550.9080955832136</v>
       </c>
       <c r="Q61">
-        <v>917.5692110151601</v>
+        <v>904.5080955832136</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1157952088839358</v>
+        <v>0.1173915631804778</v>
       </c>
       <c r="T61">
-        <v>1.281986832011311</v>
+        <v>1.311224621568952</v>
       </c>
       <c r="U61">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V61">
         <v>0.19</v>
       </c>
       <c r="W61">
-        <v>0.05360669575998017</v>
+        <v>0.05644169575998017</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.054098643324346</v>
+        <v>3.786291602338237</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08082164272817924</v>
+        <v>0.08086664931555651</v>
       </c>
       <c r="C62">
-        <v>2606.447466027564</v>
+        <v>2541.247882466609</v>
       </c>
       <c r="D62">
-        <v>5309.547466027564</v>
+        <v>5302.732882466609</v>
       </c>
       <c r="E62">
-        <v>-451.3000000000002</v>
+        <v>-392.915</v>
       </c>
       <c r="F62">
-        <v>3503.1</v>
+        <v>3561.485</v>
       </c>
       <c r="G62">
         <v>800</v>
@@ -6371,28 +6371,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M62">
-        <v>244.0998819960327</v>
+        <v>248.1682133626333</v>
       </c>
       <c r="N62">
-        <v>680.1334513373007</v>
+        <v>676.0651199707002</v>
       </c>
       <c r="O62">
-        <v>129.2253557540871</v>
+        <v>128.452372794433</v>
       </c>
       <c r="P62">
-        <v>550.9080955832136</v>
+        <v>547.6127471762671</v>
       </c>
       <c r="Q62">
-        <v>904.5080955832136</v>
+        <v>901.2127471762672</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1173915631804778</v>
+        <v>0.1190697817999195</v>
       </c>
       <c r="T62">
-        <v>1.311224621568952</v>
+        <v>1.341961784950061</v>
       </c>
       <c r="U62">
         <v>0.06968110587651873</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.786291602338237</v>
+        <v>3.724221248201545</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08086664931555651</v>
+        <v>0.08091165590293378</v>
       </c>
       <c r="C63">
-        <v>2541.247882466609</v>
+        <v>2476.065768953284</v>
       </c>
       <c r="D63">
-        <v>5302.732882466609</v>
+        <v>5295.935768953284</v>
       </c>
       <c r="E63">
-        <v>-392.915</v>
+        <v>-334.5300000000002</v>
       </c>
       <c r="F63">
-        <v>3561.485</v>
+        <v>3619.87</v>
       </c>
       <c r="G63">
         <v>800</v>
@@ -6453,28 +6453,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M63">
-        <v>248.1682133626333</v>
+        <v>252.2365447292338</v>
       </c>
       <c r="N63">
-        <v>676.0651199707002</v>
+        <v>671.9967886040996</v>
       </c>
       <c r="O63">
-        <v>128.452372794433</v>
+        <v>127.6793898347789</v>
       </c>
       <c r="P63">
-        <v>547.6127471762671</v>
+        <v>544.3173987693207</v>
       </c>
       <c r="Q63">
-        <v>901.2127471762672</v>
+        <v>897.9173987693207</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1190697817999195</v>
+        <v>0.1208363277151213</v>
       </c>
       <c r="T63">
-        <v>1.341961784950061</v>
+        <v>1.374316693772282</v>
       </c>
       <c r="U63">
         <v>0.06968110587651873</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.724221248201545</v>
+        <v>3.664153163553133</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08091165590293378</v>
+        <v>0.08095666249031104</v>
       </c>
       <c r="C64">
-        <v>2476.065768953284</v>
+        <v>2410.901058393573</v>
       </c>
       <c r="D64">
-        <v>5295.935768953284</v>
+        <v>5289.156058393573</v>
       </c>
       <c r="E64">
-        <v>-334.5300000000002</v>
+        <v>-276.145</v>
       </c>
       <c r="F64">
-        <v>3619.87</v>
+        <v>3678.255</v>
       </c>
       <c r="G64">
         <v>800</v>
@@ -6535,28 +6535,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M64">
-        <v>252.2365447292338</v>
+        <v>256.3048760958344</v>
       </c>
       <c r="N64">
-        <v>671.9967886040996</v>
+        <v>667.9284572374991</v>
       </c>
       <c r="O64">
-        <v>127.6793898347789</v>
+        <v>126.9064068751248</v>
       </c>
       <c r="P64">
-        <v>544.3173987693207</v>
+        <v>541.0220503623742</v>
       </c>
       <c r="Q64">
-        <v>897.9173987693207</v>
+        <v>894.6220503623742</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1208363277151213</v>
+        <v>0.1226983625987123</v>
       </c>
       <c r="T64">
-        <v>1.374316693772282</v>
+        <v>1.408420516584892</v>
       </c>
       <c r="U64">
         <v>0.06968110587651873</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.664153163553133</v>
+        <v>3.605992002226893</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08095666249031104</v>
+        <v>0.08100166907768833</v>
       </c>
       <c r="C65">
-        <v>2410.901058393573</v>
+        <v>2345.753684036583</v>
       </c>
       <c r="D65">
-        <v>5289.156058393573</v>
+        <v>5282.393684036583</v>
       </c>
       <c r="E65">
-        <v>-276.145</v>
+        <v>-217.7600000000002</v>
       </c>
       <c r="F65">
-        <v>3678.255</v>
+        <v>3736.64</v>
       </c>
       <c r="G65">
         <v>800</v>
@@ -6617,28 +6617,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M65">
-        <v>256.3048760958344</v>
+        <v>260.3732074624349</v>
       </c>
       <c r="N65">
-        <v>667.9284572374991</v>
+        <v>663.8601258708985</v>
       </c>
       <c r="O65">
-        <v>126.9064068751248</v>
+        <v>126.1334239154707</v>
       </c>
       <c r="P65">
-        <v>541.0220503623742</v>
+        <v>537.7267019554278</v>
       </c>
       <c r="Q65">
-        <v>894.6220503623742</v>
+        <v>891.3267019554278</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1226983625987123</v>
+        <v>0.124663843864725</v>
       </c>
       <c r="T65">
-        <v>1.408420516584892</v>
+        <v>1.444418996220426</v>
       </c>
       <c r="U65">
         <v>0.06968110587651873</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.605992002226893</v>
+        <v>3.549648377192097</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08100166907768833</v>
+        <v>0.08252087566506558</v>
       </c>
       <c r="C66">
-        <v>2345.753684036583</v>
+        <v>2068.826856355088</v>
       </c>
       <c r="D66">
-        <v>5282.393684036583</v>
+        <v>5063.851856355088</v>
       </c>
       <c r="E66">
-        <v>-217.7600000000002</v>
+        <v>-159.375</v>
       </c>
       <c r="F66">
-        <v>3736.64</v>
+        <v>3795.025</v>
       </c>
       <c r="G66">
         <v>800</v>
@@ -6699,45 +6699,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M66">
-        <v>260.3732074624349</v>
+        <v>275.0676088290355</v>
       </c>
       <c r="N66">
-        <v>663.8601258708985</v>
+        <v>649.1657245042979</v>
       </c>
       <c r="O66">
-        <v>126.1334239154707</v>
+        <v>123.3414876558166</v>
       </c>
       <c r="P66">
-        <v>537.7267019554278</v>
+        <v>525.8242368484813</v>
       </c>
       <c r="Q66">
-        <v>891.3267019554278</v>
+        <v>879.4242368484813</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.124663843864725</v>
+        <v>0.1267416383459385</v>
       </c>
       <c r="T66">
-        <v>1.444418996220426</v>
+        <v>1.482474531835132</v>
       </c>
       <c r="U66">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V66">
         <v>0.19</v>
       </c>
       <c r="W66">
-        <v>0.05644169575998017</v>
+        <v>0.05870969575998017</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.549648377192097</v>
+        <v>3.360022422370269</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08252087566506558</v>
+        <v>0.08258856225244285</v>
       </c>
       <c r="C67">
-        <v>2068.826856355088</v>
+        <v>2001.124970068835</v>
       </c>
       <c r="D67">
-        <v>5063.851856355088</v>
+        <v>5054.534970068836</v>
       </c>
       <c r="E67">
-        <v>-159.375</v>
+        <v>-100.9899999999998</v>
       </c>
       <c r="F67">
-        <v>3795.025</v>
+        <v>3853.41</v>
       </c>
       <c r="G67">
         <v>800</v>
@@ -6781,28 +6781,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M67">
-        <v>275.0676088290355</v>
+        <v>279.299418195636</v>
       </c>
       <c r="N67">
-        <v>649.1657245042979</v>
+        <v>644.9339151376975</v>
       </c>
       <c r="O67">
-        <v>123.3414876558166</v>
+        <v>122.5374438761625</v>
       </c>
       <c r="P67">
-        <v>525.8242368484813</v>
+        <v>522.396471261535</v>
       </c>
       <c r="Q67">
-        <v>879.4242368484813</v>
+        <v>875.996471261535</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1267416383459385</v>
+        <v>0.1289416560319293</v>
       </c>
       <c r="T67">
-        <v>1.482474531835132</v>
+        <v>1.522768628368351</v>
       </c>
       <c r="U67">
         <v>0.07248110587651872</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.360022422370269</v>
+        <v>3.309112991728296</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08258856225244285</v>
+        <v>0.08265624883982012</v>
       </c>
       <c r="C68">
-        <v>2001.124970068835</v>
+        <v>1933.457304749586</v>
       </c>
       <c r="D68">
-        <v>5054.534970068836</v>
+        <v>5045.252304749586</v>
       </c>
       <c r="E68">
-        <v>-100.9899999999998</v>
+        <v>-42.60500000000002</v>
       </c>
       <c r="F68">
-        <v>3853.41</v>
+        <v>3911.795</v>
       </c>
       <c r="G68">
         <v>800</v>
@@ -6863,28 +6863,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M68">
-        <v>279.299418195636</v>
+        <v>283.5312275622366</v>
       </c>
       <c r="N68">
-        <v>644.9339151376975</v>
+        <v>640.702105771097</v>
       </c>
       <c r="O68">
-        <v>122.5374438761625</v>
+        <v>121.7334000965084</v>
       </c>
       <c r="P68">
-        <v>522.396471261535</v>
+        <v>518.9687056745886</v>
       </c>
       <c r="Q68">
-        <v>875.996471261535</v>
+        <v>872.5687056745886</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1289416560319293</v>
+        <v>0.1312750081231316</v>
       </c>
       <c r="T68">
-        <v>1.522768628368351</v>
+        <v>1.565504791358129</v>
       </c>
       <c r="U68">
         <v>0.07248110587651872</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.309112991728296</v>
+        <v>3.259723245583098</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08265624883982012</v>
+        <v>0.0827239354271974</v>
       </c>
       <c r="C69">
-        <v>1933.457304749586</v>
+        <v>1865.8236722023</v>
       </c>
       <c r="D69">
-        <v>5045.252304749586</v>
+        <v>5036.003672202301</v>
       </c>
       <c r="E69">
-        <v>-42.60500000000002</v>
+        <v>15.7800000000002</v>
       </c>
       <c r="F69">
-        <v>3911.795</v>
+        <v>3970.18</v>
       </c>
       <c r="G69">
         <v>800</v>
@@ -6945,28 +6945,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M69">
-        <v>283.5312275622366</v>
+        <v>287.7630369288371</v>
       </c>
       <c r="N69">
-        <v>640.702105771097</v>
+        <v>636.4702964044964</v>
       </c>
       <c r="O69">
-        <v>121.7334000965084</v>
+        <v>120.9293563168543</v>
       </c>
       <c r="P69">
-        <v>518.9687056745886</v>
+        <v>515.5409400876421</v>
       </c>
       <c r="Q69">
-        <v>872.5687056745886</v>
+        <v>869.1409400876421</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1312750081231316</v>
+        <v>0.133754194720034</v>
       </c>
       <c r="T69">
-        <v>1.565504791358129</v>
+        <v>1.610911964534768</v>
       </c>
       <c r="U69">
         <v>0.07248110587651872</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.259723245583098</v>
+        <v>3.211786139030405</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0827239354271974</v>
+        <v>0.08279162201457467</v>
       </c>
       <c r="C70">
-        <v>1865.8236722023</v>
+        <v>1798.223885609366</v>
       </c>
       <c r="D70">
-        <v>5036.003672202301</v>
+        <v>5026.788885609367</v>
       </c>
       <c r="E70">
-        <v>15.7800000000002</v>
+        <v>74.16500000000042</v>
       </c>
       <c r="F70">
-        <v>3970.18</v>
+        <v>4028.565000000001</v>
       </c>
       <c r="G70">
         <v>800</v>
@@ -7027,28 +7027,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M70">
-        <v>287.7630369288371</v>
+        <v>291.9948462954377</v>
       </c>
       <c r="N70">
-        <v>636.4702964044964</v>
+        <v>632.2384870378958</v>
       </c>
       <c r="O70">
-        <v>120.9293563168543</v>
+        <v>120.1253125372002</v>
       </c>
       <c r="P70">
-        <v>515.5409400876421</v>
+        <v>512.1131745006955</v>
       </c>
       <c r="Q70">
-        <v>869.1409400876421</v>
+        <v>865.7131745006956</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.133754194720034</v>
+        <v>0.1363933288393173</v>
       </c>
       <c r="T70">
-        <v>1.610911964534768</v>
+        <v>1.659248632755061</v>
       </c>
       <c r="U70">
         <v>0.07248110587651872</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.211786139030405</v>
+        <v>3.165238513827065</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08279162201457467</v>
+        <v>0.08285930860195193</v>
       </c>
       <c r="C71">
-        <v>1798.223885609366</v>
+        <v>1730.657759518016</v>
       </c>
       <c r="D71">
-        <v>5026.788885609367</v>
+        <v>5017.607759518016</v>
       </c>
       <c r="E71">
-        <v>74.16500000000042</v>
+        <v>132.5500000000002</v>
       </c>
       <c r="F71">
-        <v>4028.565000000001</v>
+        <v>4086.95</v>
       </c>
       <c r="G71">
         <v>800</v>
@@ -7109,28 +7109,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M71">
-        <v>291.9948462954377</v>
+        <v>296.2266556620382</v>
       </c>
       <c r="N71">
-        <v>632.2384870378958</v>
+        <v>628.0066776712952</v>
       </c>
       <c r="O71">
-        <v>120.1253125372002</v>
+        <v>119.3212687575461</v>
       </c>
       <c r="P71">
-        <v>512.1131745006955</v>
+        <v>508.6854089137491</v>
       </c>
       <c r="Q71">
-        <v>865.7131745006956</v>
+        <v>862.2854089137491</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1363933288393173</v>
+        <v>0.1392084052332194</v>
       </c>
       <c r="T71">
-        <v>1.659248632755061</v>
+        <v>1.710807745523373</v>
       </c>
       <c r="U71">
         <v>0.07248110587651872</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.165238513827065</v>
+        <v>3.120020820772393</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08285930860195193</v>
+        <v>0.08292699518932922</v>
       </c>
       <c r="C72">
-        <v>1730.657759518016</v>
+        <v>1663.125109827872</v>
       </c>
       <c r="D72">
-        <v>5017.607759518016</v>
+        <v>5008.460109827872</v>
       </c>
       <c r="E72">
-        <v>132.5500000000002</v>
+        <v>190.9349999999999</v>
       </c>
       <c r="F72">
-        <v>4086.95</v>
+        <v>4145.335</v>
       </c>
       <c r="G72">
         <v>800</v>
@@ -7191,28 +7191,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M72">
-        <v>296.2266556620382</v>
+        <v>300.4584650286387</v>
       </c>
       <c r="N72">
-        <v>628.0066776712952</v>
+        <v>623.7748683046948</v>
       </c>
       <c r="O72">
-        <v>119.3212687575461</v>
+        <v>118.517224977892</v>
       </c>
       <c r="P72">
-        <v>508.6854089137491</v>
+        <v>505.2576433268028</v>
       </c>
       <c r="Q72">
-        <v>862.2854089137491</v>
+        <v>858.8576433268029</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1392084052332194</v>
+        <v>0.142217624826701</v>
       </c>
       <c r="T72">
-        <v>1.710807745523373</v>
+        <v>1.765922659172259</v>
       </c>
       <c r="U72">
         <v>0.07248110587651872</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.120020820772393</v>
+        <v>3.076076865550247</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08292699518932921</v>
+        <v>0.08299468177670648</v>
       </c>
       <c r="C73">
-        <v>1663.125109827874</v>
+        <v>1595.625753778678</v>
       </c>
       <c r="D73">
-        <v>5008.460109827874</v>
+        <v>4999.345753778678</v>
       </c>
       <c r="E73">
-        <v>190.9349999999999</v>
+        <v>249.3200000000002</v>
       </c>
       <c r="F73">
-        <v>4145.335</v>
+        <v>4203.72</v>
       </c>
       <c r="G73">
         <v>800</v>
@@ -7273,28 +7273,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M73">
-        <v>300.4584650286387</v>
+        <v>304.6902743952393</v>
       </c>
       <c r="N73">
-        <v>623.7748683046948</v>
+        <v>619.5430589380942</v>
       </c>
       <c r="O73">
-        <v>118.517224977892</v>
+        <v>117.7131811982379</v>
       </c>
       <c r="P73">
-        <v>505.2576433268028</v>
+        <v>501.8298777398563</v>
       </c>
       <c r="Q73">
-        <v>858.8576433268029</v>
+        <v>855.4298777398564</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.142217624826701</v>
+        <v>0.1454417886768598</v>
       </c>
       <c r="T73">
-        <v>1.765922659172259</v>
+        <v>1.824974352367493</v>
       </c>
       <c r="U73">
         <v>0.07248110587651872</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.076076865550247</v>
+        <v>3.033353575750938</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08299468177670648</v>
+        <v>0.08767450836408376</v>
       </c>
       <c r="C74">
-        <v>1595.625753778678</v>
+        <v>978.5220465736948</v>
       </c>
       <c r="D74">
-        <v>4999.345753778678</v>
+        <v>4440.627046573694</v>
       </c>
       <c r="E74">
-        <v>249.3200000000002</v>
+        <v>307.7049999999995</v>
       </c>
       <c r="F74">
-        <v>4203.72</v>
+        <v>4262.105</v>
       </c>
       <c r="G74">
         <v>800</v>
@@ -7355,45 +7355,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M74">
-        <v>304.6902743952393</v>
+        <v>342.1665027618399</v>
       </c>
       <c r="N74">
-        <v>619.5430589380942</v>
+        <v>582.0668305714936</v>
       </c>
       <c r="O74">
-        <v>117.7131811982379</v>
+        <v>110.5926978085838</v>
       </c>
       <c r="P74">
-        <v>501.8298777398563</v>
+        <v>471.4741327629098</v>
       </c>
       <c r="Q74">
-        <v>855.4298777398564</v>
+        <v>825.0741327629098</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1454417886768598</v>
+        <v>0.1489047794788823</v>
       </c>
       <c r="T74">
-        <v>1.824974352367493</v>
+        <v>1.888400245058671</v>
       </c>
       <c r="U74">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V74">
         <v>0.19</v>
       </c>
       <c r="W74">
-        <v>0.05870969575998017</v>
+        <v>0.06502769575998019</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.033353575750938</v>
+        <v>2.701121605631376</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08767450836408376</v>
+        <v>0.08780537495146103</v>
       </c>
       <c r="C75">
-        <v>978.5220465736948</v>
+        <v>906.3023954588834</v>
       </c>
       <c r="D75">
-        <v>4440.627046573694</v>
+        <v>4426.792395458883</v>
       </c>
       <c r="E75">
-        <v>307.7049999999995</v>
+        <v>366.0899999999997</v>
       </c>
       <c r="F75">
-        <v>4262.105</v>
+        <v>4320.49</v>
       </c>
       <c r="G75">
         <v>800</v>
@@ -7437,28 +7437,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M75">
-        <v>342.1665027618399</v>
+        <v>346.8537151284404</v>
       </c>
       <c r="N75">
-        <v>582.0668305714936</v>
+        <v>577.3796182048931</v>
       </c>
       <c r="O75">
-        <v>110.5926978085838</v>
+        <v>109.7021274589297</v>
       </c>
       <c r="P75">
-        <v>471.4741327629098</v>
+        <v>467.6774907459634</v>
       </c>
       <c r="Q75">
-        <v>825.0741327629098</v>
+        <v>821.2774907459634</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1489047794788823</v>
+        <v>0.1526341541887526</v>
       </c>
       <c r="T75">
-        <v>1.888400245058671</v>
+        <v>1.956705052572247</v>
       </c>
       <c r="U75">
         <v>0.08028110587651874</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.701121605631376</v>
+        <v>2.664619962312033</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08780537495146103</v>
+        <v>0.08793624153883831</v>
       </c>
       <c r="C76">
-        <v>906.3023954588834</v>
+        <v>834.1686795633887</v>
       </c>
       <c r="D76">
-        <v>4426.792395458883</v>
+        <v>4413.043679563389</v>
       </c>
       <c r="E76">
-        <v>366.0899999999997</v>
+        <v>424.4749999999999</v>
       </c>
       <c r="F76">
-        <v>4320.49</v>
+        <v>4378.875</v>
       </c>
       <c r="G76">
         <v>800</v>
@@ -7519,28 +7519,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M76">
-        <v>346.8537151284404</v>
+        <v>351.540927495041</v>
       </c>
       <c r="N76">
-        <v>577.3796182048931</v>
+        <v>572.6924058382924</v>
       </c>
       <c r="O76">
-        <v>109.7021274589297</v>
+        <v>108.8115571092756</v>
       </c>
       <c r="P76">
-        <v>467.6774907459634</v>
+        <v>463.8808487290169</v>
       </c>
       <c r="Q76">
-        <v>821.2774907459634</v>
+        <v>817.4808487290169</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1526341541887526</v>
+        <v>0.1566618788754126</v>
       </c>
       <c r="T76">
-        <v>1.956705052572247</v>
+        <v>2.03047424468691</v>
       </c>
       <c r="U76">
         <v>0.08028110587651874</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.664619962312033</v>
+        <v>2.629091696147872</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08793624153883831</v>
+        <v>0.08806710812621557</v>
       </c>
       <c r="C77">
-        <v>834.1686795633887</v>
+        <v>762.1201006744168</v>
       </c>
       <c r="D77">
-        <v>4413.043679563389</v>
+        <v>4399.380100674417</v>
       </c>
       <c r="E77">
-        <v>424.4749999999999</v>
+        <v>482.8600000000001</v>
       </c>
       <c r="F77">
-        <v>4378.875</v>
+        <v>4437.26</v>
       </c>
       <c r="G77">
         <v>800</v>
@@ -7601,28 +7601,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M77">
-        <v>351.540927495041</v>
+        <v>356.2281398616416</v>
       </c>
       <c r="N77">
-        <v>572.6924058382924</v>
+        <v>568.0051934716919</v>
       </c>
       <c r="O77">
-        <v>108.8115571092756</v>
+        <v>107.9209867596215</v>
       </c>
       <c r="P77">
-        <v>463.8808487290169</v>
+        <v>460.0842067120705</v>
       </c>
       <c r="Q77">
-        <v>817.4808487290169</v>
+        <v>813.6842067120705</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1566618788754126</v>
+        <v>0.161025247285961</v>
       </c>
       <c r="T77">
-        <v>2.03047424468691</v>
+        <v>2.110390869477794</v>
       </c>
       <c r="U77">
         <v>0.08028110587651874</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.629091696147872</v>
+        <v>2.594498384356452</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08806710812621557</v>
+        <v>0.08819797471359284</v>
       </c>
       <c r="C78">
-        <v>762.1201006744168</v>
+        <v>690.1558704342951</v>
       </c>
       <c r="D78">
-        <v>4399.380100674417</v>
+        <v>4385.800870434296</v>
       </c>
       <c r="E78">
-        <v>482.8600000000001</v>
+        <v>541.2450000000003</v>
       </c>
       <c r="F78">
-        <v>4437.26</v>
+        <v>4495.645</v>
       </c>
       <c r="G78">
         <v>800</v>
@@ -7683,28 +7683,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M78">
-        <v>356.2281398616416</v>
+        <v>360.9153522282421</v>
       </c>
       <c r="N78">
-        <v>568.0051934716919</v>
+        <v>563.3179811050913</v>
       </c>
       <c r="O78">
-        <v>107.9209867596215</v>
+        <v>107.0304164099674</v>
       </c>
       <c r="P78">
-        <v>460.0842067120705</v>
+        <v>456.287564695124</v>
       </c>
       <c r="Q78">
-        <v>813.6842067120705</v>
+        <v>809.887564695124</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.161025247285961</v>
+        <v>0.165768039036557</v>
       </c>
       <c r="T78">
-        <v>2.110390869477794</v>
+        <v>2.197256765989625</v>
       </c>
       <c r="U78">
         <v>0.08028110587651874</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.594498384356452</v>
+        <v>2.560803600144031</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08819797471359284</v>
+        <v>0.08832884130097012</v>
       </c>
       <c r="C79">
-        <v>690.1558704342951</v>
+        <v>618.2752101888582</v>
       </c>
       <c r="D79">
-        <v>4385.800870434296</v>
+        <v>4372.305210188858</v>
       </c>
       <c r="E79">
-        <v>541.2450000000003</v>
+        <v>599.6299999999997</v>
       </c>
       <c r="F79">
-        <v>4495.645</v>
+        <v>4554.03</v>
       </c>
       <c r="G79">
         <v>800</v>
@@ -7765,28 +7765,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M79">
-        <v>360.9153522282421</v>
+        <v>365.6025645948426</v>
       </c>
       <c r="N79">
-        <v>563.3179811050913</v>
+        <v>558.6307687384908</v>
       </c>
       <c r="O79">
-        <v>107.0304164099674</v>
+        <v>106.1398460603133</v>
       </c>
       <c r="P79">
-        <v>456.287564695124</v>
+        <v>452.4909226781775</v>
       </c>
       <c r="Q79">
-        <v>809.887564695124</v>
+        <v>806.0909226781775</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.165768039036557</v>
+        <v>0.1709419936735708</v>
       </c>
       <c r="T79">
-        <v>2.197256765989625</v>
+        <v>2.29201956218435</v>
       </c>
       <c r="U79">
         <v>0.08028110587651874</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.560803600144031</v>
+        <v>2.527972784757569</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08832884130097012</v>
+        <v>0.09095531788834738</v>
       </c>
       <c r="C80">
-        <v>618.2752101888582</v>
+        <v>305.5733809767644</v>
       </c>
       <c r="D80">
-        <v>4372.305210188858</v>
+        <v>4117.988380976764</v>
       </c>
       <c r="E80">
-        <v>599.6299999999997</v>
+        <v>658.0149999999999</v>
       </c>
       <c r="F80">
-        <v>4554.03</v>
+        <v>4612.415</v>
       </c>
       <c r="G80">
         <v>800</v>
@@ -7847,45 +7847,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M80">
-        <v>365.6025645948426</v>
+        <v>388.2781954614431</v>
       </c>
       <c r="N80">
-        <v>558.6307687384908</v>
+        <v>535.9551378718904</v>
       </c>
       <c r="O80">
-        <v>106.1398460603133</v>
+        <v>101.8314761956592</v>
       </c>
       <c r="P80">
-        <v>452.4909226781775</v>
+        <v>434.1236616762312</v>
       </c>
       <c r="Q80">
-        <v>806.0909226781775</v>
+        <v>787.7236616762312</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1709419936735708</v>
+        <v>0.1766087058950621</v>
       </c>
       <c r="T80">
-        <v>2.29201956218435</v>
+        <v>2.395807386588095</v>
       </c>
       <c r="U80">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V80">
         <v>0.19</v>
       </c>
       <c r="W80">
-        <v>0.06502769575998019</v>
+        <v>0.06818669575998017</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.527972784757569</v>
+        <v>2.38033797451578</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09095531788834738</v>
+        <v>0.09111777447572464</v>
       </c>
       <c r="C81">
-        <v>305.5733809767644</v>
+        <v>232.4260863369182</v>
       </c>
       <c r="D81">
-        <v>4117.988380976764</v>
+        <v>4103.226086336918</v>
       </c>
       <c r="E81">
-        <v>658.0149999999999</v>
+        <v>716.4000000000001</v>
       </c>
       <c r="F81">
-        <v>4612.415</v>
+        <v>4670.8</v>
       </c>
       <c r="G81">
         <v>800</v>
@@ -7929,28 +7929,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M81">
-        <v>388.2781954614431</v>
+        <v>393.1931093280436</v>
       </c>
       <c r="N81">
-        <v>535.9551378718904</v>
+        <v>531.0402240052898</v>
       </c>
       <c r="O81">
-        <v>101.8314761956592</v>
+        <v>100.8976425610051</v>
       </c>
       <c r="P81">
-        <v>434.1236616762312</v>
+        <v>430.1425814442848</v>
       </c>
       <c r="Q81">
-        <v>787.7236616762312</v>
+        <v>783.7425814442847</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1766087058950621</v>
+        <v>0.1828420893387026</v>
       </c>
       <c r="T81">
-        <v>2.395807386588095</v>
+        <v>2.509973993432216</v>
       </c>
       <c r="U81">
         <v>0.08418110587651872</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.38033797451578</v>
+        <v>2.350583749834333</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09111777447572464</v>
+        <v>0.0912802310631019</v>
       </c>
       <c r="C82">
-        <v>232.4260863369182</v>
+        <v>159.3842543103001</v>
       </c>
       <c r="D82">
-        <v>4103.226086336918</v>
+        <v>4088.5692543103</v>
       </c>
       <c r="E82">
-        <v>716.4000000000001</v>
+        <v>774.7850000000003</v>
       </c>
       <c r="F82">
-        <v>4670.8</v>
+        <v>4729.185</v>
       </c>
       <c r="G82">
         <v>800</v>
@@ -8011,28 +8011,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M82">
-        <v>393.1931093280436</v>
+        <v>398.1080231946443</v>
       </c>
       <c r="N82">
-        <v>531.0402240052898</v>
+        <v>526.1253101386892</v>
       </c>
       <c r="O82">
-        <v>100.8976425610051</v>
+        <v>99.96380892635095</v>
       </c>
       <c r="P82">
-        <v>430.1425814442848</v>
+        <v>426.1615012123382</v>
       </c>
       <c r="Q82">
-        <v>783.7425814442847</v>
+        <v>779.7615012123383</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1828420893387026</v>
+        <v>0.1897316184079894</v>
       </c>
       <c r="T82">
-        <v>2.509973993432216</v>
+        <v>2.636158137838875</v>
       </c>
       <c r="U82">
         <v>0.08418110587651872</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.350583749834333</v>
+        <v>2.321564197367241</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0912802310631019</v>
+        <v>0.09144268765047918</v>
       </c>
       <c r="C83">
-        <v>159.3842543103001</v>
+        <v>86.44675877372447</v>
       </c>
       <c r="D83">
-        <v>4088.5692543103</v>
+        <v>4074.016758773725</v>
       </c>
       <c r="E83">
-        <v>774.7850000000003</v>
+        <v>833.1700000000005</v>
       </c>
       <c r="F83">
-        <v>4729.185</v>
+        <v>4787.570000000001</v>
       </c>
       <c r="G83">
         <v>800</v>
@@ -8093,28 +8093,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M83">
-        <v>398.1080231946443</v>
+        <v>403.0229370612448</v>
       </c>
       <c r="N83">
-        <v>526.1253101386892</v>
+        <v>521.2103962720887</v>
       </c>
       <c r="O83">
-        <v>99.96380892635095</v>
+        <v>99.02997529169686</v>
       </c>
       <c r="P83">
-        <v>426.1615012123382</v>
+        <v>422.1804209803918</v>
       </c>
       <c r="Q83">
-        <v>779.7615012123383</v>
+        <v>775.7804209803919</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1897316184079894</v>
+        <v>0.1973866507071969</v>
       </c>
       <c r="T83">
-        <v>2.636158137838875</v>
+        <v>2.776362742735163</v>
       </c>
       <c r="U83">
         <v>0.08418110587651872</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.321564197367241</v>
+        <v>2.293252438862763</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09144268765047918</v>
+        <v>0.09160514423785646</v>
       </c>
       <c r="C84">
-        <v>86.44675877372447</v>
+        <v>13.61248958004217</v>
       </c>
       <c r="D84">
-        <v>4074.016758773725</v>
+        <v>4059.567489580043</v>
       </c>
       <c r="E84">
-        <v>833.1700000000005</v>
+        <v>891.5550000000007</v>
       </c>
       <c r="F84">
-        <v>4787.570000000001</v>
+        <v>4845.955000000001</v>
       </c>
       <c r="G84">
         <v>800</v>
@@ -8175,28 +8175,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M84">
-        <v>403.0229370612448</v>
+        <v>407.9378509278454</v>
       </c>
       <c r="N84">
-        <v>521.2103962720887</v>
+        <v>516.2954824054881</v>
       </c>
       <c r="O84">
-        <v>99.02997529169686</v>
+        <v>98.09614165704274</v>
       </c>
       <c r="P84">
-        <v>422.1804209803918</v>
+        <v>418.1993407484454</v>
       </c>
       <c r="Q84">
-        <v>775.7804209803919</v>
+        <v>771.7993407484454</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1973866507071969</v>
+        <v>0.2059422750416054</v>
       </c>
       <c r="T84">
-        <v>2.776362742735163</v>
+        <v>2.933062007031015</v>
       </c>
       <c r="U84">
         <v>0.08418110587651872</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.293252438862763</v>
+        <v>2.265622891406585</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09160514423785646</v>
+        <v>0.09176760082523372</v>
       </c>
       <c r="C85">
-        <v>13.61248958004217</v>
+        <v>-59.11964772416923</v>
       </c>
       <c r="D85">
-        <v>4059.567489580043</v>
+        <v>4045.220352275831</v>
       </c>
       <c r="E85">
-        <v>891.5550000000007</v>
+        <v>949.9400000000001</v>
       </c>
       <c r="F85">
-        <v>4845.955000000001</v>
+        <v>4904.34</v>
       </c>
       <c r="G85">
         <v>800</v>
@@ -8257,28 +8257,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M85">
-        <v>407.9378509278454</v>
+        <v>412.8527647944459</v>
       </c>
       <c r="N85">
-        <v>516.2954824054881</v>
+        <v>511.3805685388876</v>
       </c>
       <c r="O85">
-        <v>98.09614165704274</v>
+        <v>97.16230802238864</v>
       </c>
       <c r="P85">
-        <v>418.1993407484454</v>
+        <v>414.218260516499</v>
       </c>
       <c r="Q85">
-        <v>771.7993407484454</v>
+        <v>767.818260516499</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2059422750416054</v>
+        <v>0.2155673524178149</v>
       </c>
       <c r="T85">
-        <v>2.933062007031015</v>
+        <v>3.109348679363849</v>
       </c>
       <c r="U85">
         <v>0.08418110587651872</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.265622891406585</v>
+        <v>2.238651190318412</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09176760082523372</v>
+        <v>0.09193005741261098</v>
       </c>
       <c r="C86">
-        <v>-59.11964772416923</v>
+        <v>-131.7507321749572</v>
       </c>
       <c r="D86">
-        <v>4045.220352275831</v>
+        <v>4030.974267825042</v>
       </c>
       <c r="E86">
-        <v>949.9400000000001</v>
+        <v>1008.324999999999</v>
       </c>
       <c r="F86">
-        <v>4904.34</v>
+        <v>4962.724999999999</v>
       </c>
       <c r="G86">
         <v>800</v>
@@ -8339,28 +8339,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M86">
-        <v>412.8527647944459</v>
+        <v>417.7676786610463</v>
       </c>
       <c r="N86">
-        <v>511.3805685388876</v>
+        <v>506.4656546722871</v>
       </c>
       <c r="O86">
-        <v>97.16230802238864</v>
+        <v>96.22847438773456</v>
       </c>
       <c r="P86">
-        <v>414.218260516499</v>
+        <v>410.2371802845526</v>
       </c>
       <c r="Q86">
-        <v>767.818260516499</v>
+        <v>763.8371802845526</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2155673524178148</v>
+        <v>0.2264757734441856</v>
       </c>
       <c r="T86">
-        <v>3.109348679363846</v>
+        <v>3.309140241341057</v>
       </c>
       <c r="U86">
         <v>0.08418110587651872</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.238651190318412</v>
+        <v>2.212314117491137</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09193005741261098</v>
+        <v>0.09209251399998826</v>
       </c>
       <c r="C87">
-        <v>-131.7507321749572</v>
+        <v>-204.2818276615117</v>
       </c>
       <c r="D87">
-        <v>4030.974267825042</v>
+        <v>4016.828172338488</v>
       </c>
       <c r="E87">
-        <v>1008.324999999999</v>
+        <v>1066.71</v>
       </c>
       <c r="F87">
-        <v>4962.724999999999</v>
+        <v>5021.11</v>
       </c>
       <c r="G87">
         <v>800</v>
@@ -8421,28 +8421,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M87">
-        <v>417.7676786610463</v>
+        <v>422.6825925276469</v>
       </c>
       <c r="N87">
-        <v>506.4656546722871</v>
+        <v>501.5507408056865</v>
       </c>
       <c r="O87">
-        <v>96.22847438773456</v>
+        <v>95.29464075308044</v>
       </c>
       <c r="P87">
-        <v>410.2371802845526</v>
+        <v>406.2561000526061</v>
       </c>
       <c r="Q87">
-        <v>763.8371802845526</v>
+        <v>759.8561000526061</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2264757734441856</v>
+        <v>0.2389425403314665</v>
       </c>
       <c r="T87">
-        <v>3.309140241341057</v>
+        <v>3.537473455029298</v>
       </c>
       <c r="U87">
         <v>0.08418110587651872</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.212314117491137</v>
+        <v>2.186589534729611</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09209251399998826</v>
+        <v>0.09225497058736552</v>
       </c>
       <c r="C88">
-        <v>-204.2818276615117</v>
+        <v>-276.713983191009</v>
       </c>
       <c r="D88">
-        <v>4016.828172338488</v>
+        <v>4002.78101680899</v>
       </c>
       <c r="E88">
-        <v>1066.71</v>
+        <v>1125.095</v>
       </c>
       <c r="F88">
-        <v>5021.11</v>
+        <v>5079.495</v>
       </c>
       <c r="G88">
         <v>800</v>
@@ -8503,28 +8503,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M88">
-        <v>422.6825925276469</v>
+        <v>427.5975063942475</v>
       </c>
       <c r="N88">
-        <v>501.5507408056865</v>
+        <v>496.635826939086</v>
       </c>
       <c r="O88">
-        <v>95.29464075308044</v>
+        <v>94.36080711842634</v>
       </c>
       <c r="P88">
-        <v>406.2561000526061</v>
+        <v>402.2750198206596</v>
       </c>
       <c r="Q88">
-        <v>759.8561000526061</v>
+        <v>755.8750198206596</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2389425403314665</v>
+        <v>0.2533272713552521</v>
       </c>
       <c r="T88">
-        <v>3.537473455029298</v>
+        <v>3.800934855438806</v>
       </c>
       <c r="U88">
         <v>0.08418110587651872</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.186589534729611</v>
+        <v>2.161456321686742</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09225497058736552</v>
+        <v>0.0924174271747428</v>
       </c>
       <c r="C89">
-        <v>-276.713983191009</v>
+        <v>-349.048233147937</v>
       </c>
       <c r="D89">
-        <v>4002.78101680899</v>
+        <v>3988.831766852064</v>
       </c>
       <c r="E89">
-        <v>1125.095</v>
+        <v>1183.48</v>
       </c>
       <c r="F89">
-        <v>5079.495</v>
+        <v>5137.88</v>
       </c>
       <c r="G89">
         <v>800</v>
@@ -8585,28 +8585,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M89">
-        <v>427.5975063942475</v>
+        <v>432.512420260848</v>
       </c>
       <c r="N89">
-        <v>496.635826939086</v>
+        <v>491.7209130724854</v>
       </c>
       <c r="O89">
-        <v>94.36080711842634</v>
+        <v>93.42697348377223</v>
       </c>
       <c r="P89">
-        <v>402.2750198206596</v>
+        <v>398.2939395887132</v>
       </c>
       <c r="Q89">
-        <v>755.8750198206596</v>
+        <v>751.8939395887132</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2533272713552521</v>
+        <v>0.2701094575496688</v>
       </c>
       <c r="T89">
-        <v>3.800934855438806</v>
+        <v>4.1083064892499</v>
       </c>
       <c r="U89">
         <v>0.08418110587651872</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.161456321686742</v>
+        <v>2.136894318031211</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0924174271747428</v>
+        <v>0.09257988376212006</v>
       </c>
       <c r="C90">
-        <v>-349.048233147937</v>
+        <v>-421.2855975479861</v>
       </c>
       <c r="D90">
-        <v>3988.831766852064</v>
+        <v>3974.979402452015</v>
       </c>
       <c r="E90">
-        <v>1183.48</v>
+        <v>1241.865</v>
       </c>
       <c r="F90">
-        <v>5137.88</v>
+        <v>5196.265</v>
       </c>
       <c r="G90">
         <v>800</v>
@@ -8667,28 +8667,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M90">
-        <v>432.512420260848</v>
+        <v>437.4273341274486</v>
       </c>
       <c r="N90">
-        <v>491.7209130724854</v>
+        <v>486.8059992058849</v>
       </c>
       <c r="O90">
-        <v>93.42697348377223</v>
+        <v>92.49313984911812</v>
       </c>
       <c r="P90">
-        <v>398.2939395887132</v>
+        <v>394.3128593567668</v>
       </c>
       <c r="Q90">
-        <v>751.8939395887132</v>
+        <v>747.9128593567668</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2701094575496688</v>
+        <v>0.2899429503248883</v>
       </c>
       <c r="T90">
-        <v>4.1083064892499</v>
+        <v>4.471563874663009</v>
       </c>
       <c r="U90">
         <v>0.08418110587651872</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.136894318031211</v>
+        <v>2.112884269514006</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09257988376212006</v>
+        <v>0.09274234034949733</v>
       </c>
       <c r="C91">
-        <v>-421.2855975479861</v>
+        <v>-493.4270822866974</v>
       </c>
       <c r="D91">
-        <v>3974.979402452015</v>
+        <v>3961.222917713303</v>
       </c>
       <c r="E91">
-        <v>1241.865</v>
+        <v>1300.25</v>
       </c>
       <c r="F91">
-        <v>5196.265</v>
+        <v>5254.650000000001</v>
       </c>
       <c r="G91">
         <v>800</v>
@@ -8749,28 +8749,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M91">
-        <v>437.4273341274486</v>
+        <v>442.3422479940492</v>
       </c>
       <c r="N91">
-        <v>486.8059992058849</v>
+        <v>481.8910853392843</v>
       </c>
       <c r="O91">
-        <v>92.49313984911812</v>
+        <v>91.55930621446402</v>
       </c>
       <c r="P91">
-        <v>394.3128593567668</v>
+        <v>390.3317791248203</v>
       </c>
       <c r="Q91">
-        <v>747.9128593567668</v>
+        <v>743.9317791248203</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2899429503248883</v>
+        <v>0.3137431416551519</v>
       </c>
       <c r="T91">
-        <v>4.471563874663009</v>
+        <v>4.907472737158742</v>
       </c>
       <c r="U91">
         <v>0.08418110587651872</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.112884269514006</v>
+        <v>2.089407777630517</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09274234034949733</v>
+        <v>0.09290479693687462</v>
       </c>
       <c r="C92">
-        <v>-493.4270822866974</v>
+        <v>-565.4736793829506</v>
       </c>
       <c r="D92">
-        <v>3961.222917713303</v>
+        <v>3947.56132061705</v>
       </c>
       <c r="E92">
-        <v>1300.25</v>
+        <v>1358.635</v>
       </c>
       <c r="F92">
-        <v>5254.650000000001</v>
+        <v>5313.035</v>
       </c>
       <c r="G92">
         <v>800</v>
@@ -8831,28 +8831,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M92">
-        <v>442.3422479940492</v>
+        <v>447.2571618606497</v>
       </c>
       <c r="N92">
-        <v>481.8910853392843</v>
+        <v>476.9761714726838</v>
       </c>
       <c r="O92">
-        <v>91.55930621446402</v>
+        <v>90.62547257980992</v>
       </c>
       <c r="P92">
-        <v>390.3317791248203</v>
+        <v>386.3506988928739</v>
       </c>
       <c r="Q92">
-        <v>743.9317791248203</v>
+        <v>739.9506988928739</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3137431416551519</v>
+        <v>0.3428322643921407</v>
       </c>
       <c r="T92">
-        <v>4.907472737158742</v>
+        <v>5.440250235764638</v>
       </c>
       <c r="U92">
         <v>0.08418110587651872</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.089407777630517</v>
+        <v>2.066447252601611</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09290479693687462</v>
+        <v>0.09306725352425188</v>
       </c>
       <c r="C93">
-        <v>-565.4736793829506</v>
+        <v>-637.4263672174229</v>
       </c>
       <c r="D93">
-        <v>3947.56132061705</v>
+        <v>3933.993632782577</v>
       </c>
       <c r="E93">
-        <v>1358.635</v>
+        <v>1417.02</v>
       </c>
       <c r="F93">
-        <v>5313.035</v>
+        <v>5371.42</v>
       </c>
       <c r="G93">
         <v>800</v>
@@ -8913,28 +8913,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M93">
-        <v>447.2571618606497</v>
+        <v>452.1720757272502</v>
       </c>
       <c r="N93">
-        <v>476.9761714726838</v>
+        <v>472.0612576060832</v>
       </c>
       <c r="O93">
-        <v>90.62547257980992</v>
+        <v>89.69163894515582</v>
       </c>
       <c r="P93">
-        <v>386.3506988928739</v>
+        <v>382.3696186609274</v>
       </c>
       <c r="Q93">
-        <v>739.9506988928739</v>
+        <v>735.9696186609274</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3428322643921407</v>
+        <v>0.3791936678133767</v>
       </c>
       <c r="T93">
-        <v>5.440250235764638</v>
+        <v>6.106222109022008</v>
       </c>
       <c r="U93">
         <v>0.08418110587651872</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.066447252601611</v>
+        <v>2.043985869421158</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09306725352425188</v>
+        <v>0.09322971011162914</v>
       </c>
       <c r="C94">
-        <v>-637.4263672174229</v>
+        <v>-709.2861107661729</v>
       </c>
       <c r="D94">
-        <v>3933.993632782577</v>
+        <v>3920.518889233827</v>
       </c>
       <c r="E94">
-        <v>1417.02</v>
+        <v>1475.405</v>
       </c>
       <c r="F94">
-        <v>5371.42</v>
+        <v>5429.805</v>
       </c>
       <c r="G94">
         <v>800</v>
@@ -8995,28 +8995,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M94">
-        <v>452.1720757272502</v>
+        <v>457.0869895938508</v>
       </c>
       <c r="N94">
-        <v>472.0612576060832</v>
+        <v>467.1463437394827</v>
       </c>
       <c r="O94">
-        <v>89.69163894515582</v>
+        <v>88.75780531050171</v>
       </c>
       <c r="P94">
-        <v>382.3696186609274</v>
+        <v>378.388538428981</v>
       </c>
       <c r="Q94">
-        <v>735.9696186609274</v>
+        <v>731.988538428981</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3791936678133767</v>
+        <v>0.4259440436406801</v>
       </c>
       <c r="T94">
-        <v>6.106222109022008</v>
+        <v>6.962471660352911</v>
       </c>
       <c r="U94">
         <v>0.08418110587651872</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.043985869421158</v>
+        <v>2.022007526739211</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09322971011162914</v>
+        <v>0.09339216669900641</v>
       </c>
       <c r="C95">
-        <v>-709.2861107661729</v>
+        <v>-781.053861829414</v>
       </c>
       <c r="D95">
-        <v>3920.518889233827</v>
+        <v>3907.136138170587</v>
       </c>
       <c r="E95">
-        <v>1475.405</v>
+        <v>1533.79</v>
       </c>
       <c r="F95">
-        <v>5429.805</v>
+        <v>5488.190000000001</v>
       </c>
       <c r="G95">
         <v>800</v>
@@ -9077,28 +9077,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M95">
-        <v>457.0869895938508</v>
+        <v>462.0019034604513</v>
       </c>
       <c r="N95">
-        <v>467.1463437394827</v>
+        <v>462.2314298728821</v>
       </c>
       <c r="O95">
-        <v>88.75780531050171</v>
+        <v>87.8239716758476</v>
       </c>
       <c r="P95">
-        <v>378.388538428981</v>
+        <v>374.4074581970345</v>
       </c>
       <c r="Q95">
-        <v>731.988538428981</v>
+        <v>728.0074581970346</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4259440436406801</v>
+        <v>0.4882778780770847</v>
       </c>
       <c r="T95">
-        <v>6.962471660352911</v>
+        <v>8.104137728794118</v>
       </c>
       <c r="U95">
         <v>0.08418110587651872</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.022007526739211</v>
+        <v>2.000496808369644</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09339216669900641</v>
+        <v>0.1044815232863837</v>
       </c>
       <c r="C96">
-        <v>-781.053861829414</v>
+        <v>-1577.790960498527</v>
       </c>
       <c r="D96">
-        <v>3907.136138170587</v>
+        <v>3168.784039501474</v>
       </c>
       <c r="E96">
-        <v>1533.79</v>
+        <v>1592.175000000001</v>
       </c>
       <c r="F96">
-        <v>5488.190000000001</v>
+        <v>5546.575000000001</v>
       </c>
       <c r="G96">
         <v>800</v>
@@ -9159,45 +9159,45 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M96">
-        <v>462.0019034604513</v>
+        <v>545.6781823270519</v>
       </c>
       <c r="N96">
-        <v>462.2314298728821</v>
+        <v>378.5551510062816</v>
       </c>
       <c r="O96">
-        <v>87.8239716758476</v>
+        <v>71.9254786911935</v>
       </c>
       <c r="P96">
-        <v>374.4074581970345</v>
+        <v>306.629672315088</v>
       </c>
       <c r="Q96">
-        <v>728.0074581970346</v>
+        <v>660.229672315088</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4882778780770847</v>
+        <v>0.5755452462880511</v>
       </c>
       <c r="T96">
-        <v>8.104137728794118</v>
+        <v>9.702470224611806</v>
       </c>
       <c r="U96">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V96">
         <v>0.19</v>
       </c>
       <c r="W96">
-        <v>0.06818669575998017</v>
+        <v>0.07968869575998018</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.000496808369644</v>
+        <v>1.69373334552598</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1044815232863837</v>
+        <v>0.104758999873761</v>
       </c>
       <c r="C97">
-        <v>-1577.790960498527</v>
+        <v>-1651.089093070297</v>
       </c>
       <c r="D97">
-        <v>3168.784039501474</v>
+        <v>3153.870906929703</v>
       </c>
       <c r="E97">
-        <v>1592.175000000001</v>
+        <v>1650.56</v>
       </c>
       <c r="F97">
-        <v>5546.575000000001</v>
+        <v>5604.96</v>
       </c>
       <c r="G97">
         <v>800</v>
@@ -9241,28 +9241,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M97">
-        <v>545.6781823270519</v>
+        <v>551.4221631936524</v>
       </c>
       <c r="N97">
-        <v>378.5551510062816</v>
+        <v>372.8111701396811</v>
       </c>
       <c r="O97">
-        <v>71.9254786911935</v>
+        <v>70.8341223265394</v>
       </c>
       <c r="P97">
-        <v>306.629672315088</v>
+        <v>301.9770478131417</v>
       </c>
       <c r="Q97">
-        <v>660.229672315088</v>
+        <v>655.5770478131417</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5755452462880511</v>
+        <v>0.706446298604501</v>
       </c>
       <c r="T97">
-        <v>9.702470224611806</v>
+        <v>12.09996896833834</v>
       </c>
       <c r="U97">
         <v>0.09838110587651873</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.69373334552598</v>
+        <v>1.676090289843418</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.104758999873761</v>
+        <v>0.1050364764611382</v>
       </c>
       <c r="C98">
-        <v>-1651.089093070298</v>
+        <v>-1724.247512904907</v>
       </c>
       <c r="D98">
-        <v>3153.870906929702</v>
+        <v>3139.097487095094</v>
       </c>
       <c r="E98">
-        <v>1650.56</v>
+        <v>1708.945</v>
       </c>
       <c r="F98">
-        <v>5604.96</v>
+        <v>5663.345</v>
       </c>
       <c r="G98">
         <v>800</v>
@@ -9323,28 +9323,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M98">
-        <v>551.4221631936524</v>
+        <v>557.166144060253</v>
       </c>
       <c r="N98">
-        <v>372.8111701396811</v>
+        <v>367.0671892730804</v>
       </c>
       <c r="O98">
-        <v>70.8341223265394</v>
+        <v>69.74276596188528</v>
       </c>
       <c r="P98">
-        <v>301.9770478131417</v>
+        <v>297.3244233111951</v>
       </c>
       <c r="Q98">
-        <v>655.5770478131417</v>
+        <v>650.9244233111951</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7064462986044993</v>
+        <v>0.9246147191319147</v>
       </c>
       <c r="T98">
-        <v>12.09996896833831</v>
+        <v>16.09580020788252</v>
       </c>
       <c r="U98">
         <v>0.09838110587651873</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.676090289843418</v>
+        <v>1.658811008504826</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1050364764611382</v>
+        <v>0.1053139530485155</v>
       </c>
       <c r="C99">
-        <v>-1724.247512904907</v>
+        <v>-1797.268174183424</v>
       </c>
       <c r="D99">
-        <v>3139.097487095094</v>
+        <v>3124.461825816575</v>
       </c>
       <c r="E99">
-        <v>1708.945</v>
+        <v>1767.329999999999</v>
       </c>
       <c r="F99">
-        <v>5663.345</v>
+        <v>5721.73</v>
       </c>
       <c r="G99">
         <v>800</v>
@@ -9405,28 +9405,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M99">
-        <v>557.166144060253</v>
+        <v>562.9101249268534</v>
       </c>
       <c r="N99">
-        <v>367.0671892730804</v>
+        <v>361.32320840648</v>
       </c>
       <c r="O99">
-        <v>69.74276596188528</v>
+        <v>68.65140959723121</v>
       </c>
       <c r="P99">
-        <v>297.3244233111951</v>
+        <v>292.6717988092488</v>
       </c>
       <c r="Q99">
-        <v>650.9244233111951</v>
+        <v>646.2717988092488</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9246147191319147</v>
+        <v>1.360951560186745</v>
       </c>
       <c r="T99">
-        <v>16.09580020788252</v>
+        <v>24.08746268697093</v>
       </c>
       <c r="U99">
         <v>0.09838110587651873</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.658811008504826</v>
+        <v>1.641884365560899</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1053139530485155</v>
+        <v>0.1055914296358928</v>
       </c>
       <c r="C100">
-        <v>-1797.268174183424</v>
+        <v>-1870.152994811525</v>
       </c>
       <c r="D100">
-        <v>3124.461825816575</v>
+        <v>3109.962005188475</v>
       </c>
       <c r="E100">
-        <v>1767.329999999999</v>
+        <v>1825.715</v>
       </c>
       <c r="F100">
-        <v>5721.73</v>
+        <v>5780.115</v>
       </c>
       <c r="G100">
         <v>800</v>
@@ -9487,28 +9487,28 @@
         <v>924.2333333333335</v>
       </c>
       <c r="M100">
-        <v>562.9101249268534</v>
+        <v>568.6541057934541</v>
       </c>
       <c r="N100">
-        <v>361.32320840648</v>
+        <v>355.5792275398794</v>
       </c>
       <c r="O100">
-        <v>68.65140959723121</v>
+        <v>67.56005323257709</v>
       </c>
       <c r="P100">
-        <v>292.6717988092488</v>
+        <v>288.0191743073023</v>
       </c>
       <c r="Q100">
-        <v>646.2717988092488</v>
+        <v>641.6191743073023</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.360951560186745</v>
+        <v>2.669962083351238</v>
       </c>
       <c r="T100">
-        <v>24.08746268697093</v>
+        <v>48.06245012423618</v>
       </c>
       <c r="U100">
         <v>0.09838110587651873</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.641884365560899</v>
+        <v>1.625299674999678</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1055914296358928</v>
-      </c>
-      <c r="C101">
-        <v>-1870.152994811525</v>
-      </c>
-      <c r="D101">
-        <v>3109.962005188475</v>
-      </c>
-      <c r="E101">
-        <v>1825.715</v>
-      </c>
-      <c r="F101">
-        <v>5780.115</v>
-      </c>
-      <c r="G101">
-        <v>800</v>
-      </c>
-      <c r="H101">
-        <v>1884.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1277.833333333333</v>
-      </c>
-      <c r="K101">
-        <v>353.6</v>
-      </c>
-      <c r="L101">
-        <v>924.2333333333335</v>
-      </c>
-      <c r="M101">
-        <v>568.6541057934541</v>
-      </c>
-      <c r="N101">
-        <v>355.5792275398794</v>
-      </c>
-      <c r="O101">
-        <v>67.56005323257709</v>
-      </c>
-      <c r="P101">
-        <v>288.0191743073023</v>
-      </c>
-      <c r="Q101">
-        <v>641.6191743073023</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.669962083351238</v>
-      </c>
-      <c r="T101">
-        <v>48.06245012423618</v>
-      </c>
-      <c r="U101">
-        <v>0.09838110587651873</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.07968869575998018</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.625299674999678</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
